--- a/reports/screener_2026-08-10.xlsx
+++ b/reports/screener_2026-08-10.xlsx
@@ -1212,7 +1212,7 @@
         <v>6.24</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.77</v>
+        <v>7.91</v>
       </c>
       <c r="AU3" t="n">
         <v>27.12</v>
@@ -1237,10 +1237,10 @@
         <v>10.78999996185303</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.991220388920124</v>
+        <v>6.095304552635779</v>
       </c>
       <c r="BD3" t="n">
-        <v>11.11371382144683</v>
+        <v>11.30678994513937</v>
       </c>
       <c r="BE3" t="n">
         <v>37.13441545313054</v>
@@ -1249,19 +1249,19 @@
         <v>25.57794609703624</v>
       </c>
       <c r="BG3" t="n">
-        <v>63.82521685004601</v>
+        <v>64.20370471810294</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL3" t="b">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ3" t="n">
@@ -1302,7 +1302,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="CB3" t="n">
-        <v>-23.76550462277683</v>
+        <v>-23.76550987166468</v>
       </c>
       <c r="CC3" t="b">
         <v>1</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1477,10 +1477,10 @@
         <v>14.03999996185303</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.50260757461884</v>
+        <v>15.50260772965087</v>
       </c>
       <c r="BD4" t="n">
-        <v>28.75733705091795</v>
+        <v>28.75733733850236</v>
       </c>
       <c r="BE4" t="n">
         <v>38.75624989469846</v>
@@ -1489,16 +1489,16 @@
         <v>23.45217391409519</v>
       </c>
       <c r="BG4" t="n">
-        <v>71.67343946141401</v>
+        <v>71.67343915263154</v>
       </c>
       <c r="BH4" t="n">
-        <v>35.62836157914889</v>
+        <v>35.62836160591569</v>
       </c>
       <c r="BI4" t="n">
-        <v>28.75733705091795</v>
+        <v>28.75733733850236</v>
       </c>
       <c r="BJ4" t="n">
-        <v>25.88160334582616</v>
+        <v>25.88160360465212</v>
       </c>
       <c r="BK4" t="n">
         <v>5</v>
@@ -1510,10 +1510,10 @@
         <v>4.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>84.3419046734118</v>
+        <v>84.34190651690156</v>
       </c>
       <c r="BO4" t="n">
-        <v>153.7632598002271</v>
+        <v>153.7632599908738</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -1530,16 +1530,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>A Vulcabras (VULC3) apresenta uma notável combinação de alta qualidade operacional e valuation descontado no setor de consumo discricionário, evidenciada por um ROE de 35,1% e um ROIC de 17,8% que se posicionam confortavelmente acima das médias setoriais de 12,2% e 12,5%, respectivamente. Essa rentabilidade robusta convive com múltiplos de preço bastante atrativos, visto que o P/L de 4,8 e o P/VP de 1,68 sugerem que o mercado ainda não precificou totalmente a eficiência da companhia, configurando uma relação favorável entre qualidade e preço. No âmbito financeiro, a excelente rentabilidade é suportada por um endividamento sob controle, com uma relação Dívida/Patrimônio de apenas 0,37 e uma sólida liquidez corrente de 2,96, o que garante robustez ao balanço. Essa estrutura de capital saudável confere sustentabilidade ao expressivo Dividend Yield de 28,86%, uma vez que a geração de lucro e a folga financeira permitem a distribuição de proventos sem comprometer a solvência da empresa. Por outro lado, o crescimento histórico acende um sinal de alerta, dado que o CAGR de receita de cinco anos contraiu 64,7%, situando-se drasticamente abaixo da média de expansão do setor, que foi de 49,8%. Esse descompasso de crescimento reflete-se no checklist de critérios fundamentalistas, no qual a Vulcabras atende a 5 dos 7 requisitos avaliados, penalizada justamente pela taxa de crescimento inferior à dos pares e por movimentações de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 15,50 por Bazin até os otimistas R$ 71,67 por Lynch, mas convergindo para uma média de R$ 35,63 e uma mediana de R$ 28,76. Tomando como referência o preço-teto ajustado com margem de segurança de R$ 25,88, o papel oferece um expressivo potencial de valorização de 84,3% frente à cotação atual de R$ 14,04, em um momento técnico de tendência lateral com pivô de alta. Em suma, os prós da tese concentram-se na rentabilidade excepcional, no endividamento muito baixo, no valuation atraente e no retorno de dividendos fora da curva, enquanto os contras residem na severa retração histórica de receita a longo prazo e nas transações de insiders identificadas no checklist.</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="b">
         <v>0</v>
       </c>
@@ -1550,7 +1542,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BZ4" t="n">
@@ -1566,14 +1558,14 @@
         <v>1</v>
       </c>
       <c r="CD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -1735,10 +1727,10 @@
         <v>4.210000038146973</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.562927795375999</v>
+        <v>3.563012712319659</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.609231060422478</v>
+        <v>6.609388581352968</v>
       </c>
       <c r="BE5" t="n">
         <v>12.73573070900625</v>
@@ -1747,16 +1739,16 @@
         <v>8.568907623857728</v>
       </c>
       <c r="BG5" t="n">
-        <v>24.4828797252006</v>
+        <v>24.48281447052321</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.869199297165614</v>
+        <v>7.869259906634151</v>
       </c>
       <c r="BI5" t="n">
-        <v>7.589069342140103</v>
+        <v>7.589148102605348</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6.830162407926093</v>
+        <v>6.830233292344813</v>
       </c>
       <c r="BK5" t="n">
         <v>4</v>
@@ -1768,10 +1760,10 @@
         <v>6.9</v>
       </c>
       <c r="BN5" t="n">
-        <v>62.23663529780828</v>
+        <v>62.23831901320204</v>
       </c>
       <c r="BO5" t="n">
-        <v>86.91684622001176</v>
+        <v>86.91828587483334</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
@@ -1985,10 +1977,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.057497389947812</v>
+        <v>3.057569932790789</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.671657658353192</v>
+        <v>5.671792225326912</v>
       </c>
       <c r="BE6" t="n">
         <v>12.71549888477204</v>
@@ -1997,10 +1989,10 @@
         <v>8.566302726978416</v>
       </c>
       <c r="BG6" t="n">
-        <v>23.48300704313526</v>
+        <v>23.48322266942012</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.984486423367882</v>
+        <v>8.98453127902579</v>
       </c>
       <c r="BI6" t="n">
         <v>8.566302726978416</v>
@@ -2021,7 +2013,7 @@
         <v>70.56797537198747</v>
       </c>
       <c r="BO6" t="n">
-        <v>98.771824364615</v>
+        <v>98.77281674643132</v>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
@@ -2235,10 +2227,10 @@
         <v>24.89999961853027</v>
       </c>
       <c r="BC7" t="n">
-        <v>16.36919309137854</v>
+        <v>16.36919305358049</v>
       </c>
       <c r="BD7" t="n">
-        <v>30.36485318450719</v>
+        <v>30.36485311439181</v>
       </c>
       <c r="BE7" t="n">
         <v>64.43847557529806</v>
@@ -2247,10 +2239,10 @@
         <v>47.06554188781961</v>
       </c>
       <c r="BG7" t="n">
-        <v>106.2977601940779</v>
+        <v>106.2977602173549</v>
       </c>
       <c r="BH7" t="n">
-        <v>62.04165771042569</v>
+        <v>62.04165769871609</v>
       </c>
       <c r="BI7" t="n">
         <v>55.75200873155883</v>
@@ -2271,7 +2263,7 @@
         <v>101.5132876590969</v>
       </c>
       <c r="BO7" t="n">
-        <v>149.163287794812</v>
+        <v>149.1632877477855</v>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
@@ -2479,10 +2471,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="BC8" t="n">
-        <v>19.20546150394244</v>
+        <v>19.20366125867804</v>
       </c>
       <c r="BD8" t="n">
-        <v>35.62613108981321</v>
+        <v>35.62279163484776</v>
       </c>
       <c r="BE8" t="n">
         <v>75.48756788005936</v>
@@ -2491,16 +2483,16 @@
         <v>56.56486624961452</v>
       </c>
       <c r="BG8" t="n">
-        <v>99.09361281859876</v>
+        <v>99.09652143724021</v>
       </c>
       <c r="BH8" t="n">
-        <v>43.43972015793833</v>
+        <v>43.43800692452839</v>
       </c>
       <c r="BI8" t="n">
-        <v>35.62613108981321</v>
+        <v>35.62279163484776</v>
       </c>
       <c r="BJ8" t="n">
-        <v>32.0635179808319</v>
+        <v>32.06051247136298</v>
       </c>
       <c r="BK8" t="n">
         <v>3</v>
@@ -2512,10 +2504,10 @@
         <v>3.9</v>
       </c>
       <c r="BN8" t="n">
-        <v>-36.40714171905611</v>
+        <v>-36.41310266625576</v>
       </c>
       <c r="BO8" t="n">
-        <v>-13.84426470548005</v>
+        <v>-13.84766262985958</v>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
@@ -2729,10 +2721,10 @@
         <v>15.60000038146973</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.388296788541452</v>
+        <v>6.38829676523164</v>
       </c>
       <c r="BD9" t="n">
-        <v>11.85029054274439</v>
+        <v>11.85029049950469</v>
       </c>
       <c r="BE9" t="n">
         <v>25.39312101406313</v>
@@ -2741,10 +2733,10 @@
         <v>18.62099144680682</v>
       </c>
       <c r="BG9" t="n">
-        <v>35.32345346571161</v>
+        <v>35.32345350332195</v>
       </c>
       <c r="BH9" t="n">
-        <v>22.79696411733149</v>
+        <v>22.79696411592415</v>
       </c>
       <c r="BI9" t="n">
         <v>22.00705623043497</v>
@@ -2765,7 +2757,7 @@
         <v>26.96378284014795</v>
       </c>
       <c r="BO9" t="n">
-        <v>46.13438179405809</v>
+        <v>46.13438178503668</v>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
@@ -2979,10 +2971,10 @@
         <v>31.36000061035156</v>
       </c>
       <c r="BC10" t="n">
-        <v>22.00307399921919</v>
+        <v>22.00390976620893</v>
       </c>
       <c r="BD10" t="n">
-        <v>40.8157022685516</v>
+        <v>40.81725261631757</v>
       </c>
       <c r="BE10" t="n">
         <v>45.81256980012768</v>
@@ -2991,16 +2983,16 @@
         <v>19.75712144035349</v>
       </c>
       <c r="BG10" t="n">
-        <v>59.9654157784598</v>
+        <v>59.95863816798309</v>
       </c>
       <c r="BH10" t="n">
-        <v>37.67077665734235</v>
+        <v>37.66989835819815</v>
       </c>
       <c r="BI10" t="n">
-        <v>40.8157022685516</v>
+        <v>40.81725261631757</v>
       </c>
       <c r="BJ10" t="n">
-        <v>36.73413204169644</v>
+        <v>36.73552735468581</v>
       </c>
       <c r="BK10" t="n">
         <v>5</v>
@@ -3012,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="BN10" t="n">
-        <v>17.13689836335954</v>
+        <v>17.14134770316253</v>
       </c>
       <c r="BO10" t="n">
-        <v>20.12364771736541</v>
+        <v>20.12084701861827</v>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
@@ -3229,10 +3221,10 @@
         <v>32.11000061035156</v>
       </c>
       <c r="BC11" t="n">
-        <v>44.83658198839334</v>
+        <v>44.8371712772876</v>
       </c>
       <c r="BD11" t="n">
-        <v>83.17185958846964</v>
+        <v>83.1729527193685</v>
       </c>
       <c r="BE11" t="n">
         <v>64.95534474613102</v>
@@ -3244,7 +3236,7 @@
         <v>147.0687050855797</v>
       </c>
       <c r="BH11" t="n">
-        <v>73.91364695878947</v>
+        <v>73.9139834427481</v>
       </c>
       <c r="BI11" t="n">
         <v>64.95534474613102</v>
@@ -3265,7 +3257,7 @@
         <v>82.06106870229006</v>
       </c>
       <c r="BO11" t="n">
-        <v>130.1888681215451</v>
+        <v>130.1899160317047</v>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
@@ -3452,7 +3444,7 @@
         <v>11.54</v>
       </c>
       <c r="AT12" t="n">
-        <v>10.15</v>
+        <v>10.16</v>
       </c>
       <c r="AU12" t="n">
         <v>13.99</v>
@@ -3473,10 +3465,10 @@
         <v>13.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.973464542971879</v>
+        <v>9.973917616330635</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.50077672721283</v>
+        <v>18.50161717829333</v>
       </c>
       <c r="BE12" t="n">
         <v>51.32042253521126</v>
@@ -3485,16 +3477,16 @@
         <v>48.95474340049645</v>
       </c>
       <c r="BG12" t="n">
-        <v>73.98456490996804</v>
+        <v>73.98546428866297</v>
       </c>
       <c r="BH12" t="n">
-        <v>14.23712063509236</v>
+        <v>14.23776739731198</v>
       </c>
       <c r="BI12" t="n">
-        <v>14.23712063509236</v>
+        <v>14.23776739731198</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12.81340857158312</v>
+        <v>12.81399065758078</v>
       </c>
       <c r="BK12" t="n">
         <v>2</v>
@@ -3506,10 +3498,10 @@
         <v>5.1</v>
       </c>
       <c r="BN12" t="n">
-        <v>-6.811574024850032</v>
+        <v>-6.807340672139761</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.542695527944417</v>
+        <v>3.547399253178041</v>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
@@ -3723,10 +3715,10 @@
         <v>7.760000228881836</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.255436204498124</v>
+        <v>7.25568765613328</v>
       </c>
       <c r="BD13" t="n">
-        <v>13.45883415934402</v>
+        <v>13.45930060212723</v>
       </c>
       <c r="BE13" t="n">
         <v>40.48031615460012</v>
@@ -3735,7 +3727,7 @@
         <v>27.21885716623862</v>
       </c>
       <c r="BG13" t="n">
-        <v>85.81736625834695</v>
+        <v>85.81875221224152</v>
       </c>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
@@ -3782,10 +3774,10 @@
         </is>
       </c>
       <c r="BZ13" t="n">
-        <v>8.420000076293945</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="CA13" t="n">
-        <v>-7.83847792674377</v>
+        <v>-5.596107338245182</v>
       </c>
       <c r="CB13" t="n">
         <v>-28.37008112858783</v>
@@ -3801,7 +3793,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -3957,10 +3949,10 @@
         <v>19.31999969482422</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.28432179013185</v>
+        <v>13.28320923196645</v>
       </c>
       <c r="BD14" t="n">
-        <v>24.64241692069458</v>
+        <v>24.64035312529776</v>
       </c>
       <c r="BE14" t="n">
         <v>19.39318151185007</v>
@@ -3969,10 +3961,10 @@
         <v>12.29335323539705</v>
       </c>
       <c r="BG14" t="n">
-        <v>27.99397743656636</v>
+        <v>27.99279745063336</v>
       </c>
       <c r="BH14" t="n">
-        <v>19.1066400742255</v>
+        <v>19.10558128970476</v>
       </c>
       <c r="BI14" t="n">
         <v>19.39318151185007</v>
@@ -3993,7 +3985,7 @@
         <v>-9.659090909090917</v>
       </c>
       <c r="BO14" t="n">
-        <v>-1.104345879756308</v>
+        <v>-1.109826130985425</v>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
@@ -4207,10 +4199,10 @@
         <v>7.019999980926514</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.169581645457426</v>
+        <v>3.169581649888222</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.879573952323525</v>
+        <v>5.879573960542651</v>
       </c>
       <c r="BE15" t="n">
         <v>21.83450698292871</v>
@@ -4219,7 +4211,7 @@
         <v>13.93706005001388</v>
       </c>
       <c r="BG15" t="n">
-        <v>35.13477529349805</v>
+        <v>35.13477530805935</v>
       </c>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
@@ -4266,10 +4258,10 @@
         </is>
       </c>
       <c r="BZ15" t="n">
-        <v>7.929999828338623</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="CA15" t="n">
-        <v>-11.47540816028945</v>
+        <v>-8.831166820555026</v>
       </c>
       <c r="CB15" t="n">
         <v>-59.61021964227024</v>
@@ -4285,7 +4277,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
         </is>
       </c>
     </row>
@@ -4447,22 +4439,22 @@
         <v>33.47999954223633</v>
       </c>
       <c r="BC16" t="n">
-        <v>24.07987549388067</v>
+        <v>24.08086488925293</v>
       </c>
       <c r="BD16" t="n">
-        <v>32.1070312060865</v>
+        <v>32.10533852574593</v>
       </c>
       <c r="BE16" t="n">
-        <v>36.65085143552953</v>
+        <v>36.64741343419143</v>
       </c>
       <c r="BF16" t="n">
         <v>36.13604254760104</v>
       </c>
       <c r="BG16" t="n">
-        <v>50.93895722258051</v>
+        <v>50.93701028581805</v>
       </c>
       <c r="BH16" t="n">
-        <v>35.98255158113565</v>
+        <v>35.98133393652187</v>
       </c>
       <c r="BI16" t="n">
         <v>36.13604254760104</v>
@@ -4483,7 +4475,7 @@
         <v>-2.860099350322265</v>
       </c>
       <c r="BO16" t="n">
-        <v>7.474767243476976</v>
+        <v>7.471130312083818</v>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
@@ -4512,7 +4504,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ16" t="n">
@@ -4535,7 +4527,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (+0.6%))</t>
+          <t>sem sinal (Lateral; sem novo topo (+0.6%))</t>
         </is>
       </c>
     </row>
@@ -4699,10 +4691,10 @@
         <v>40.86999893188477</v>
       </c>
       <c r="BC17" t="n">
-        <v>114.1776439158827</v>
+        <v>114.1767440032</v>
       </c>
       <c r="BD17" t="n">
-        <v>211.7995294639624</v>
+        <v>211.797860125936</v>
       </c>
       <c r="BE17" t="n">
         <v>137.0955660373349</v>
@@ -4758,10 +4750,10 @@
         </is>
       </c>
       <c r="BZ17" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="CA17" t="n">
-        <v>-5.063880008850452</v>
+        <v>-5.87286813587281</v>
       </c>
       <c r="CB17" t="n">
         <v>-16.85980497860918</v>
@@ -4777,7 +4769,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -4939,10 +4931,10 @@
         <v>9.439999580383301</v>
       </c>
       <c r="BC18" t="n">
-        <v>9.432360694008512</v>
+        <v>9.434030265257377</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.49702908738579</v>
+        <v>17.50012614205243</v>
       </c>
       <c r="BE18" t="n">
         <v>24.47749401958487</v>
@@ -4951,10 +4943,10 @@
         <v>17.5772497487596</v>
       </c>
       <c r="BG18" t="n">
-        <v>38.96008989028776</v>
+        <v>38.95884393271933</v>
       </c>
       <c r="BH18" t="n">
-        <v>21.58884468800531</v>
+        <v>21.58954882167473</v>
       </c>
       <c r="BI18" t="n">
         <v>17.5772497487596</v>
@@ -4975,7 +4967,7 @@
         <v>67.57971903682341</v>
       </c>
       <c r="BO18" t="n">
-        <v>128.6953988098452</v>
+        <v>128.702857853285</v>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
@@ -5189,10 +5181,10 @@
         <v>14.72000026702881</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.523498109876001</v>
+        <v>4.523236434623613</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.391088993819979</v>
+        <v>8.390603586226803</v>
       </c>
       <c r="BE19" t="n">
         <v>24.13861429927372</v>
@@ -5201,10 +5193,10 @@
         <v>20.32904459945394</v>
       </c>
       <c r="BG19" t="n">
-        <v>29.31380328899641</v>
+        <v>29.31401187733537</v>
       </c>
       <c r="BH19" t="n">
-        <v>20.54313779538601</v>
+        <v>20.54306859057246</v>
       </c>
       <c r="BI19" t="n">
         <v>22.23382944936383</v>
@@ -5225,7 +5217,7 @@
         <v>35.94053085208606</v>
       </c>
       <c r="BO19" t="n">
-        <v>39.55935749132014</v>
+        <v>39.55888734993225</v>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
@@ -5254,7 +5246,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ19" t="n">
@@ -5277,7 +5269,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -5439,10 +5431,10 @@
         <v>17.03000068664551</v>
       </c>
       <c r="BC20" t="n">
-        <v>10.09561411747972</v>
+        <v>10.09569791997182</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.72736418792487</v>
+        <v>18.72751964154773</v>
       </c>
       <c r="BE20" t="n">
         <v>37.48297493323139</v>
@@ -5451,10 +5443,10 @@
         <v>37.04197491142868</v>
       </c>
       <c r="BG20" t="n">
-        <v>42.13469686609152</v>
+        <v>42.13473712324961</v>
       </c>
       <c r="BH20" t="n">
-        <v>33.84675272466912</v>
+        <v>33.84680165236436</v>
       </c>
       <c r="BI20" t="n">
         <v>37.26247492233004</v>
@@ -5475,7 +5467,7 @@
         <v>96.9244044505253</v>
       </c>
       <c r="BO20" t="n">
-        <v>98.74780598929087</v>
+        <v>98.74809329224605</v>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
@@ -5691,10 +5683,10 @@
         <v>45.68999862670898</v>
       </c>
       <c r="BC21" t="n">
-        <v>121.4155479667476</v>
+        <v>121.4142902743408</v>
       </c>
       <c r="BD21" t="n">
-        <v>225.2258414783169</v>
+        <v>225.2235084589022</v>
       </c>
       <c r="BE21" t="n">
         <v>136.9666248425099</v>
@@ -5706,7 +5698,7 @@
         <v>310.1131128509659</v>
       </c>
       <c r="BH21" t="n">
-        <v>177.4102292193072</v>
+        <v>177.4095110769429</v>
       </c>
       <c r="BI21" t="n">
         <v>136.9666248425099</v>
@@ -5727,7 +5719,7 @@
         <v>169.7963800904977</v>
       </c>
       <c r="BO21" t="n">
-        <v>288.2911677646639</v>
+        <v>288.2895959931913</v>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
@@ -5760,10 +5752,10 @@
         </is>
       </c>
       <c r="BZ21" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="CA21" t="n">
-        <v>-6.180702441633368</v>
+        <v>-6.831162777889876</v>
       </c>
       <c r="CB21" t="n">
         <v>-16.33828883951265</v>
@@ -5779,7 +5771,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
         </is>
       </c>
     </row>
@@ -5941,28 +5933,28 @@
         <v>26.27000045776367</v>
       </c>
       <c r="BC22" t="n">
-        <v>16.70734195419739</v>
+        <v>16.70768559348043</v>
       </c>
       <c r="BD22" t="n">
-        <v>28.26185713482154</v>
+        <v>28.26190220158057</v>
       </c>
       <c r="BE22" t="n">
-        <v>48.38620269869156</v>
+        <v>48.38528465973992</v>
       </c>
       <c r="BF22" t="n">
         <v>53.40235057980205</v>
       </c>
       <c r="BG22" t="n">
-        <v>56.82499432074687</v>
+        <v>56.8251162255253</v>
       </c>
       <c r="BH22" t="n">
-        <v>46.7188511835155</v>
+        <v>46.71866341666196</v>
       </c>
       <c r="BI22" t="n">
-        <v>50.8942766392468</v>
+        <v>50.89381761977099</v>
       </c>
       <c r="BJ22" t="n">
-        <v>45.80484897532212</v>
+        <v>45.80443585779389</v>
       </c>
       <c r="BK22" t="n">
         <v>4</v>
@@ -5974,10 +5966,10 @@
         <v>3.4</v>
       </c>
       <c r="BN22" t="n">
-        <v>74.36181262716821</v>
+        <v>74.36024004429407</v>
       </c>
       <c r="BO22" t="n">
-        <v>77.84107487409086</v>
+        <v>77.84036011638142</v>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
@@ -6191,10 +6183,10 @@
         <v>12.39000034332275</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.853327558146693</v>
+        <v>3.85351393913391</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.147922620362116</v>
+        <v>7.148268357093401</v>
       </c>
       <c r="BE23" t="n">
         <v>19.66077898790736</v>
@@ -6203,10 +6195,10 @@
         <v>18.56644334558858</v>
       </c>
       <c r="BG23" t="n">
-        <v>20.06899048854631</v>
+        <v>20.06892697861108</v>
       </c>
       <c r="BH23" t="n">
-        <v>19.43207094068075</v>
+        <v>19.43204977070235</v>
       </c>
       <c r="BI23" t="n">
         <v>19.66077898790736</v>
@@ -6227,7 +6219,7 @@
         <v>42.81437125748499</v>
       </c>
       <c r="BO23" t="n">
-        <v>56.83672641020645</v>
+        <v>56.83655554678582</v>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
@@ -6441,10 +6433,10 @@
         <v>21.6299991607666</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.04249252145397</v>
+        <v>3.042492522367858</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.643823627297114</v>
+        <v>5.643823628992376</v>
       </c>
       <c r="BE24" t="n">
         <v>32.8666845046052</v>
@@ -6453,7 +6445,7 @@
         <v>27.46815743134023</v>
       </c>
       <c r="BG24" t="n">
-        <v>42.09230306328607</v>
+        <v>42.09230306475333</v>
       </c>
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
@@ -6500,10 +6492,10 @@
         </is>
       </c>
       <c r="BZ24" t="n">
-        <v>23.35000038146973</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="CA24" t="n">
-        <v>-7.366172131063841</v>
+        <v>-5.29772759955166</v>
       </c>
       <c r="CB24" t="n">
         <v>-39.73503176095192</v>
@@ -6519,7 +6511,7 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -6675,28 +6667,28 @@
         <v>23.53000068664551</v>
       </c>
       <c r="BC25" t="n">
-        <v>16.88052200439253</v>
+        <v>16.88052201842914</v>
       </c>
       <c r="BD25" t="n">
-        <v>29.59210750656573</v>
+        <v>29.59210750444302</v>
       </c>
       <c r="BE25" t="n">
-        <v>49.02408039903741</v>
+        <v>49.02408035475595</v>
       </c>
       <c r="BF25" t="n">
         <v>49.67482203402362</v>
       </c>
       <c r="BG25" t="n">
-        <v>61.12609935860196</v>
+        <v>61.12609936368955</v>
       </c>
       <c r="BH25" t="n">
-        <v>31.83223663666523</v>
+        <v>31.83223662587604</v>
       </c>
       <c r="BI25" t="n">
-        <v>29.59210750656573</v>
+        <v>29.59210750444302</v>
       </c>
       <c r="BJ25" t="n">
-        <v>26.63289675590916</v>
+        <v>26.63289675399872</v>
       </c>
       <c r="BK25" t="n">
         <v>3</v>
@@ -6708,10 +6700,10 @@
         <v>2.9</v>
       </c>
       <c r="BN25" t="n">
-        <v>13.18697823508652</v>
+        <v>13.18697822696737</v>
       </c>
       <c r="BO25" t="n">
-        <v>35.28361966743021</v>
+        <v>35.28361962157731</v>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
@@ -6923,10 +6915,10 @@
         <v>3.559999942779541</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.971223935552619</v>
+        <v>4.97136938593848</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.238102050164614</v>
+        <v>7.238313825926427</v>
       </c>
       <c r="BE26" t="n">
         <v>6.683032383557261</v>
@@ -6936,7 +6928,7 @@
       </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="n">
-        <v>6.516692818220029</v>
+        <v>6.516782124756947</v>
       </c>
       <c r="BI26" t="n">
         <v>6.928722643581441</v>
@@ -6957,7 +6949,7 @@
         <v>75.16433931048137</v>
       </c>
       <c r="BO26" t="n">
-        <v>83.0531719933678</v>
+        <v>83.05568060399573</v>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
@@ -7171,10 +7163,10 @@
         <v>27.79000091552734</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.35600930737357</v>
+        <v>7.356371103595649</v>
       </c>
       <c r="BD27" t="n">
-        <v>13.64539726517797</v>
+        <v>13.64606839716993</v>
       </c>
       <c r="BE27" t="n">
         <v>35.78401478432821</v>
@@ -7183,10 +7175,10 @@
         <v>28.28986696159874</v>
       </c>
       <c r="BG27" t="n">
-        <v>44.29379339956643</v>
+        <v>44.29324627113758</v>
       </c>
       <c r="BH27" t="n">
-        <v>30.50326810266784</v>
+        <v>30.50329910355861</v>
       </c>
       <c r="BI27" t="n">
         <v>32.03694087296348</v>
@@ -7207,7 +7199,7 @@
         <v>3.754033234151066</v>
       </c>
       <c r="BO27" t="n">
-        <v>9.763465627035984</v>
+        <v>9.763577181155281</v>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
@@ -7240,13 +7232,13 @@
         </is>
       </c>
       <c r="BZ27" t="n">
-        <v>29.21999931335449</v>
+        <v>29.06999969482422</v>
       </c>
       <c r="CA27" t="n">
-        <v>-4.89390291386349</v>
+        <v>-4.403160621720859</v>
       </c>
       <c r="CB27" t="n">
-        <v>-21.22606264717445</v>
+        <v>-21.22605409112423</v>
       </c>
       <c r="CC27" t="b">
         <v>1</v>
@@ -7259,7 +7251,7 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -7415,10 +7407,10 @@
         <v>15.14999961853027</v>
       </c>
       <c r="BC28" t="n">
-        <v>9.409156498452109</v>
+        <v>9.409156371490303</v>
       </c>
       <c r="BD28" t="n">
-        <v>17.45398530462866</v>
+        <v>17.45398506911451</v>
       </c>
       <c r="BE28" t="n">
         <v>30.97800847924785</v>
@@ -7427,16 +7419,16 @@
         <v>29.43218226899666</v>
       </c>
       <c r="BG28" t="n">
-        <v>34.7506469833056</v>
+        <v>34.75064696016124</v>
       </c>
       <c r="BH28" t="n">
-        <v>19.28038342744287</v>
+        <v>19.28038330661755</v>
       </c>
       <c r="BI28" t="n">
-        <v>17.45398530462866</v>
+        <v>17.45398506911451</v>
       </c>
       <c r="BJ28" t="n">
-        <v>15.7085867741658</v>
+        <v>15.70858656220306</v>
       </c>
       <c r="BK28" t="n">
         <v>3</v>
@@ -7448,10 +7440,10 @@
         <v>3.3</v>
       </c>
       <c r="BN28" t="n">
-        <v>3.687044024425612</v>
+        <v>3.687042625331594</v>
       </c>
       <c r="BO28" t="n">
-        <v>27.26326015124545</v>
+        <v>27.26325935371856</v>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
@@ -7490,7 +7482,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="CB28" t="n">
-        <v>-16.71340819915189</v>
+        <v>-16.71342624530195</v>
       </c>
       <c r="CC28" t="b">
         <v>1</v>
@@ -7665,10 +7657,10 @@
         <v>21.67000007629395</v>
       </c>
       <c r="BC29" t="n">
-        <v>11.24293050073338</v>
+        <v>11.24293048606617</v>
       </c>
       <c r="BD29" t="n">
-        <v>20.85563607886042</v>
+        <v>20.85563605165274</v>
       </c>
       <c r="BE29" t="n">
         <v>57.77213300018003</v>
@@ -7677,10 +7669,10 @@
         <v>47.81129458798794</v>
       </c>
       <c r="BG29" t="n">
-        <v>83.49262998802884</v>
+        <v>83.49262998490619</v>
       </c>
       <c r="BH29" t="n">
-        <v>52.48292341376431</v>
+        <v>52.48292340618172</v>
       </c>
       <c r="BI29" t="n">
         <v>52.79171379408398</v>
@@ -7701,7 +7693,7 @@
         <v>119.2549249995263</v>
       </c>
       <c r="BO29" t="n">
-        <v>142.1916161928324</v>
+        <v>142.1916161578411</v>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
@@ -7907,10 +7899,10 @@
         <v>38.38000106811523</v>
       </c>
       <c r="BC30" t="n">
-        <v>35.20932546220636</v>
+        <v>35.20215235865994</v>
       </c>
       <c r="BD30" t="n">
-        <v>51.26477787297246</v>
+        <v>51.25433383420889</v>
       </c>
       <c r="BE30" t="n">
         <v>49.21726400843384</v>
@@ -7920,7 +7912,7 @@
       </c>
       <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="n">
-        <v>45.23045578120422</v>
+        <v>45.22458340043422</v>
       </c>
       <c r="BI30" t="n">
         <v>49.21726400843384</v>
@@ -7941,7 +7933,7 @@
         <v>15.41307028360048</v>
       </c>
       <c r="BO30" t="n">
-        <v>17.84902168431701</v>
+        <v>17.83372105741088</v>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
@@ -8155,28 +8147,28 @@
         <v>11.57999992370605</v>
       </c>
       <c r="BC31" t="n">
-        <v>10.02516923195222</v>
+        <v>10.02516919997956</v>
       </c>
       <c r="BD31" t="n">
-        <v>16.49101883006962</v>
+        <v>16.49101899634692</v>
       </c>
       <c r="BE31" t="n">
-        <v>18.92375886756921</v>
+        <v>18.92375911872798</v>
       </c>
       <c r="BF31" t="n">
         <v>12.17705177601623</v>
       </c>
       <c r="BG31" t="n">
-        <v>27.66777750578778</v>
+        <v>27.66777761966962</v>
       </c>
       <c r="BH31" t="n">
-        <v>17.05695524227901</v>
+        <v>17.05695534214806</v>
       </c>
       <c r="BI31" t="n">
-        <v>16.49101883006962</v>
+        <v>16.49101899634692</v>
       </c>
       <c r="BJ31" t="n">
-        <v>14.84191694706266</v>
+        <v>14.84191709671223</v>
       </c>
       <c r="BK31" t="n">
         <v>5</v>
@@ -8188,10 +8180,10 @@
         <v>2.8</v>
       </c>
       <c r="BN31" t="n">
-        <v>28.16854097450339</v>
+        <v>28.16854226681407</v>
       </c>
       <c r="BO31" t="n">
-        <v>47.2966783649176</v>
+        <v>47.29667922734466</v>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
@@ -8224,10 +8216,10 @@
         </is>
       </c>
       <c r="BZ31" t="n">
-        <v>12.38000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="CA31" t="n">
-        <v>-6.46203702212963</v>
+        <v>-3.820598335584846</v>
       </c>
       <c r="CB31" t="n">
         <v>-32.90019903655219</v>
@@ -8243,7 +8235,7 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -8403,10 +8395,10 @@
         <v>6.110000133514404</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.214093399413781</v>
+        <v>7.214093422639239</v>
       </c>
       <c r="BD32" t="n">
-        <v>10.50371998954647</v>
+        <v>10.50372002336273</v>
       </c>
       <c r="BE32" t="n">
         <v>8.552355503169556</v>
@@ -8416,7 +8408,7 @@
       </c>
       <c r="BG32" t="inlineStr"/>
       <c r="BH32" t="n">
-        <v>8.822148337417094</v>
+        <v>8.822148351677525</v>
       </c>
       <c r="BI32" t="n">
         <v>8.785389980354065</v>
@@ -8437,7 +8429,7 @@
         <v>29.4083602216016</v>
       </c>
       <c r="BO32" t="n">
-        <v>44.38867667164341</v>
+        <v>44.38867690503834</v>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
@@ -8651,10 +8643,10 @@
         <v>13.52999973297119</v>
       </c>
       <c r="BC33" t="n">
-        <v>8.476983910706878</v>
+        <v>8.47698390092085</v>
       </c>
       <c r="BD33" t="n">
-        <v>15.72480515436126</v>
+        <v>15.72480513620818</v>
       </c>
       <c r="BE33" t="n">
         <v>13.60185860863947</v>
@@ -8666,7 +8658,7 @@
         <v>30.79666100069315</v>
       </c>
       <c r="BH33" t="n">
-        <v>15.93413122503725</v>
+        <v>15.93413121944943</v>
       </c>
       <c r="BI33" t="n">
         <v>13.60185860863947</v>
@@ -8687,7 +8679,7 @@
         <v>-9.52200303490136</v>
       </c>
       <c r="BO33" t="n">
-        <v>17.76889534008963</v>
+        <v>17.76889529879013</v>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
@@ -8901,10 +8893,10 @@
         <v>32.20999908447266</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.192050002079939</v>
+        <v>3.192362671148793</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.921252753858287</v>
+        <v>5.921832754981011</v>
       </c>
       <c r="BE34" t="n">
         <v>32.6037041916931</v>
@@ -8913,7 +8905,7 @@
         <v>22.83489900991191</v>
       </c>
       <c r="BG34" t="n">
-        <v>40.32381102339259</v>
+        <v>40.32414542881382</v>
       </c>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr"/>
@@ -8966,7 +8958,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="CB34" t="n">
-        <v>-32.45081207696994</v>
+        <v>-32.45080650614594</v>
       </c>
       <c r="CC34" t="b">
         <v>1</v>
@@ -9210,10 +9202,10 @@
         </is>
       </c>
       <c r="BZ35" t="n">
-        <v>9.979999542236328</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="CA35" t="n">
-        <v>-8.016024787124209</v>
+        <v>-6.134963641897039</v>
       </c>
       <c r="CB35" t="n">
         <v>-49.20898677565268</v>
@@ -9229,7 +9221,7 @@
       </c>
       <c r="CF35" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.1%))</t>
         </is>
       </c>
     </row>
@@ -9391,10 +9383,10 @@
         <v>4.559999942779541</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.956948888576273</v>
+        <v>2.957201535081606</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.485140188308986</v>
+        <v>5.485608847576378</v>
       </c>
       <c r="BE36" t="n">
         <v>14.3175353653623</v>
@@ -9403,7 +9395,7 @@
         <v>15.35857567147518</v>
       </c>
       <c r="BG36" t="n">
-        <v>17.28898861901261</v>
+        <v>17.28942992564379</v>
       </c>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr"/>
@@ -9592,7 +9584,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>188206235648</v>
+        <v>188534882304</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.4</v>
@@ -9625,28 +9617,28 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BC37" t="n">
-        <v>10.29196479333712</v>
+        <v>10.29196489591731</v>
       </c>
       <c r="BD37" t="n">
-        <v>17.71772032851441</v>
+        <v>17.71772031125781</v>
       </c>
       <c r="BE37" t="n">
-        <v>28.76383900524755</v>
+        <v>28.76383869054264</v>
       </c>
       <c r="BF37" t="n">
         <v>29.45627353735216</v>
       </c>
       <c r="BG37" t="n">
-        <v>32.16446221345369</v>
+        <v>32.16446220460018</v>
       </c>
       <c r="BH37" t="n">
-        <v>18.92450804236636</v>
+        <v>18.92450796590592</v>
       </c>
       <c r="BI37" t="n">
-        <v>17.71772032851441</v>
+        <v>17.71772031125781</v>
       </c>
       <c r="BJ37" t="n">
-        <v>15.94594829566297</v>
+        <v>15.94594828013203</v>
       </c>
       <c r="BK37" t="n">
         <v>3</v>
@@ -9658,10 +9650,10 @@
         <v>2.8</v>
       </c>
       <c r="BN37" t="n">
-        <v>-7.880134098000424</v>
+        <v>-7.880134187722765</v>
       </c>
       <c r="BO37" t="n">
-        <v>9.327028458900521</v>
+        <v>9.327028017187988</v>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
@@ -9700,7 +9692,7 @@
         <v>-8.657228523376116</v>
       </c>
       <c r="CB37" t="n">
-        <v>-18.49891039167376</v>
+        <v>-18.49889545631056</v>
       </c>
       <c r="CC37" t="b">
         <v>1</v>
@@ -9869,10 +9861,10 @@
         <v>29.27000045776367</v>
       </c>
       <c r="BC38" t="n">
-        <v>15.30076006391005</v>
+        <v>15.30119803780329</v>
       </c>
       <c r="BD38" t="n">
-        <v>28.38290991855315</v>
+        <v>28.3837223601251</v>
       </c>
       <c r="BE38" t="n">
         <v>54.77789633691646</v>
@@ -9881,16 +9873,16 @@
         <v>49.52629840645571</v>
       </c>
       <c r="BG38" t="n">
-        <v>61.51138830760567</v>
+        <v>61.51129230422315</v>
       </c>
       <c r="BH38" t="n">
-        <v>32.82052210645989</v>
+        <v>32.82093891161495</v>
       </c>
       <c r="BI38" t="n">
-        <v>28.38290991855315</v>
+        <v>28.3837223601251</v>
       </c>
       <c r="BJ38" t="n">
-        <v>25.54461892669783</v>
+        <v>25.54535012411259</v>
       </c>
       <c r="BK38" t="n">
         <v>3</v>
@@ -9902,10 +9894,10 @@
         <v>3.6</v>
       </c>
       <c r="BN38" t="n">
-        <v>-12.72764425282988</v>
+        <v>-12.72514614075842</v>
       </c>
       <c r="BO38" t="n">
-        <v>12.13024117925652</v>
+        <v>12.1316651804473</v>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
@@ -10117,10 +10109,10 @@
         <v>10.92000007629395</v>
       </c>
       <c r="BC39" t="n">
-        <v>13.59146666882773</v>
+        <v>13.59140307875292</v>
       </c>
       <c r="BD39" t="n">
-        <v>19.78917546981318</v>
+        <v>19.78908288266425</v>
       </c>
       <c r="BE39" t="n">
         <v>17.5801858813401</v>
@@ -10130,7 +10122,7 @@
       </c>
       <c r="BG39" t="inlineStr"/>
       <c r="BH39" t="n">
-        <v>17.64279923284483</v>
+        <v>17.64276018853889</v>
       </c>
       <c r="BI39" t="n">
         <v>18.5952773963692</v>
@@ -10151,7 +10143,7 @@
         <v>53.25777966855196</v>
       </c>
       <c r="BO39" t="n">
-        <v>61.56409441008432</v>
+        <v>61.56373686149765</v>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
@@ -10180,14 +10172,14 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ39" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="CA39" t="n">
-        <v>-3.191486393612009</v>
+        <v>-3.703704326653801</v>
       </c>
       <c r="CB39" t="n">
         <v>-18.11425560893279</v>
@@ -10203,7 +10195,7 @@
       </c>
       <c r="CF39" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -10365,10 +10357,10 @@
         <v>8.729999542236328</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.378128805017484</v>
+        <v>2.378314290465513</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.411428933307432</v>
+        <v>4.411773008813526</v>
       </c>
       <c r="BE40" t="n">
         <v>13.85299328558459</v>
@@ -10377,10 +10369,10 @@
         <v>15.19033105613702</v>
       </c>
       <c r="BG40" t="n">
-        <v>11.5619104374289</v>
+        <v>11.5619453915507</v>
       </c>
       <c r="BH40" t="n">
-        <v>13.53507825971684</v>
+        <v>13.53508991109077</v>
       </c>
       <c r="BI40" t="n">
         <v>13.85299328558459</v>
@@ -10401,7 +10393,7 @@
         <v>42.81437125748504</v>
       </c>
       <c r="BO40" t="n">
-        <v>55.04099621349597</v>
+        <v>55.04112967712187</v>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
@@ -10434,10 +10426,10 @@
         </is>
       </c>
       <c r="BZ40" t="n">
-        <v>9.680000305175781</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="CA40" t="n">
-        <v>-9.81405715898066</v>
+        <v>-5.005441340050498</v>
       </c>
       <c r="CB40" t="n">
         <v>-38.87866417350647</v>
@@ -10453,7 +10445,7 @@
       </c>
       <c r="CF40" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
         </is>
       </c>
     </row>
@@ -10615,10 +10607,10 @@
         <v>3.730000019073486</v>
       </c>
       <c r="BC41" t="n">
-        <v>0.862959732186426</v>
+        <v>0.8629597286553933</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.60079030320582</v>
+        <v>1.600790296655755</v>
       </c>
       <c r="BE41" t="n">
         <v>9.964213760629777</v>
@@ -10627,7 +10619,7 @@
         <v>8.938110288944346</v>
       </c>
       <c r="BG41" t="n">
-        <v>12.42769746260571</v>
+        <v>12.42769746046456</v>
       </c>
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr"/>
@@ -10674,10 +10666,10 @@
         </is>
       </c>
       <c r="BZ41" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="CA41" t="n">
-        <v>-6.28140700507328</v>
+        <v>-7.444173079810589</v>
       </c>
       <c r="CB41" t="n">
         <v>-50.82278080073881</v>
@@ -10693,7 +10685,7 @@
       </c>
       <c r="CF41" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -10845,28 +10837,28 @@
         <v>13.21000003814697</v>
       </c>
       <c r="BC42" t="n">
-        <v>8.866942296153921</v>
+        <v>8.86683587771911</v>
       </c>
       <c r="BD42" t="n">
-        <v>12.10923275158588</v>
+        <v>12.10932066192482</v>
       </c>
       <c r="BE42" t="n">
-        <v>14.77750254834482</v>
+        <v>14.77778718838715</v>
       </c>
       <c r="BF42" t="n">
         <v>16.56967199529428</v>
       </c>
       <c r="BG42" t="n">
-        <v>19.38660580884031</v>
+        <v>19.38671549383291</v>
       </c>
       <c r="BH42" t="n">
-        <v>11.9178925320282</v>
+        <v>11.91798124267702</v>
       </c>
       <c r="BI42" t="n">
-        <v>12.10923275158588</v>
+        <v>12.10932066192482</v>
       </c>
       <c r="BJ42" t="n">
-        <v>10.89830947642729</v>
+        <v>10.89838859573234</v>
       </c>
       <c r="BK42" t="n">
         <v>3</v>
@@ -10878,10 +10870,10 @@
         <v>1.7</v>
       </c>
       <c r="BN42" t="n">
-        <v>-17.49955000033409</v>
+        <v>-17.4989510653998</v>
       </c>
       <c r="BO42" t="n">
-        <v>-9.781283136922825</v>
+        <v>-9.780611595298572</v>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
@@ -11095,10 +11087,10 @@
         <v>32.06000137329102</v>
       </c>
       <c r="BC43" t="n">
-        <v>10.53316571572151</v>
+        <v>10.53323127692031</v>
       </c>
       <c r="BD43" t="n">
-        <v>19.5390224026634</v>
+        <v>19.53914401868718</v>
       </c>
       <c r="BE43" t="n">
         <v>55.7473777160244</v>
@@ -11107,10 +11099,10 @@
         <v>52.52680285382178</v>
       </c>
       <c r="BG43" t="n">
-        <v>58.6485861312441</v>
+        <v>58.64857459708476</v>
       </c>
       <c r="BH43" t="n">
-        <v>55.64092223369676</v>
+        <v>55.64091838897698</v>
       </c>
       <c r="BI43" t="n">
         <v>55.7473777160244</v>
@@ -11131,7 +11123,7 @@
         <v>56.49606299212597</v>
       </c>
       <c r="BO43" t="n">
-        <v>73.55246366287076</v>
+        <v>73.55245167060747</v>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
@@ -11345,28 +11337,28 @@
         <v>10.22999954223633</v>
       </c>
       <c r="BC44" t="n">
-        <v>7.128662244245931</v>
+        <v>7.12866225188</v>
       </c>
       <c r="BD44" t="n">
-        <v>11.18073448119771</v>
+        <v>11.18073448395422</v>
       </c>
       <c r="BE44" t="n">
-        <v>19.06932858947494</v>
+        <v>19.06932857375501</v>
       </c>
       <c r="BF44" t="n">
         <v>24.00353367466198</v>
       </c>
       <c r="BG44" t="n">
-        <v>24.53460084233446</v>
+        <v>24.5346008480833</v>
       </c>
       <c r="BH44" t="n">
-        <v>19.69704939691727</v>
+        <v>19.69704939511363</v>
       </c>
       <c r="BI44" t="n">
-        <v>21.53643113206846</v>
+        <v>21.5364311242085</v>
       </c>
       <c r="BJ44" t="n">
-        <v>19.38278801886161</v>
+        <v>19.38278801178765</v>
       </c>
       <c r="BK44" t="n">
         <v>4</v>
@@ -11378,10 +11370,10 @@
         <v>3.4</v>
       </c>
       <c r="BN44" t="n">
-        <v>89.47007708882499</v>
+        <v>89.47007701967577</v>
       </c>
       <c r="BO44" t="n">
-        <v>92.54203595605833</v>
+        <v>92.54203593842738</v>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
@@ -11603,28 +11595,28 @@
         <v>15.47999954223633</v>
       </c>
       <c r="BC45" t="n">
-        <v>6.00531792663848</v>
+        <v>6.005304912799816</v>
       </c>
       <c r="BD45" t="n">
-        <v>8.192697921389517</v>
+        <v>8.192707861552107</v>
       </c>
       <c r="BE45" t="n">
-        <v>10.04301041040262</v>
+        <v>10.04304435934426</v>
       </c>
       <c r="BF45" t="n">
         <v>11.40440666376979</v>
       </c>
       <c r="BG45" t="n">
-        <v>9.091315837895866</v>
+        <v>9.091337231468279</v>
       </c>
       <c r="BH45" t="n">
-        <v>8.947349752019255</v>
+        <v>8.94736020578685</v>
       </c>
       <c r="BI45" t="n">
-        <v>9.091315837895866</v>
+        <v>9.091337231468279</v>
       </c>
       <c r="BJ45" t="n">
-        <v>8.18218425410628</v>
+        <v>8.18220350832145</v>
       </c>
       <c r="BK45" t="n">
         <v>5</v>
@@ -11636,10 +11628,10 @@
         <v>1.9</v>
       </c>
       <c r="BN45" t="n">
-        <v>-47.14351100733795</v>
+        <v>-47.14338662609933</v>
       </c>
       <c r="BO45" t="n">
-        <v>-42.20058128808788</v>
+        <v>-42.20051375728746</v>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
@@ -11847,10 +11839,10 @@
         <v>40.75</v>
       </c>
       <c r="BC46" t="n">
-        <v>20.81475789541569</v>
+        <v>20.8234608320114</v>
       </c>
       <c r="BD46" t="n">
-        <v>38.6113758959961</v>
+        <v>38.62751984338114</v>
       </c>
       <c r="BE46" t="n">
         <v>56.01011410788382</v>
@@ -11859,16 +11851,16 @@
         <v>42.35975890449271</v>
       </c>
       <c r="BG46" t="n">
-        <v>59.70827304423335</v>
+        <v>59.69355883405037</v>
       </c>
       <c r="BH46" t="n">
-        <v>38.47874929976521</v>
+        <v>38.48703159442545</v>
       </c>
       <c r="BI46" t="n">
-        <v>38.6113758959961</v>
+        <v>38.62751984338114</v>
       </c>
       <c r="BJ46" t="n">
-        <v>34.75023830639649</v>
+        <v>34.76476785904303</v>
       </c>
       <c r="BK46" t="n">
         <v>3</v>
@@ -11880,10 +11872,10 @@
         <v>2.7</v>
       </c>
       <c r="BN46" t="n">
-        <v>-14.72334157939512</v>
+        <v>-14.68768623547722</v>
       </c>
       <c r="BO46" t="n">
-        <v>-5.573621350269431</v>
+        <v>-5.553296700796439</v>
       </c>
       <c r="BP46" t="inlineStr">
         <is>
@@ -11922,7 +11914,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="CB46" t="n">
-        <v>-16.35819966493404</v>
+        <v>-16.32274316665727</v>
       </c>
       <c r="CC46" t="b">
         <v>1</v>
@@ -12097,10 +12089,10 @@
         <v>14.60999965667725</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.796142723561469</v>
+        <v>1.796142703837045</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.331844752206525</v>
+        <v>3.331844715617718</v>
       </c>
       <c r="BE47" t="n">
         <v>12.42506389287378</v>
@@ -12109,7 +12101,7 @@
         <v>9.006705029899456</v>
       </c>
       <c r="BG47" t="n">
-        <v>15.68010224518737</v>
+        <v>15.68010222746324</v>
       </c>
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr"/>
@@ -12337,10 +12329,10 @@
         <v>10.76000022888184</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.224745449055138</v>
+        <v>4.224894025804548</v>
       </c>
       <c r="BD48" t="n">
-        <v>7.836902807997281</v>
+        <v>7.837178417867436</v>
       </c>
       <c r="BE48" t="n">
         <v>25.36832794175877</v>
@@ -12349,10 +12341,10 @@
         <v>28.51661379864785</v>
       </c>
       <c r="BG48" t="n">
-        <v>23.95401013502834</v>
+        <v>23.95416912748375</v>
       </c>
       <c r="BH48" t="n">
-        <v>25.94631729181166</v>
+        <v>25.94637028929679</v>
       </c>
       <c r="BI48" t="n">
         <v>25.36832794175877</v>
@@ -12373,7 +12365,7 @@
         <v>112.1886120996441</v>
       </c>
       <c r="BO48" t="n">
-        <v>141.1367726755891</v>
+        <v>141.137265217262</v>
       </c>
       <c r="BP48" t="inlineStr">
         <is>
@@ -12406,10 +12398,10 @@
         </is>
       </c>
       <c r="BZ48" t="n">
-        <v>12.0600004196167</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="CA48" t="n">
-        <v>-10.77943735905924</v>
+        <v>-10.40799314053285</v>
       </c>
       <c r="CB48" t="n">
         <v>-35.14712749925304</v>
@@ -12425,7 +12417,7 @@
       </c>
       <c r="CF48" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.4%))</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12474,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -12587,10 +12579,10 @@
         <v>33.63000106811523</v>
       </c>
       <c r="BC49" t="n">
-        <v>9.265734339630411</v>
+        <v>9.265734313710745</v>
       </c>
       <c r="BD49" t="n">
-        <v>17.18793720001441</v>
+        <v>17.18793715193343</v>
       </c>
       <c r="BE49" t="n">
         <v>62.58392052704027</v>
@@ -12599,7 +12591,7 @@
         <v>36.51831633599926</v>
       </c>
       <c r="BG49" t="n">
-        <v>89.06886190681941</v>
+        <v>89.06886185585377</v>
       </c>
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr"/>
@@ -12630,8 +12622,16 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BS49" t="inlineStr"/>
-      <c r="BT49" t="inlineStr"/>
+      <c r="BS49" t="inlineStr">
+        <is>
+          <t>A Construtora Tenda (TEND3) apresenta uma dinâmica intrigante de qualidade versus preço, onde a alta rentabilidade medida pelo ROE de 37,6% e pelo ROIC de 14,4% — ambos posicionados acima dos pares do setor de consumo discricionário, que registram 12,2% e 12,5% respectivamente — convive com um múltiplo P/L de 7,12, sugerindo que o mercado pode estar precificando o papel com desconto, embora o P/VP de 2,68 indique um prêmio sobre o valor patrimonial. Essa forte rentabilidade operacional é suportada por um endividamento controlado, com a relação dívida/patrimônio em 0,79 e uma liquidez corrente confortável de 1,96, demonstrando que a empresa consegue gerar retornos expressivos sem comprometer sua saúde financeira de curto prazo. Por outro lado, o dividendo atual de 2,45% mostra-se modesto e altamente sustentável frente ao lucro gerado, indicando uma postura conservadora de retenção de caixa para fazer frente à estrutura de capital, especialmente quando se observa que a companhia enfrenta uma severa contração histórica, com um CAGR de receita nos últimos cinco anos de -11,5%, performance que está drasticamente abaixo da média setorial de 49,8%. Esse gargalo no crescimento e a existência de vendas por parte de insiders pesaram no checklist de critérios fundamentalistas, no qual a empresa atendeu a apenas 4 dos 7 requisitos avaliados, falhando em atingir a margem líquida desejada de 15% e em superar a expansão de seus pares. No campo do valuation, a análise dos preços-teto revela uma dispersão brutal entre os métodos de fluxo de caixa descontado e múltiplos de crescimento, com o modelo DCF apontando R$ 62,58 e o método de Lynch alcançando R$ 89,07, enquanto as metodologias focadas em dividendos de Bazin e Gordon limitam-se a R$ 9,27 e R$ 17,19, respectivamente, situando o preço atual de R$ 33,63 próximo ao teto de Graham de R$ 36,52. Em balanço, os prós da TEND3 residem em sua eficiência operacional superior à média do setor e na sólida liquidez, ao passo que os contras concentram-se no encolhimento histórico de sua receita, no baixo retorno em dividendos e na tendência gráfica de baixa que atualmente pressiona o ativo.</t>
+        </is>
+      </c>
+      <c r="BT49" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="BU49" t="b">
         <v>0</v>
       </c>
@@ -12658,14 +12658,14 @@
         <v>1</v>
       </c>
       <c r="CD49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+0.5%))</t>
+          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -12827,28 +12827,28 @@
         <v>39.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>29.94848816372241</v>
+        <v>29.94881197511332</v>
       </c>
       <c r="BD50" t="n">
-        <v>34.22993623235111</v>
+        <v>34.22970054837481</v>
       </c>
       <c r="BE50" t="n">
-        <v>37.17367914326704</v>
+        <v>37.17302126563244</v>
       </c>
       <c r="BF50" t="n">
         <v>48.635437456445</v>
       </c>
       <c r="BG50" t="n">
-        <v>55.74358174330671</v>
+        <v>55.74321458326236</v>
       </c>
       <c r="BH50" t="n">
-        <v>41.14622454781845</v>
+        <v>41.14603716576559</v>
       </c>
       <c r="BI50" t="n">
-        <v>37.17367914326704</v>
+        <v>37.17302126563244</v>
       </c>
       <c r="BJ50" t="n">
-        <v>33.45631122894034</v>
+        <v>33.4557191390692</v>
       </c>
       <c r="BK50" t="n">
         <v>5</v>
@@ -12860,10 +12860,10 @@
         <v>1.9</v>
       </c>
       <c r="BN50" t="n">
-        <v>-14.76099049951507</v>
+        <v>-14.76249900874088</v>
       </c>
       <c r="BO50" t="n">
-        <v>4.831145344760368</v>
+        <v>4.830667938256283</v>
       </c>
       <c r="BP50" t="inlineStr">
         <is>
@@ -13077,10 +13077,10 @@
         <v>21.60000038146973</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.970936721719919</v>
+        <v>5.971129789919972</v>
       </c>
       <c r="BD51" t="n">
-        <v>11.07608761879045</v>
+        <v>11.07644576030155</v>
       </c>
       <c r="BE51" t="n">
         <v>32.85878358834372</v>
@@ -13089,10 +13089,10 @@
         <v>33.87983533191721</v>
       </c>
       <c r="BG51" t="n">
-        <v>29.48949481451582</v>
+        <v>29.4894780847462</v>
       </c>
       <c r="BH51" t="n">
-        <v>32.07603791159224</v>
+        <v>32.07603233500237</v>
       </c>
       <c r="BI51" t="n">
         <v>32.85878358834372</v>
@@ -13113,7 +13113,7 @@
         <v>36.91159586681971</v>
       </c>
       <c r="BO51" t="n">
-        <v>48.50017289402333</v>
+        <v>48.50014707647809</v>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
@@ -13335,28 +13335,28 @@
         <v>44.79999923706055</v>
       </c>
       <c r="BC52" t="n">
-        <v>32.52363716000399</v>
+        <v>32.52379706107593</v>
       </c>
       <c r="BD52" t="n">
-        <v>39.13675493205022</v>
+        <v>39.13655681504563</v>
       </c>
       <c r="BE52" t="n">
-        <v>42.97616582344318</v>
+        <v>42.9757369823044</v>
       </c>
       <c r="BF52" t="n">
         <v>48.75816249197349</v>
       </c>
       <c r="BG52" t="n">
-        <v>61.413686761819</v>
+        <v>61.4134056077642</v>
       </c>
       <c r="BH52" t="n">
-        <v>44.96168143385798</v>
+        <v>44.96153179163273</v>
       </c>
       <c r="BI52" t="n">
-        <v>42.97616582344318</v>
+        <v>42.9757369823044</v>
       </c>
       <c r="BJ52" t="n">
-        <v>38.67854924109886</v>
+        <v>38.67816328407396</v>
       </c>
       <c r="BK52" t="n">
         <v>5</v>
@@ -13368,10 +13368,10 @@
         <v>1.9</v>
       </c>
       <c r="BN52" t="n">
-        <v>-13.66395111653874</v>
+        <v>-13.66481262776972</v>
       </c>
       <c r="BO52" t="n">
-        <v>0.3608977668545954</v>
+        <v>0.3605637440247111</v>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="BZ52" t="n">
-        <v>47.18999862670898</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="CA52" t="n">
-        <v>-5.064631191355295</v>
+        <v>-4.416470539784967</v>
       </c>
       <c r="CB52" t="n">
         <v>-15.45867760032158</v>
@@ -13423,7 +13423,7 @@
       </c>
       <c r="CF52" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -13585,10 +13585,10 @@
         <v>17.01000022888184</v>
       </c>
       <c r="BC53" t="n">
-        <v>4.289789745148792</v>
+        <v>4.28978974483453</v>
       </c>
       <c r="BD53" t="n">
-        <v>7.95755997725101</v>
+        <v>7.957559976668052</v>
       </c>
       <c r="BE53" t="n">
         <v>53.40817607409581</v>
@@ -13597,7 +13597,7 @@
         <v>59.21244778820295</v>
       </c>
       <c r="BG53" t="n">
-        <v>49.87167345048983</v>
+        <v>49.87167344990439</v>
       </c>
       <c r="BH53" t="inlineStr"/>
       <c r="BI53" t="inlineStr"/>
@@ -13825,10 +13825,10 @@
         <v>26.88999938964844</v>
       </c>
       <c r="BC54" t="n">
-        <v>4.92953099137617</v>
+        <v>4.92961332041522</v>
       </c>
       <c r="BD54" t="n">
-        <v>9.144279989002793</v>
+        <v>9.144432709370232</v>
       </c>
       <c r="BE54" t="n">
         <v>32.80778010247162</v>
@@ -13837,7 +13837,7 @@
         <v>26.27467010357014</v>
       </c>
       <c r="BG54" t="n">
-        <v>42.01974116688378</v>
+        <v>42.01961712455591</v>
       </c>
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr"/>
@@ -13884,10 +13884,10 @@
         </is>
       </c>
       <c r="BZ54" t="n">
-        <v>29.29999923706055</v>
+        <v>29.29000091552734</v>
       </c>
       <c r="CA54" t="n">
-        <v>-8.225255666094988</v>
+        <v>-8.193927793995414</v>
       </c>
       <c r="CB54" t="n">
         <v>-23.86318934952274</v>
@@ -14059,10 +14059,10 @@
         <v>53.90999984741211</v>
       </c>
       <c r="BC55" t="n">
-        <v>9.565171248510964</v>
+        <v>9.5651712637509</v>
       </c>
       <c r="BD55" t="n">
-        <v>17.74339266598784</v>
+        <v>17.74339269425792</v>
       </c>
       <c r="BE55" t="n">
         <v>58.9362622094233</v>
@@ -14071,16 +14071,16 @@
         <v>43.81836007058834</v>
       </c>
       <c r="BG55" t="n">
-        <v>77.76917452065473</v>
+        <v>77.76917453825861</v>
       </c>
       <c r="BH55" t="n">
-        <v>13.6542819572494</v>
+        <v>13.65428197900441</v>
       </c>
       <c r="BI55" t="n">
-        <v>13.6542819572494</v>
+        <v>13.65428197900441</v>
       </c>
       <c r="BJ55" t="n">
-        <v>12.28885376152446</v>
+        <v>12.28885378110397</v>
       </c>
       <c r="BK55" t="n">
         <v>2</v>
@@ -14092,10 +14092,10 @@
         <v>6.2</v>
       </c>
       <c r="BN55" t="n">
-        <v>-77.20487145927089</v>
+        <v>-77.20487142295201</v>
       </c>
       <c r="BO55" t="n">
-        <v>-74.67207939918987</v>
+        <v>-74.67207935883556</v>
       </c>
       <c r="BP55" t="inlineStr">
         <is>
@@ -14309,28 +14309,28 @@
         <v>22.85000038146973</v>
       </c>
       <c r="BC56" t="n">
-        <v>9.749536076112411</v>
+        <v>9.749536059041692</v>
       </c>
       <c r="BD56" t="n">
-        <v>14.83800011875651</v>
+        <v>14.83800012820692</v>
       </c>
       <c r="BE56" t="n">
-        <v>20.27745782861943</v>
+        <v>20.2774578770386</v>
       </c>
       <c r="BF56" t="n">
         <v>21.84295533173045</v>
       </c>
       <c r="BG56" t="n">
-        <v>19.34340932121063</v>
+        <v>19.34340934087171</v>
       </c>
       <c r="BH56" t="n">
-        <v>17.21027173528589</v>
+        <v>17.21027174737788</v>
       </c>
       <c r="BI56" t="n">
-        <v>19.34340932121063</v>
+        <v>19.34340934087171</v>
       </c>
       <c r="BJ56" t="n">
-        <v>17.40906838908957</v>
+        <v>17.40906840678454</v>
       </c>
       <c r="BK56" t="n">
         <v>5</v>
@@ -14342,10 +14342,10 @@
         <v>2.2</v>
       </c>
       <c r="BN56" t="n">
-        <v>-23.81151816869334</v>
+        <v>-23.81151809125361</v>
       </c>
       <c r="BO56" t="n">
-        <v>-24.68152539182186</v>
+        <v>-24.68152533890285</v>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
@@ -14559,28 +14559,28 @@
         <v>25.25</v>
       </c>
       <c r="BC57" t="n">
-        <v>23.84003426283585</v>
+        <v>23.8394546539541</v>
       </c>
       <c r="BD57" t="n">
-        <v>29.17643732372149</v>
+        <v>29.17629081891948</v>
       </c>
       <c r="BE57" t="n">
-        <v>37.22237140002338</v>
+        <v>37.22308947716972</v>
       </c>
       <c r="BF57" t="n">
         <v>61.96622221610712</v>
       </c>
       <c r="BG57" t="n">
-        <v>66.06729468284735</v>
+        <v>66.06678887156686</v>
       </c>
       <c r="BH57" t="n">
-        <v>43.65447197710704</v>
+        <v>43.65436920754346</v>
       </c>
       <c r="BI57" t="n">
-        <v>37.22237140002338</v>
+        <v>37.22308947716972</v>
       </c>
       <c r="BJ57" t="n">
-        <v>33.50013426002105</v>
+        <v>33.50078052945275</v>
       </c>
       <c r="BK57" t="n">
         <v>5</v>
@@ -14592,10 +14592,10 @@
         <v>2.8</v>
       </c>
       <c r="BN57" t="n">
-        <v>32.67379904958831</v>
+        <v>32.67635853248614</v>
       </c>
       <c r="BO57" t="n">
-        <v>72.88899792913676</v>
+        <v>72.88859092096421</v>
       </c>
       <c r="BP57" t="inlineStr">
         <is>
@@ -14628,10 +14628,10 @@
         </is>
       </c>
       <c r="BZ57" t="n">
-        <v>26.54999923706055</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="CA57" t="n">
-        <v>-4.896419112682715</v>
+        <v>-4.283545097481212</v>
       </c>
       <c r="CB57" t="n">
         <v>-12.02090826211568</v>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="CF57" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -14809,10 +14809,10 @@
         <v>17.48999977111816</v>
       </c>
       <c r="BC58" t="n">
-        <v>4.023650646863912</v>
+        <v>4.023974876566939</v>
       </c>
       <c r="BD58" t="n">
-        <v>7.463871949932558</v>
+        <v>7.464473396031672</v>
       </c>
       <c r="BE58" t="n">
         <v>27.23178577759291</v>
@@ -14821,7 +14821,7 @@
         <v>33.75103601978793</v>
       </c>
       <c r="BG58" t="n">
-        <v>19.04707891521709</v>
+        <v>19.04723419640374</v>
       </c>
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr"/>
@@ -14868,13 +14868,13 @@
         </is>
       </c>
       <c r="BZ58" t="n">
-        <v>18.00869941711426</v>
+        <v>17.81902885437012</v>
       </c>
       <c r="CA58" t="n">
-        <v>-2.880272661462469</v>
+        <v>-1.846504015123462</v>
       </c>
       <c r="CB58" t="n">
-        <v>-39.62281758244762</v>
+        <v>-39.62282580198882</v>
       </c>
       <c r="CC58" t="b">
         <v>1</v>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="CF58" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
         </is>
       </c>
     </row>
@@ -15047,10 +15047,10 @@
         <v>5.449999809265137</v>
       </c>
       <c r="BC59" t="n">
-        <v>6.469480044243205</v>
+        <v>6.469162172284941</v>
       </c>
       <c r="BD59" t="n">
-        <v>9.419562944418105</v>
+        <v>9.419100122846874</v>
       </c>
       <c r="BE59" t="n">
         <v>4.268072139785951</v>
@@ -15060,13 +15060,13 @@
       </c>
       <c r="BG59" t="inlineStr"/>
       <c r="BH59" t="n">
-        <v>5.906721042393592</v>
+        <v>5.906525869011218</v>
       </c>
       <c r="BI59" t="n">
-        <v>5.368776092014578</v>
+        <v>5.368617156035446</v>
       </c>
       <c r="BJ59" t="n">
-        <v>4.83189848281312</v>
+        <v>4.831755440431902</v>
       </c>
       <c r="BK59" t="n">
         <v>4</v>
@@ -15078,10 +15078,10 @@
         <v>2.7</v>
       </c>
       <c r="BN59" t="n">
-        <v>-11.34130913915316</v>
+        <v>-11.34393377009305</v>
       </c>
       <c r="BO59" t="n">
-        <v>8.380206405732672</v>
+        <v>8.376625242627988</v>
       </c>
       <c r="BP59" t="inlineStr">
         <is>
@@ -15295,10 +15295,10 @@
         <v>48.11999893188477</v>
       </c>
       <c r="BC60" t="n">
-        <v>8.009597792940541</v>
+        <v>8.009589100297546</v>
       </c>
       <c r="BD60" t="n">
-        <v>14.8578039059047</v>
+        <v>14.85778778105195</v>
       </c>
       <c r="BE60" t="n">
         <v>19.73962804481341</v>
@@ -15307,16 +15307,16 @@
         <v>12.27215611980214</v>
       </c>
       <c r="BG60" t="n">
-        <v>15.68910802594344</v>
+        <v>15.68914461296023</v>
       </c>
       <c r="BH60" t="n">
-        <v>14.11365877788085</v>
+        <v>14.11366113178506</v>
       </c>
       <c r="BI60" t="n">
-        <v>14.8578039059047</v>
+        <v>14.85778778105195</v>
       </c>
       <c r="BJ60" t="n">
-        <v>13.37202351531423</v>
+        <v>13.37200900294675</v>
       </c>
       <c r="BK60" t="n">
         <v>5</v>
@@ -15328,10 +15328,10 @@
         <v>2.5</v>
       </c>
       <c r="BN60" t="n">
-        <v>-72.2110893347219</v>
+        <v>-72.21111949342473</v>
       </c>
       <c r="BO60" t="n">
-        <v>-70.66986888786275</v>
+        <v>-70.66986399612489</v>
       </c>
       <c r="BP60" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ60" t="n">
@@ -15370,7 +15370,7 @@
         <v>-2.135446972059685</v>
       </c>
       <c r="CB60" t="n">
-        <v>-11.35737468710545</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="CC60" t="b">
         <v>1</v>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="CF60" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -15545,28 +15545,28 @@
         <v>34.04000091552734</v>
       </c>
       <c r="BC61" t="n">
-        <v>15.41291056384467</v>
+        <v>15.41342429954083</v>
       </c>
       <c r="BD61" t="n">
-        <v>23.75471177736489</v>
+        <v>23.75503652995809</v>
       </c>
       <c r="BE61" t="n">
-        <v>44.61155365552684</v>
+        <v>44.61067660215662</v>
       </c>
       <c r="BF61" t="n">
         <v>61.90114319514688</v>
       </c>
       <c r="BG61" t="n">
-        <v>43.95187360773868</v>
+        <v>43.95203649620341</v>
       </c>
       <c r="BH61" t="n">
-        <v>43.55482055894431</v>
+        <v>43.55472320586625</v>
       </c>
       <c r="BI61" t="n">
-        <v>44.28171363163275</v>
+        <v>44.28135654918002</v>
       </c>
       <c r="BJ61" t="n">
-        <v>39.85354226846948</v>
+        <v>39.85322089426202</v>
       </c>
       <c r="BK61" t="n">
         <v>4</v>
@@ -15578,10 +15578,10 @@
         <v>4</v>
       </c>
       <c r="BN61" t="n">
-        <v>17.07855815682511</v>
+        <v>17.07761404930801</v>
       </c>
       <c r="BO61" t="n">
-        <v>27.95187834168591</v>
+        <v>27.95159234557707</v>
       </c>
       <c r="BP61" t="inlineStr">
         <is>
@@ -15614,10 +15614,10 @@
         </is>
       </c>
       <c r="BZ61" t="n">
-        <v>37.22999954223633</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="CA61" t="n">
-        <v>-8.568355267074413</v>
+        <v>-8.346791936095499</v>
       </c>
       <c r="CB61" t="n">
         <v>-30.1313627614148</v>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="CF61" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
         </is>
       </c>
     </row>
@@ -15795,10 +15795,10 @@
         <v>14.67000007629395</v>
       </c>
       <c r="BC62" t="n">
-        <v>9.603373387456351</v>
+        <v>9.603183653427763</v>
       </c>
       <c r="BD62" t="n">
-        <v>17.81425763373153</v>
+        <v>17.8139056771085</v>
       </c>
       <c r="BE62" t="n">
         <v>13.92388975722742</v>
@@ -15810,7 +15810,7 @@
         <v>31.52578812957152</v>
       </c>
       <c r="BH62" t="n">
-        <v>17.34212017461504</v>
+        <v>17.34201183648471</v>
       </c>
       <c r="BI62" t="n">
         <v>13.92388975722742</v>
@@ -15831,7 +15831,7 @@
         <v>-14.57736389684815</v>
       </c>
       <c r="BO62" t="n">
-        <v>18.21486083452118</v>
+        <v>18.21412233329578</v>
       </c>
       <c r="BP62" t="inlineStr">
         <is>
@@ -16045,10 +16045,10 @@
         <v>12.02000045776367</v>
       </c>
       <c r="BC63" t="n">
-        <v>2.065662775782936</v>
+        <v>2.065318666548591</v>
       </c>
       <c r="BD63" t="n">
-        <v>3.831804449077346</v>
+        <v>3.831166126447637</v>
       </c>
       <c r="BE63" t="n">
         <v>25.40111739479564</v>
@@ -16057,7 +16057,7 @@
         <v>21.80965139478351</v>
       </c>
       <c r="BG63" t="n">
-        <v>32.93730972477155</v>
+        <v>32.93737962888861</v>
       </c>
       <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr"/>
@@ -16285,10 +16285,10 @@
         <v>14.77000045776367</v>
       </c>
       <c r="BC64" t="n">
-        <v>3.587795689824245</v>
+        <v>3.588011762197898</v>
       </c>
       <c r="BD64" t="n">
-        <v>6.655361004623973</v>
+        <v>6.655761818877101</v>
       </c>
       <c r="BE64" t="n">
         <v>33.33943885270335</v>
@@ -16297,7 +16297,7 @@
         <v>35.32769610508908</v>
       </c>
       <c r="BG64" t="n">
-        <v>31.41460505996929</v>
+        <v>31.4147770554192</v>
       </c>
       <c r="BH64" t="inlineStr"/>
       <c r="BI64" t="inlineStr"/>
@@ -16519,34 +16519,34 @@
         <v>0.3</v>
       </c>
       <c r="BA65" t="n">
-        <v>38.78</v>
+        <v>38.87</v>
       </c>
       <c r="BB65" t="n">
         <v>30.57999992370605</v>
       </c>
       <c r="BC65" t="n">
-        <v>14.05016486467948</v>
+        <v>14.05152757352989</v>
       </c>
       <c r="BD65" t="n">
-        <v>14.50370224052288</v>
+        <v>14.50397490819717</v>
       </c>
       <c r="BE65" t="n">
-        <v>15.08223511028423</v>
+        <v>15.08105596054267</v>
       </c>
       <c r="BF65" t="n">
         <v>30.63109436188252</v>
       </c>
       <c r="BG65" t="n">
-        <v>13.94588675370759</v>
+        <v>13.94524553766648</v>
       </c>
       <c r="BH65" t="n">
-        <v>17.64261666621534</v>
+        <v>17.64257966836374</v>
       </c>
       <c r="BI65" t="n">
-        <v>14.50370224052288</v>
+        <v>14.50397490819717</v>
       </c>
       <c r="BJ65" t="n">
-        <v>13.05333201647059</v>
+        <v>13.05357741737745</v>
       </c>
       <c r="BK65" t="n">
         <v>5</v>
@@ -16558,10 +16558,10 @@
         <v>2.2</v>
       </c>
       <c r="BN65" t="n">
-        <v>-57.31415288084594</v>
+        <v>-57.31335039259391</v>
       </c>
       <c r="BO65" t="n">
-        <v>-42.30668178472254</v>
+        <v>-42.30680277181111</v>
       </c>
       <c r="BP65" t="inlineStr">
         <is>
@@ -16775,10 +16775,10 @@
         <v>14.48999977111816</v>
       </c>
       <c r="BC66" t="n">
-        <v>2.3376867816433</v>
+        <v>2.337709886727121</v>
       </c>
       <c r="BD66" t="n">
-        <v>4.336408979948322</v>
+        <v>4.336451839878809</v>
       </c>
       <c r="BE66" t="n">
         <v>25.42946979699545</v>
@@ -16787,7 +16787,7 @@
         <v>19.47350783979101</v>
       </c>
       <c r="BG66" t="n">
-        <v>33.12286245162632</v>
+        <v>33.12290529549036</v>
       </c>
       <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr"/>
@@ -16978,7 +16978,7 @@
         <v>1</v>
       </c>
       <c r="AP67" t="n">
-        <v>14564848640</v>
+        <v>14560741376</v>
       </c>
       <c r="AQ67" t="n">
         <v>18.33</v>
@@ -17015,10 +17015,10 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BC67" t="n">
-        <v>6.50100164074772</v>
+        <v>6.500814309339336</v>
       </c>
       <c r="BD67" t="n">
-        <v>12.05935804358702</v>
+        <v>12.05901054382447</v>
       </c>
       <c r="BE67" t="n">
         <v>7.958674469868212</v>
@@ -17030,13 +17030,13 @@
         <v>18.01964030913558</v>
       </c>
       <c r="BH67" t="n">
-        <v>11.70620423882222</v>
+        <v>11.70609727258804</v>
       </c>
       <c r="BI67" t="n">
-        <v>12.05935804358702</v>
+        <v>12.05901054382447</v>
       </c>
       <c r="BJ67" t="n">
-        <v>10.85342223922832</v>
+        <v>10.85310948944202</v>
       </c>
       <c r="BK67" t="n">
         <v>5</v>
@@ -17048,10 +17048,10 @@
         <v>2.8</v>
       </c>
       <c r="BN67" t="n">
-        <v>-1.422143382365948</v>
+        <v>-1.424983979820904</v>
       </c>
       <c r="BO67" t="n">
-        <v>6.323378705425275</v>
+        <v>6.322407168350197</v>
       </c>
       <c r="BP67" t="inlineStr">
         <is>
@@ -17265,28 +17265,28 @@
         <v>18.95000076293945</v>
       </c>
       <c r="BC68" t="n">
-        <v>8.192805130248425</v>
+        <v>8.19280512203467</v>
       </c>
       <c r="BD68" t="n">
-        <v>9.244987540860647</v>
+        <v>9.244987541182551</v>
       </c>
       <c r="BE68" t="n">
-        <v>10.37640922769413</v>
+        <v>10.37640923845837</v>
       </c>
       <c r="BF68" t="n">
         <v>16.95234968520165</v>
       </c>
       <c r="BG68" t="n">
-        <v>9.616899129095341</v>
+        <v>9.61689913623238</v>
       </c>
       <c r="BH68" t="n">
-        <v>10.87669014262004</v>
+        <v>10.87669014462192</v>
       </c>
       <c r="BI68" t="n">
-        <v>9.616899129095341</v>
+        <v>9.61689913623238</v>
       </c>
       <c r="BJ68" t="n">
-        <v>8.655209216185806</v>
+        <v>8.655209222609143</v>
       </c>
       <c r="BK68" t="n">
         <v>5</v>
@@ -17298,10 +17298,10 @@
         <v>2.1</v>
       </c>
       <c r="BN68" t="n">
-        <v>-54.32607457666803</v>
+        <v>-54.32607454277179</v>
       </c>
       <c r="BO68" t="n">
-        <v>-42.6032205555812</v>
+        <v>-42.60322054501716</v>
       </c>
       <c r="BP68" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="CF68" t="inlineStr">
         <is>
-          <t>Rompimento (vol x6.2, +8.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x6.3, +8.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -17523,10 +17523,10 @@
         <v>41.70000076293945</v>
       </c>
       <c r="BC69" t="n">
-        <v>9.123429543655545</v>
+        <v>9.123432723708207</v>
       </c>
       <c r="BD69" t="n">
-        <v>16.92396180348103</v>
+        <v>16.92396770247873</v>
       </c>
       <c r="BE69" t="n">
         <v>119.078665971756</v>
@@ -17535,7 +17535,7 @@
         <v>87.55319300258704</v>
       </c>
       <c r="BG69" t="n">
-        <v>162.3336260894977</v>
+        <v>162.3336356844842</v>
       </c>
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr"/>
@@ -17582,10 +17582,10 @@
         </is>
       </c>
       <c r="BZ69" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="CA69" t="n">
-        <v>-3.248254665304118</v>
+        <v>-3.739609749070061</v>
       </c>
       <c r="CB69" t="n">
         <v>-30.08510558619815</v>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="CF69" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -17763,10 +17763,10 @@
         <v>29.72999954223633</v>
       </c>
       <c r="BC70" t="n">
-        <v>12.89493640222505</v>
+        <v>12.89530572849013</v>
       </c>
       <c r="BD70" t="n">
-        <v>23.92010702612746</v>
+        <v>23.92079212634919</v>
       </c>
       <c r="BE70" t="n">
         <v>37.02279078333001</v>
@@ -17775,10 +17775,10 @@
         <v>25.83665772834909</v>
       </c>
       <c r="BG70" t="n">
-        <v>43.04383446319062</v>
+        <v>43.04295694009713</v>
       </c>
       <c r="BH70" t="n">
-        <v>28.54366528064445</v>
+        <v>28.54370066132311</v>
       </c>
       <c r="BI70" t="n">
         <v>25.83665772834909</v>
@@ -17799,7 +17799,7 @@
         <v>-21.78610052623948</v>
       </c>
       <c r="BO70" t="n">
-        <v>-3.99036084715203</v>
+        <v>-3.990241840494768</v>
       </c>
       <c r="BP70" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         </is>
       </c>
       <c r="BZ70" t="n">
-        <v>30.39999961853027</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="CA70" t="n">
-        <v>-2.20394764704388</v>
+        <v>-2.010549134092643</v>
       </c>
       <c r="CB70" t="n">
         <v>-23.41079410625997</v>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="CF70" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -18013,28 +18013,28 @@
         <v>3.470000028610229</v>
       </c>
       <c r="BC71" t="n">
-        <v>2.663573178856252</v>
+        <v>2.663573179221207</v>
       </c>
       <c r="BD71" t="n">
-        <v>3.085953419586554</v>
+        <v>3.08595341970474</v>
       </c>
       <c r="BE71" t="n">
-        <v>3.75374477646637</v>
+        <v>3.753744776095803</v>
       </c>
       <c r="BF71" t="n">
         <v>6.965119785642171</v>
       </c>
       <c r="BG71" t="n">
-        <v>5.64998743979841</v>
+        <v>5.649987439975291</v>
       </c>
       <c r="BH71" t="n">
-        <v>4.423675720069951</v>
+        <v>4.423675720127843</v>
       </c>
       <c r="BI71" t="n">
-        <v>3.75374477646637</v>
+        <v>3.753744776095803</v>
       </c>
       <c r="BJ71" t="n">
-        <v>3.378370298819733</v>
+        <v>3.378370298486223</v>
       </c>
       <c r="BK71" t="n">
         <v>5</v>
@@ -18046,10 +18046,10 @@
         <v>2.6</v>
       </c>
       <c r="BN71" t="n">
-        <v>-2.640626196974283</v>
+        <v>-2.640626206585506</v>
       </c>
       <c r="BO71" t="n">
-        <v>27.48344909500415</v>
+        <v>27.48344909667249</v>
       </c>
       <c r="BP71" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>6.24</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.77</v>
+        <v>7.91</v>
       </c>
       <c r="AU3" t="n">
         <v>27.12</v>
@@ -18939,10 +18939,10 @@
         <v>10.78999996185303</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.991220388920124</v>
+        <v>6.095304552635779</v>
       </c>
       <c r="BD3" t="n">
-        <v>11.11371382144683</v>
+        <v>11.30678994513937</v>
       </c>
       <c r="BE3" t="n">
         <v>37.13441545313054</v>
@@ -18951,19 +18951,19 @@
         <v>25.57794609703624</v>
       </c>
       <c r="BG3" t="n">
-        <v>63.82521685004601</v>
+        <v>64.20370471810294</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL3" t="b">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
@@ -18994,7 +18994,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ3" t="n">
@@ -19004,7 +19004,7 @@
         <v>-4.846816893197337</v>
       </c>
       <c r="CB3" t="n">
-        <v>-23.76550462277683</v>
+        <v>-23.76550987166468</v>
       </c>
       <c r="CC3" t="b">
         <v>1</v>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -19179,10 +19179,10 @@
         <v>14.03999996185303</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.50260757461884</v>
+        <v>15.50260772965087</v>
       </c>
       <c r="BD4" t="n">
-        <v>28.75733705091795</v>
+        <v>28.75733733850236</v>
       </c>
       <c r="BE4" t="n">
         <v>38.75624989469846</v>
@@ -19191,16 +19191,16 @@
         <v>23.45217391409519</v>
       </c>
       <c r="BG4" t="n">
-        <v>71.67343946141401</v>
+        <v>71.67343915263154</v>
       </c>
       <c r="BH4" t="n">
-        <v>35.62836157914889</v>
+        <v>35.62836160591569</v>
       </c>
       <c r="BI4" t="n">
-        <v>28.75733705091795</v>
+        <v>28.75733733850236</v>
       </c>
       <c r="BJ4" t="n">
-        <v>25.88160334582616</v>
+        <v>25.88160360465212</v>
       </c>
       <c r="BK4" t="n">
         <v>5</v>
@@ -19212,10 +19212,10 @@
         <v>4.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>84.3419046734118</v>
+        <v>84.34190651690156</v>
       </c>
       <c r="BO4" t="n">
-        <v>153.7632598002271</v>
+        <v>153.7632599908738</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -19232,16 +19232,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>A Vulcabras (VULC3) apresenta uma notável combinação de alta qualidade operacional e valuation descontado no setor de consumo discricionário, evidenciada por um ROE de 35,1% e um ROIC de 17,8% que se posicionam confortavelmente acima das médias setoriais de 12,2% e 12,5%, respectivamente. Essa rentabilidade robusta convive com múltiplos de preço bastante atrativos, visto que o P/L de 4,8 e o P/VP de 1,68 sugerem que o mercado ainda não precificou totalmente a eficiência da companhia, configurando uma relação favorável entre qualidade e preço. No âmbito financeiro, a excelente rentabilidade é suportada por um endividamento sob controle, com uma relação Dívida/Patrimônio de apenas 0,37 e uma sólida liquidez corrente de 2,96, o que garante robustez ao balanço. Essa estrutura de capital saudável confere sustentabilidade ao expressivo Dividend Yield de 28,86%, uma vez que a geração de lucro e a folga financeira permitem a distribuição de proventos sem comprometer a solvência da empresa. Por outro lado, o crescimento histórico acende um sinal de alerta, dado que o CAGR de receita de cinco anos contraiu 64,7%, situando-se drasticamente abaixo da média de expansão do setor, que foi de 49,8%. Esse descompasso de crescimento reflete-se no checklist de critérios fundamentalistas, no qual a Vulcabras atende a 5 dos 7 requisitos avaliados, penalizada justamente pela taxa de crescimento inferior à dos pares e por movimentações de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 15,50 por Bazin até os otimistas R$ 71,67 por Lynch, mas convergindo para uma média de R$ 35,63 e uma mediana de R$ 28,76. Tomando como referência o preço-teto ajustado com margem de segurança de R$ 25,88, o papel oferece um expressivo potencial de valorização de 84,3% frente à cotação atual de R$ 14,04, em um momento técnico de tendência lateral com pivô de alta. Em suma, os prós da tese concentram-se na rentabilidade excepcional, no endividamento muito baixo, no valuation atraente e no retorno de dividendos fora da curva, enquanto os contras residem na severa retração histórica de receita a longo prazo e nas transações de insiders identificadas no checklist.</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="b">
         <v>0</v>
       </c>
@@ -19252,7 +19244,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="BZ4" t="n">
@@ -19268,14 +19260,14 @@
         <v>1</v>
       </c>
       <c r="CD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -19437,10 +19429,10 @@
         <v>4.210000038146973</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.562927795375999</v>
+        <v>3.563012712319659</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.609231060422478</v>
+        <v>6.609388581352968</v>
       </c>
       <c r="BE5" t="n">
         <v>12.73573070900625</v>
@@ -19449,16 +19441,16 @@
         <v>8.568907623857728</v>
       </c>
       <c r="BG5" t="n">
-        <v>24.4828797252006</v>
+        <v>24.48281447052321</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.869199297165614</v>
+        <v>7.869259906634151</v>
       </c>
       <c r="BI5" t="n">
-        <v>7.589069342140103</v>
+        <v>7.589148102605348</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6.830162407926093</v>
+        <v>6.830233292344813</v>
       </c>
       <c r="BK5" t="n">
         <v>4</v>
@@ -19470,10 +19462,10 @@
         <v>6.9</v>
       </c>
       <c r="BN5" t="n">
-        <v>62.23663529780828</v>
+        <v>62.23831901320204</v>
       </c>
       <c r="BO5" t="n">
-        <v>86.91684622001176</v>
+        <v>86.91828587483334</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
@@ -19861,10 +19853,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.057497389947812</v>
+        <v>3.057569932790789</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.671657658353192</v>
+        <v>5.671792225326912</v>
       </c>
       <c r="BE7" t="n">
         <v>12.71549888477204</v>
@@ -19873,10 +19865,10 @@
         <v>8.566302726978416</v>
       </c>
       <c r="BG7" t="n">
-        <v>23.48300704313526</v>
+        <v>23.48322266942012</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.984486423367882</v>
+        <v>8.98453127902579</v>
       </c>
       <c r="BI7" t="n">
         <v>8.566302726978416</v>
@@ -19897,7 +19889,7 @@
         <v>70.56797537198747</v>
       </c>
       <c r="BO7" t="n">
-        <v>98.771824364615</v>
+        <v>98.77281674643132</v>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
@@ -20111,10 +20103,10 @@
         <v>24.89999961853027</v>
       </c>
       <c r="BC8" t="n">
-        <v>16.36919309137854</v>
+        <v>16.36919305358049</v>
       </c>
       <c r="BD8" t="n">
-        <v>30.36485318450719</v>
+        <v>30.36485311439181</v>
       </c>
       <c r="BE8" t="n">
         <v>64.43847557529806</v>
@@ -20123,10 +20115,10 @@
         <v>47.06554188781961</v>
       </c>
       <c r="BG8" t="n">
-        <v>106.2977601940779</v>
+        <v>106.2977602173549</v>
       </c>
       <c r="BH8" t="n">
-        <v>62.04165771042569</v>
+        <v>62.04165769871609</v>
       </c>
       <c r="BI8" t="n">
         <v>55.75200873155883</v>
@@ -20147,7 +20139,7 @@
         <v>101.5132876590969</v>
       </c>
       <c r="BO8" t="n">
-        <v>149.163287794812</v>
+        <v>149.1632877477855</v>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
@@ -20355,10 +20347,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.20546150394244</v>
+        <v>19.20366125867804</v>
       </c>
       <c r="BD9" t="n">
-        <v>35.62613108981321</v>
+        <v>35.62279163484776</v>
       </c>
       <c r="BE9" t="n">
         <v>75.48756788005936</v>
@@ -20367,16 +20359,16 @@
         <v>56.56486624961452</v>
       </c>
       <c r="BG9" t="n">
-        <v>99.09361281859876</v>
+        <v>99.09652143724021</v>
       </c>
       <c r="BH9" t="n">
-        <v>43.43972015793833</v>
+        <v>43.43800692452839</v>
       </c>
       <c r="BI9" t="n">
-        <v>35.62613108981321</v>
+        <v>35.62279163484776</v>
       </c>
       <c r="BJ9" t="n">
-        <v>32.0635179808319</v>
+        <v>32.06051247136298</v>
       </c>
       <c r="BK9" t="n">
         <v>3</v>
@@ -20388,10 +20380,10 @@
         <v>3.9</v>
       </c>
       <c r="BN9" t="n">
-        <v>-36.40714171905611</v>
+        <v>-36.41310266625576</v>
       </c>
       <c r="BO9" t="n">
-        <v>-13.84426470548005</v>
+        <v>-13.84766262985958</v>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
@@ -20605,10 +20597,10 @@
         <v>15.60000038146973</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.388296788541452</v>
+        <v>6.38829676523164</v>
       </c>
       <c r="BD10" t="n">
-        <v>11.85029054274439</v>
+        <v>11.85029049950469</v>
       </c>
       <c r="BE10" t="n">
         <v>25.39312101406313</v>
@@ -20617,10 +20609,10 @@
         <v>18.62099144680682</v>
       </c>
       <c r="BG10" t="n">
-        <v>35.32345346571161</v>
+        <v>35.32345350332195</v>
       </c>
       <c r="BH10" t="n">
-        <v>22.79696411733149</v>
+        <v>22.79696411592415</v>
       </c>
       <c r="BI10" t="n">
         <v>22.00705623043497</v>
@@ -20641,7 +20633,7 @@
         <v>26.96378284014795</v>
       </c>
       <c r="BO10" t="n">
-        <v>46.13438179405809</v>
+        <v>46.13438178503668</v>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
@@ -20855,10 +20847,10 @@
         <v>31.36000061035156</v>
       </c>
       <c r="BC11" t="n">
-        <v>22.00307399921919</v>
+        <v>22.00390976620893</v>
       </c>
       <c r="BD11" t="n">
-        <v>40.8157022685516</v>
+        <v>40.81725261631757</v>
       </c>
       <c r="BE11" t="n">
         <v>45.81256980012768</v>
@@ -20867,16 +20859,16 @@
         <v>19.75712144035349</v>
       </c>
       <c r="BG11" t="n">
-        <v>59.9654157784598</v>
+        <v>59.95863816798309</v>
       </c>
       <c r="BH11" t="n">
-        <v>37.67077665734235</v>
+        <v>37.66989835819815</v>
       </c>
       <c r="BI11" t="n">
-        <v>40.8157022685516</v>
+        <v>40.81725261631757</v>
       </c>
       <c r="BJ11" t="n">
-        <v>36.73413204169644</v>
+        <v>36.73552735468581</v>
       </c>
       <c r="BK11" t="n">
         <v>5</v>
@@ -20888,10 +20880,10 @@
         <v>3</v>
       </c>
       <c r="BN11" t="n">
-        <v>17.13689836335954</v>
+        <v>17.14134770316253</v>
       </c>
       <c r="BO11" t="n">
-        <v>20.12364771736541</v>
+        <v>20.12084701861827</v>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
@@ -21105,10 +21097,10 @@
         <v>32.11000061035156</v>
       </c>
       <c r="BC12" t="n">
-        <v>44.83658198839334</v>
+        <v>44.8371712772876</v>
       </c>
       <c r="BD12" t="n">
-        <v>83.17185958846964</v>
+        <v>83.1729527193685</v>
       </c>
       <c r="BE12" t="n">
         <v>64.95534474613102</v>
@@ -21120,7 +21112,7 @@
         <v>147.0687050855797</v>
       </c>
       <c r="BH12" t="n">
-        <v>73.91364695878947</v>
+        <v>73.9139834427481</v>
       </c>
       <c r="BI12" t="n">
         <v>64.95534474613102</v>
@@ -21141,7 +21133,7 @@
         <v>82.06106870229006</v>
       </c>
       <c r="BO12" t="n">
-        <v>130.1888681215451</v>
+        <v>130.1899160317047</v>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
@@ -21328,7 +21320,7 @@
         <v>11.54</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.15</v>
+        <v>10.16</v>
       </c>
       <c r="AU13" t="n">
         <v>13.99</v>
@@ -21349,10 +21341,10 @@
         <v>13.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.973464542971879</v>
+        <v>9.973917616330635</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.50077672721283</v>
+        <v>18.50161717829333</v>
       </c>
       <c r="BE13" t="n">
         <v>51.32042253521126</v>
@@ -21361,16 +21353,16 @@
         <v>48.95474340049645</v>
       </c>
       <c r="BG13" t="n">
-        <v>73.98456490996804</v>
+        <v>73.98546428866297</v>
       </c>
       <c r="BH13" t="n">
-        <v>14.23712063509236</v>
+        <v>14.23776739731198</v>
       </c>
       <c r="BI13" t="n">
-        <v>14.23712063509236</v>
+        <v>14.23776739731198</v>
       </c>
       <c r="BJ13" t="n">
-        <v>12.81340857158312</v>
+        <v>12.81399065758078</v>
       </c>
       <c r="BK13" t="n">
         <v>2</v>
@@ -21382,10 +21374,10 @@
         <v>5.1</v>
       </c>
       <c r="BN13" t="n">
-        <v>-6.811574024850032</v>
+        <v>-6.807340672139761</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.542695527944417</v>
+        <v>3.547399253178041</v>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
@@ -21599,10 +21591,10 @@
         <v>7.760000228881836</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.255436204498124</v>
+        <v>7.25568765613328</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.45883415934402</v>
+        <v>13.45930060212723</v>
       </c>
       <c r="BE14" t="n">
         <v>40.48031615460012</v>
@@ -21611,7 +21603,7 @@
         <v>27.21885716623862</v>
       </c>
       <c r="BG14" t="n">
-        <v>85.81736625834695</v>
+        <v>85.81875221224152</v>
       </c>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
@@ -21658,10 +21650,10 @@
         </is>
       </c>
       <c r="BZ14" t="n">
-        <v>8.420000076293945</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="CA14" t="n">
-        <v>-7.83847792674377</v>
+        <v>-5.596107338245182</v>
       </c>
       <c r="CB14" t="n">
         <v>-28.37008112858783</v>
@@ -21677,7 +21669,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -21833,10 +21825,10 @@
         <v>19.31999969482422</v>
       </c>
       <c r="BC15" t="n">
-        <v>13.28432179013185</v>
+        <v>13.28320923196645</v>
       </c>
       <c r="BD15" t="n">
-        <v>24.64241692069458</v>
+        <v>24.64035312529776</v>
       </c>
       <c r="BE15" t="n">
         <v>19.39318151185007</v>
@@ -21845,10 +21837,10 @@
         <v>12.29335323539705</v>
       </c>
       <c r="BG15" t="n">
-        <v>27.99397743656636</v>
+        <v>27.99279745063336</v>
       </c>
       <c r="BH15" t="n">
-        <v>19.1066400742255</v>
+        <v>19.10558128970476</v>
       </c>
       <c r="BI15" t="n">
         <v>19.39318151185007</v>
@@ -21869,7 +21861,7 @@
         <v>-9.659090909090917</v>
       </c>
       <c r="BO15" t="n">
-        <v>-1.104345879756308</v>
+        <v>-1.109826130985425</v>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
@@ -22083,10 +22075,10 @@
         <v>7.019999980926514</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.169581645457426</v>
+        <v>3.169581649888222</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.879573952323525</v>
+        <v>5.879573960542651</v>
       </c>
       <c r="BE16" t="n">
         <v>21.83450698292871</v>
@@ -22095,7 +22087,7 @@
         <v>13.93706005001388</v>
       </c>
       <c r="BG16" t="n">
-        <v>35.13477529349805</v>
+        <v>35.13477530805935</v>
       </c>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr"/>
@@ -22142,10 +22134,10 @@
         </is>
       </c>
       <c r="BZ16" t="n">
-        <v>7.929999828338623</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="CA16" t="n">
-        <v>-11.47540816028945</v>
+        <v>-8.831166820555026</v>
       </c>
       <c r="CB16" t="n">
         <v>-59.61021964227024</v>
@@ -22161,7 +22153,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.8%))</t>
         </is>
       </c>
     </row>
@@ -22323,22 +22315,22 @@
         <v>33.47999954223633</v>
       </c>
       <c r="BC17" t="n">
-        <v>24.07987549388067</v>
+        <v>24.08086488925293</v>
       </c>
       <c r="BD17" t="n">
-        <v>32.1070312060865</v>
+        <v>32.10533852574593</v>
       </c>
       <c r="BE17" t="n">
-        <v>36.65085143552953</v>
+        <v>36.64741343419143</v>
       </c>
       <c r="BF17" t="n">
         <v>36.13604254760104</v>
       </c>
       <c r="BG17" t="n">
-        <v>50.93895722258051</v>
+        <v>50.93701028581805</v>
       </c>
       <c r="BH17" t="n">
-        <v>35.98255158113565</v>
+        <v>35.98133393652187</v>
       </c>
       <c r="BI17" t="n">
         <v>36.13604254760104</v>
@@ -22359,7 +22351,7 @@
         <v>-2.860099350322265</v>
       </c>
       <c r="BO17" t="n">
-        <v>7.474767243476976</v>
+        <v>7.471130312083818</v>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
@@ -22388,7 +22380,7 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ17" t="n">
@@ -22411,7 +22403,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (+0.6%))</t>
+          <t>sem sinal (Lateral; sem novo topo (+0.6%))</t>
         </is>
       </c>
     </row>
@@ -22575,10 +22567,10 @@
         <v>40.86999893188477</v>
       </c>
       <c r="BC18" t="n">
-        <v>114.1776439158827</v>
+        <v>114.1767440032</v>
       </c>
       <c r="BD18" t="n">
-        <v>211.7995294639624</v>
+        <v>211.797860125936</v>
       </c>
       <c r="BE18" t="n">
         <v>137.0955660373349</v>
@@ -22634,10 +22626,10 @@
         </is>
       </c>
       <c r="BZ18" t="n">
-        <v>43.04999923706055</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="CA18" t="n">
-        <v>-5.063880008850452</v>
+        <v>-5.87286813587281</v>
       </c>
       <c r="CB18" t="n">
         <v>-16.85980497860918</v>
@@ -22653,7 +22645,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -22815,10 +22807,10 @@
         <v>9.439999580383301</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.432360694008512</v>
+        <v>9.434030265257377</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.49702908738579</v>
+        <v>17.50012614205243</v>
       </c>
       <c r="BE19" t="n">
         <v>24.47749401958487</v>
@@ -22827,10 +22819,10 @@
         <v>17.5772497487596</v>
       </c>
       <c r="BG19" t="n">
-        <v>38.96008989028776</v>
+        <v>38.95884393271933</v>
       </c>
       <c r="BH19" t="n">
-        <v>21.58884468800531</v>
+        <v>21.58954882167473</v>
       </c>
       <c r="BI19" t="n">
         <v>17.5772497487596</v>
@@ -22851,7 +22843,7 @@
         <v>67.57971903682341</v>
       </c>
       <c r="BO19" t="n">
-        <v>128.6953988098452</v>
+        <v>128.702857853285</v>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
@@ -23065,10 +23057,10 @@
         <v>14.72000026702881</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.523498109876001</v>
+        <v>4.523236434623613</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.391088993819979</v>
+        <v>8.390603586226803</v>
       </c>
       <c r="BE20" t="n">
         <v>24.13861429927372</v>
@@ -23077,10 +23069,10 @@
         <v>20.32904459945394</v>
       </c>
       <c r="BG20" t="n">
-        <v>29.31380328899641</v>
+        <v>29.31401187733537</v>
       </c>
       <c r="BH20" t="n">
-        <v>20.54313779538601</v>
+        <v>20.54306859057246</v>
       </c>
       <c r="BI20" t="n">
         <v>22.23382944936383</v>
@@ -23101,7 +23093,7 @@
         <v>35.94053085208606</v>
       </c>
       <c r="BO20" t="n">
-        <v>39.55935749132014</v>
+        <v>39.55888734993225</v>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
@@ -23130,7 +23122,7 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ20" t="n">
@@ -23153,7 +23145,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.7%))</t>
         </is>
       </c>
     </row>
@@ -23315,10 +23307,10 @@
         <v>17.03000068664551</v>
       </c>
       <c r="BC21" t="n">
-        <v>10.09561411747972</v>
+        <v>10.09569791997182</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.72736418792487</v>
+        <v>18.72751964154773</v>
       </c>
       <c r="BE21" t="n">
         <v>37.48297493323139</v>
@@ -23327,10 +23319,10 @@
         <v>37.04197491142868</v>
       </c>
       <c r="BG21" t="n">
-        <v>42.13469686609152</v>
+        <v>42.13473712324961</v>
       </c>
       <c r="BH21" t="n">
-        <v>33.84675272466912</v>
+        <v>33.84680165236436</v>
       </c>
       <c r="BI21" t="n">
         <v>37.26247492233004</v>
@@ -23351,7 +23343,7 @@
         <v>96.9244044505253</v>
       </c>
       <c r="BO21" t="n">
-        <v>98.74780598929087</v>
+        <v>98.74809329224605</v>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
@@ -23567,10 +23559,10 @@
         <v>45.68999862670898</v>
       </c>
       <c r="BC22" t="n">
-        <v>121.4155479667476</v>
+        <v>121.4142902743408</v>
       </c>
       <c r="BD22" t="n">
-        <v>225.2258414783169</v>
+        <v>225.2235084589022</v>
       </c>
       <c r="BE22" t="n">
         <v>136.9666248425099</v>
@@ -23582,7 +23574,7 @@
         <v>310.1131128509659</v>
       </c>
       <c r="BH22" t="n">
-        <v>177.4102292193072</v>
+        <v>177.4095110769429</v>
       </c>
       <c r="BI22" t="n">
         <v>136.9666248425099</v>
@@ -23603,7 +23595,7 @@
         <v>169.7963800904977</v>
       </c>
       <c r="BO22" t="n">
-        <v>288.2911677646639</v>
+        <v>288.2895959931913</v>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
@@ -23636,10 +23628,10 @@
         </is>
       </c>
       <c r="BZ22" t="n">
-        <v>48.70000076293945</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="CA22" t="n">
-        <v>-6.180702441633368</v>
+        <v>-6.831162777889876</v>
       </c>
       <c r="CB22" t="n">
         <v>-16.33828883951265</v>
@@ -23655,7 +23647,7 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
         </is>
       </c>
     </row>
@@ -23817,28 +23809,28 @@
         <v>26.27000045776367</v>
       </c>
       <c r="BC23" t="n">
-        <v>16.70734195419739</v>
+        <v>16.70768559348043</v>
       </c>
       <c r="BD23" t="n">
-        <v>28.26185713482154</v>
+        <v>28.26190220158057</v>
       </c>
       <c r="BE23" t="n">
-        <v>48.38620269869156</v>
+        <v>48.38528465973992</v>
       </c>
       <c r="BF23" t="n">
         <v>53.40235057980205</v>
       </c>
       <c r="BG23" t="n">
-        <v>56.82499432074687</v>
+        <v>56.8251162255253</v>
       </c>
       <c r="BH23" t="n">
-        <v>46.7188511835155</v>
+        <v>46.71866341666196</v>
       </c>
       <c r="BI23" t="n">
-        <v>50.8942766392468</v>
+        <v>50.89381761977099</v>
       </c>
       <c r="BJ23" t="n">
-        <v>45.80484897532212</v>
+        <v>45.80443585779389</v>
       </c>
       <c r="BK23" t="n">
         <v>4</v>
@@ -23850,10 +23842,10 @@
         <v>3.4</v>
       </c>
       <c r="BN23" t="n">
-        <v>74.36181262716821</v>
+        <v>74.36024004429407</v>
       </c>
       <c r="BO23" t="n">
-        <v>77.84107487409086</v>
+        <v>77.84036011638142</v>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
@@ -24067,10 +24059,10 @@
         <v>12.39000034332275</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.853327558146693</v>
+        <v>3.85351393913391</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.147922620362116</v>
+        <v>7.148268357093401</v>
       </c>
       <c r="BE24" t="n">
         <v>19.66077898790736</v>
@@ -24079,10 +24071,10 @@
         <v>18.56644334558858</v>
       </c>
       <c r="BG24" t="n">
-        <v>20.06899048854631</v>
+        <v>20.06892697861108</v>
       </c>
       <c r="BH24" t="n">
-        <v>19.43207094068075</v>
+        <v>19.43204977070235</v>
       </c>
       <c r="BI24" t="n">
         <v>19.66077898790736</v>
@@ -24103,7 +24095,7 @@
         <v>42.81437125748499</v>
       </c>
       <c r="BO24" t="n">
-        <v>56.83672641020645</v>
+        <v>56.83655554678582</v>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
@@ -24317,10 +24309,10 @@
         <v>21.6299991607666</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.04249252145397</v>
+        <v>3.042492522367858</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.643823627297114</v>
+        <v>5.643823628992376</v>
       </c>
       <c r="BE25" t="n">
         <v>32.8666845046052</v>
@@ -24329,7 +24321,7 @@
         <v>27.46815743134023</v>
       </c>
       <c r="BG25" t="n">
-        <v>42.09230306328607</v>
+        <v>42.09230306475333</v>
       </c>
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr"/>
@@ -24376,10 +24368,10 @@
         </is>
       </c>
       <c r="BZ25" t="n">
-        <v>23.35000038146973</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="CA25" t="n">
-        <v>-7.366172131063841</v>
+        <v>-5.29772759955166</v>
       </c>
       <c r="CB25" t="n">
         <v>-39.73503176095192</v>
@@ -24395,7 +24387,7 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -24551,28 +24543,28 @@
         <v>23.53000068664551</v>
       </c>
       <c r="BC26" t="n">
-        <v>16.88052200439253</v>
+        <v>16.88052201842914</v>
       </c>
       <c r="BD26" t="n">
-        <v>29.59210750656573</v>
+        <v>29.59210750444302</v>
       </c>
       <c r="BE26" t="n">
-        <v>49.02408039903741</v>
+        <v>49.02408035475595</v>
       </c>
       <c r="BF26" t="n">
         <v>49.67482203402362</v>
       </c>
       <c r="BG26" t="n">
-        <v>61.12609935860196</v>
+        <v>61.12609936368955</v>
       </c>
       <c r="BH26" t="n">
-        <v>31.83223663666523</v>
+        <v>31.83223662587604</v>
       </c>
       <c r="BI26" t="n">
-        <v>29.59210750656573</v>
+        <v>29.59210750444302</v>
       </c>
       <c r="BJ26" t="n">
-        <v>26.63289675590916</v>
+        <v>26.63289675399872</v>
       </c>
       <c r="BK26" t="n">
         <v>3</v>
@@ -24584,10 +24576,10 @@
         <v>2.9</v>
       </c>
       <c r="BN26" t="n">
-        <v>13.18697823508652</v>
+        <v>13.18697822696737</v>
       </c>
       <c r="BO26" t="n">
-        <v>35.28361966743021</v>
+        <v>35.28361962157731</v>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
@@ -24799,10 +24791,10 @@
         <v>3.559999942779541</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.971223935552619</v>
+        <v>4.97136938593848</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.238102050164614</v>
+        <v>7.238313825926427</v>
       </c>
       <c r="BE27" t="n">
         <v>6.683032383557261</v>
@@ -24812,7 +24804,7 @@
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="n">
-        <v>6.516692818220029</v>
+        <v>6.516782124756947</v>
       </c>
       <c r="BI27" t="n">
         <v>6.928722643581441</v>
@@ -24833,7 +24825,7 @@
         <v>75.16433931048137</v>
       </c>
       <c r="BO27" t="n">
-        <v>83.0531719933678</v>
+        <v>83.05568060399573</v>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
@@ -25047,10 +25039,10 @@
         <v>27.79000091552734</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.35600930737357</v>
+        <v>7.356371103595649</v>
       </c>
       <c r="BD28" t="n">
-        <v>13.64539726517797</v>
+        <v>13.64606839716993</v>
       </c>
       <c r="BE28" t="n">
         <v>35.78401478432821</v>
@@ -25059,10 +25051,10 @@
         <v>28.28986696159874</v>
       </c>
       <c r="BG28" t="n">
-        <v>44.29379339956643</v>
+        <v>44.29324627113758</v>
       </c>
       <c r="BH28" t="n">
-        <v>30.50326810266784</v>
+        <v>30.50329910355861</v>
       </c>
       <c r="BI28" t="n">
         <v>32.03694087296348</v>
@@ -25083,7 +25075,7 @@
         <v>3.754033234151066</v>
       </c>
       <c r="BO28" t="n">
-        <v>9.763465627035984</v>
+        <v>9.763577181155281</v>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
@@ -25116,13 +25108,13 @@
         </is>
       </c>
       <c r="BZ28" t="n">
-        <v>29.21999931335449</v>
+        <v>29.06999969482422</v>
       </c>
       <c r="CA28" t="n">
-        <v>-4.89390291386349</v>
+        <v>-4.403160621720859</v>
       </c>
       <c r="CB28" t="n">
-        <v>-21.22606264717445</v>
+        <v>-21.22605409112423</v>
       </c>
       <c r="CC28" t="b">
         <v>1</v>
@@ -25135,7 +25127,7 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -25291,10 +25283,10 @@
         <v>15.14999961853027</v>
       </c>
       <c r="BC29" t="n">
-        <v>9.409156498452109</v>
+        <v>9.409156371490303</v>
       </c>
       <c r="BD29" t="n">
-        <v>17.45398530462866</v>
+        <v>17.45398506911451</v>
       </c>
       <c r="BE29" t="n">
         <v>30.97800847924785</v>
@@ -25303,16 +25295,16 @@
         <v>29.43218226899666</v>
       </c>
       <c r="BG29" t="n">
-        <v>34.7506469833056</v>
+        <v>34.75064696016124</v>
       </c>
       <c r="BH29" t="n">
-        <v>19.28038342744287</v>
+        <v>19.28038330661755</v>
       </c>
       <c r="BI29" t="n">
-        <v>17.45398530462866</v>
+        <v>17.45398506911451</v>
       </c>
       <c r="BJ29" t="n">
-        <v>15.7085867741658</v>
+        <v>15.70858656220306</v>
       </c>
       <c r="BK29" t="n">
         <v>3</v>
@@ -25324,10 +25316,10 @@
         <v>3.3</v>
       </c>
       <c r="BN29" t="n">
-        <v>3.687044024425612</v>
+        <v>3.687042625331594</v>
       </c>
       <c r="BO29" t="n">
-        <v>27.26326015124545</v>
+        <v>27.26325935371856</v>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
@@ -25366,7 +25358,7 @@
         <v>-8.195107168235239</v>
       </c>
       <c r="CB29" t="n">
-        <v>-16.71340819915189</v>
+        <v>-16.71342624530195</v>
       </c>
       <c r="CC29" t="b">
         <v>1</v>
@@ -25541,10 +25533,10 @@
         <v>21.67000007629395</v>
       </c>
       <c r="BC30" t="n">
-        <v>11.24293050073338</v>
+        <v>11.24293048606617</v>
       </c>
       <c r="BD30" t="n">
-        <v>20.85563607886042</v>
+        <v>20.85563605165274</v>
       </c>
       <c r="BE30" t="n">
         <v>57.77213300018003</v>
@@ -25553,10 +25545,10 @@
         <v>47.81129458798794</v>
       </c>
       <c r="BG30" t="n">
-        <v>83.49262998802884</v>
+        <v>83.49262998490619</v>
       </c>
       <c r="BH30" t="n">
-        <v>52.48292341376431</v>
+        <v>52.48292340618172</v>
       </c>
       <c r="BI30" t="n">
         <v>52.79171379408398</v>
@@ -25577,7 +25569,7 @@
         <v>119.2549249995263</v>
       </c>
       <c r="BO30" t="n">
-        <v>142.1916161928324</v>
+        <v>142.1916161578411</v>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
@@ -25783,10 +25775,10 @@
         <v>38.38000106811523</v>
       </c>
       <c r="BC31" t="n">
-        <v>35.20932546220636</v>
+        <v>35.20215235865994</v>
       </c>
       <c r="BD31" t="n">
-        <v>51.26477787297246</v>
+        <v>51.25433383420889</v>
       </c>
       <c r="BE31" t="n">
         <v>49.21726400843384</v>
@@ -25796,7 +25788,7 @@
       </c>
       <c r="BG31" t="inlineStr"/>
       <c r="BH31" t="n">
-        <v>45.23045578120422</v>
+        <v>45.22458340043422</v>
       </c>
       <c r="BI31" t="n">
         <v>49.21726400843384</v>
@@ -25817,7 +25809,7 @@
         <v>15.41307028360048</v>
       </c>
       <c r="BO31" t="n">
-        <v>17.84902168431701</v>
+        <v>17.83372105741088</v>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
@@ -26031,28 +26023,28 @@
         <v>11.57999992370605</v>
       </c>
       <c r="BC32" t="n">
-        <v>10.02516923195222</v>
+        <v>10.02516919997956</v>
       </c>
       <c r="BD32" t="n">
-        <v>16.49101883006962</v>
+        <v>16.49101899634692</v>
       </c>
       <c r="BE32" t="n">
-        <v>18.92375886756921</v>
+        <v>18.92375911872798</v>
       </c>
       <c r="BF32" t="n">
         <v>12.17705177601623</v>
       </c>
       <c r="BG32" t="n">
-        <v>27.66777750578778</v>
+        <v>27.66777761966962</v>
       </c>
       <c r="BH32" t="n">
-        <v>17.05695524227901</v>
+        <v>17.05695534214806</v>
       </c>
       <c r="BI32" t="n">
-        <v>16.49101883006962</v>
+        <v>16.49101899634692</v>
       </c>
       <c r="BJ32" t="n">
-        <v>14.84191694706266</v>
+        <v>14.84191709671223</v>
       </c>
       <c r="BK32" t="n">
         <v>5</v>
@@ -26064,10 +26056,10 @@
         <v>2.8</v>
       </c>
       <c r="BN32" t="n">
-        <v>28.16854097450339</v>
+        <v>28.16854226681407</v>
       </c>
       <c r="BO32" t="n">
-        <v>47.2966783649176</v>
+        <v>47.29667922734466</v>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
@@ -26100,10 +26092,10 @@
         </is>
       </c>
       <c r="BZ32" t="n">
-        <v>12.38000011444092</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="CA32" t="n">
-        <v>-6.46203702212963</v>
+        <v>-3.820598335584846</v>
       </c>
       <c r="CB32" t="n">
         <v>-32.90019903655219</v>
@@ -26119,7 +26111,7 @@
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.8%))</t>
         </is>
       </c>
     </row>
@@ -26279,10 +26271,10 @@
         <v>6.110000133514404</v>
       </c>
       <c r="BC33" t="n">
-        <v>7.214093399413781</v>
+        <v>7.214093422639239</v>
       </c>
       <c r="BD33" t="n">
-        <v>10.50371998954647</v>
+        <v>10.50372002336273</v>
       </c>
       <c r="BE33" t="n">
         <v>8.552355503169556</v>
@@ -26292,7 +26284,7 @@
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="n">
-        <v>8.822148337417094</v>
+        <v>8.822148351677525</v>
       </c>
       <c r="BI33" t="n">
         <v>8.785389980354065</v>
@@ -26313,7 +26305,7 @@
         <v>29.4083602216016</v>
       </c>
       <c r="BO33" t="n">
-        <v>44.38867667164341</v>
+        <v>44.38867690503834</v>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
@@ -26527,10 +26519,10 @@
         <v>13.52999973297119</v>
       </c>
       <c r="BC34" t="n">
-        <v>8.476983910706878</v>
+        <v>8.47698390092085</v>
       </c>
       <c r="BD34" t="n">
-        <v>15.72480515436126</v>
+        <v>15.72480513620818</v>
       </c>
       <c r="BE34" t="n">
         <v>13.60185860863947</v>
@@ -26542,7 +26534,7 @@
         <v>30.79666100069315</v>
       </c>
       <c r="BH34" t="n">
-        <v>15.93413122503725</v>
+        <v>15.93413121944943</v>
       </c>
       <c r="BI34" t="n">
         <v>13.60185860863947</v>
@@ -26563,7 +26555,7 @@
         <v>-9.52200303490136</v>
       </c>
       <c r="BO34" t="n">
-        <v>17.76889534008963</v>
+        <v>17.76889529879013</v>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
@@ -26777,10 +26769,10 @@
         <v>32.20999908447266</v>
       </c>
       <c r="BC35" t="n">
-        <v>3.192050002079939</v>
+        <v>3.192362671148793</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.921252753858287</v>
+        <v>5.921832754981011</v>
       </c>
       <c r="BE35" t="n">
         <v>32.6037041916931</v>
@@ -26789,7 +26781,7 @@
         <v>22.83489900991191</v>
       </c>
       <c r="BG35" t="n">
-        <v>40.32381102339259</v>
+        <v>40.32414542881382</v>
       </c>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr"/>
@@ -26842,7 +26834,7 @@
         <v>-0.9227906876323688</v>
       </c>
       <c r="CB35" t="n">
-        <v>-32.45081207696994</v>
+        <v>-32.45080650614594</v>
       </c>
       <c r="CC35" t="b">
         <v>1</v>
@@ -27086,10 +27078,10 @@
         </is>
       </c>
       <c r="BZ36" t="n">
-        <v>9.979999542236328</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="CA36" t="n">
-        <v>-8.016024787124209</v>
+        <v>-6.134963641897039</v>
       </c>
       <c r="CB36" t="n">
         <v>-49.20898677565268</v>
@@ -27105,7 +27097,7 @@
       </c>
       <c r="CF36" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.1%))</t>
         </is>
       </c>
     </row>
@@ -27267,10 +27259,10 @@
         <v>4.559999942779541</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.956948888576273</v>
+        <v>2.957201535081606</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.485140188308986</v>
+        <v>5.485608847576378</v>
       </c>
       <c r="BE37" t="n">
         <v>14.3175353653623</v>
@@ -27279,7 +27271,7 @@
         <v>15.35857567147518</v>
       </c>
       <c r="BG37" t="n">
-        <v>17.28898861901261</v>
+        <v>17.28942992564379</v>
       </c>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
@@ -27468,7 +27460,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>188206235648</v>
+        <v>188534882304</v>
       </c>
       <c r="AQ38" t="n">
         <v>7.4</v>
@@ -27501,28 +27493,28 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BC38" t="n">
-        <v>10.29196479333712</v>
+        <v>10.29196489591731</v>
       </c>
       <c r="BD38" t="n">
-        <v>17.71772032851441</v>
+        <v>17.71772031125781</v>
       </c>
       <c r="BE38" t="n">
-        <v>28.76383900524755</v>
+        <v>28.76383869054264</v>
       </c>
       <c r="BF38" t="n">
         <v>29.45627353735216</v>
       </c>
       <c r="BG38" t="n">
-        <v>32.16446221345369</v>
+        <v>32.16446220460018</v>
       </c>
       <c r="BH38" t="n">
-        <v>18.92450804236636</v>
+        <v>18.92450796590592</v>
       </c>
       <c r="BI38" t="n">
-        <v>17.71772032851441</v>
+        <v>17.71772031125781</v>
       </c>
       <c r="BJ38" t="n">
-        <v>15.94594829566297</v>
+        <v>15.94594828013203</v>
       </c>
       <c r="BK38" t="n">
         <v>3</v>
@@ -27534,10 +27526,10 @@
         <v>2.8</v>
       </c>
       <c r="BN38" t="n">
-        <v>-7.880134098000424</v>
+        <v>-7.880134187722765</v>
       </c>
       <c r="BO38" t="n">
-        <v>9.327028458900521</v>
+        <v>9.327028017187988</v>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
@@ -27576,7 +27568,7 @@
         <v>-8.657228523376116</v>
       </c>
       <c r="CB38" t="n">
-        <v>-18.49891039167376</v>
+        <v>-18.49889545631056</v>
       </c>
       <c r="CC38" t="b">
         <v>1</v>
@@ -27745,10 +27737,10 @@
         <v>29.27000045776367</v>
       </c>
       <c r="BC39" t="n">
-        <v>15.30076006391005</v>
+        <v>15.30119803780329</v>
       </c>
       <c r="BD39" t="n">
-        <v>28.38290991855315</v>
+        <v>28.3837223601251</v>
       </c>
       <c r="BE39" t="n">
         <v>54.77789633691646</v>
@@ -27757,16 +27749,16 @@
         <v>49.52629840645571</v>
       </c>
       <c r="BG39" t="n">
-        <v>61.51138830760567</v>
+        <v>61.51129230422315</v>
       </c>
       <c r="BH39" t="n">
-        <v>32.82052210645989</v>
+        <v>32.82093891161495</v>
       </c>
       <c r="BI39" t="n">
-        <v>28.38290991855315</v>
+        <v>28.3837223601251</v>
       </c>
       <c r="BJ39" t="n">
-        <v>25.54461892669783</v>
+        <v>25.54535012411259</v>
       </c>
       <c r="BK39" t="n">
         <v>3</v>
@@ -27778,10 +27770,10 @@
         <v>3.6</v>
       </c>
       <c r="BN39" t="n">
-        <v>-12.72764425282988</v>
+        <v>-12.72514614075842</v>
       </c>
       <c r="BO39" t="n">
-        <v>12.13024117925652</v>
+        <v>12.1316651804473</v>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
@@ -27993,10 +27985,10 @@
         <v>10.92000007629395</v>
       </c>
       <c r="BC40" t="n">
-        <v>13.59146666882773</v>
+        <v>13.59140307875292</v>
       </c>
       <c r="BD40" t="n">
-        <v>19.78917546981318</v>
+        <v>19.78908288266425</v>
       </c>
       <c r="BE40" t="n">
         <v>17.5801858813401</v>
@@ -28006,7 +27998,7 @@
       </c>
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="n">
-        <v>17.64279923284483</v>
+        <v>17.64276018853889</v>
       </c>
       <c r="BI40" t="n">
         <v>18.5952773963692</v>
@@ -28027,7 +28019,7 @@
         <v>53.25777966855196</v>
       </c>
       <c r="BO40" t="n">
-        <v>61.56409441008432</v>
+        <v>61.56373686149765</v>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
@@ -28056,14 +28048,14 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ40" t="n">
-        <v>11.27999973297119</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="CA40" t="n">
-        <v>-3.191486393612009</v>
+        <v>-3.703704326653801</v>
       </c>
       <c r="CB40" t="n">
         <v>-18.11425560893279</v>
@@ -28079,7 +28071,7 @@
       </c>
       <c r="CF40" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -28241,10 +28233,10 @@
         <v>8.729999542236328</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.378128805017484</v>
+        <v>2.378314290465513</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.411428933307432</v>
+        <v>4.411773008813526</v>
       </c>
       <c r="BE41" t="n">
         <v>13.85299328558459</v>
@@ -28253,10 +28245,10 @@
         <v>15.19033105613702</v>
       </c>
       <c r="BG41" t="n">
-        <v>11.5619104374289</v>
+        <v>11.5619453915507</v>
       </c>
       <c r="BH41" t="n">
-        <v>13.53507825971684</v>
+        <v>13.53508991109077</v>
       </c>
       <c r="BI41" t="n">
         <v>13.85299328558459</v>
@@ -28277,7 +28269,7 @@
         <v>42.81437125748504</v>
       </c>
       <c r="BO41" t="n">
-        <v>55.04099621349597</v>
+        <v>55.04112967712187</v>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
@@ -28310,10 +28302,10 @@
         </is>
       </c>
       <c r="BZ41" t="n">
-        <v>9.680000305175781</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="CA41" t="n">
-        <v>-9.81405715898066</v>
+        <v>-5.005441340050498</v>
       </c>
       <c r="CB41" t="n">
         <v>-38.87866417350647</v>
@@ -28329,7 +28321,7 @@
       </c>
       <c r="CF41" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.0%))</t>
         </is>
       </c>
     </row>
@@ -28491,10 +28483,10 @@
         <v>3.730000019073486</v>
       </c>
       <c r="BC42" t="n">
-        <v>0.862959732186426</v>
+        <v>0.8629597286553933</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.60079030320582</v>
+        <v>1.600790296655755</v>
       </c>
       <c r="BE42" t="n">
         <v>9.964213760629777</v>
@@ -28503,7 +28495,7 @@
         <v>8.938110288944346</v>
       </c>
       <c r="BG42" t="n">
-        <v>12.42769746260571</v>
+        <v>12.42769746046456</v>
       </c>
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr"/>
@@ -28550,10 +28542,10 @@
         </is>
       </c>
       <c r="BZ42" t="n">
-        <v>3.980000019073486</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="CA42" t="n">
-        <v>-6.28140700507328</v>
+        <v>-7.444173079810589</v>
       </c>
       <c r="CB42" t="n">
         <v>-50.82278080073881</v>
@@ -28569,7 +28561,7 @@
       </c>
       <c r="CF42" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-7.4%))</t>
         </is>
       </c>
     </row>
@@ -28721,28 +28713,28 @@
         <v>13.21000003814697</v>
       </c>
       <c r="BC43" t="n">
-        <v>8.866942296153921</v>
+        <v>8.86683587771911</v>
       </c>
       <c r="BD43" t="n">
-        <v>12.10923275158588</v>
+        <v>12.10932066192482</v>
       </c>
       <c r="BE43" t="n">
-        <v>14.77750254834482</v>
+        <v>14.77778718838715</v>
       </c>
       <c r="BF43" t="n">
         <v>16.56967199529428</v>
       </c>
       <c r="BG43" t="n">
-        <v>19.38660580884031</v>
+        <v>19.38671549383291</v>
       </c>
       <c r="BH43" t="n">
-        <v>11.9178925320282</v>
+        <v>11.91798124267702</v>
       </c>
       <c r="BI43" t="n">
-        <v>12.10923275158588</v>
+        <v>12.10932066192482</v>
       </c>
       <c r="BJ43" t="n">
-        <v>10.89830947642729</v>
+        <v>10.89838859573234</v>
       </c>
       <c r="BK43" t="n">
         <v>3</v>
@@ -28754,10 +28746,10 @@
         <v>1.7</v>
       </c>
       <c r="BN43" t="n">
-        <v>-17.49955000033409</v>
+        <v>-17.4989510653998</v>
       </c>
       <c r="BO43" t="n">
-        <v>-9.781283136922825</v>
+        <v>-9.780611595298572</v>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
@@ -28971,10 +28963,10 @@
         <v>32.06000137329102</v>
       </c>
       <c r="BC44" t="n">
-        <v>10.53316571572151</v>
+        <v>10.53323127692031</v>
       </c>
       <c r="BD44" t="n">
-        <v>19.5390224026634</v>
+        <v>19.53914401868718</v>
       </c>
       <c r="BE44" t="n">
         <v>55.7473777160244</v>
@@ -28983,10 +28975,10 @@
         <v>52.52680285382178</v>
       </c>
       <c r="BG44" t="n">
-        <v>58.6485861312441</v>
+        <v>58.64857459708476</v>
       </c>
       <c r="BH44" t="n">
-        <v>55.64092223369676</v>
+        <v>55.64091838897698</v>
       </c>
       <c r="BI44" t="n">
         <v>55.7473777160244</v>
@@ -29007,7 +28999,7 @@
         <v>56.49606299212597</v>
       </c>
       <c r="BO44" t="n">
-        <v>73.55246366287076</v>
+        <v>73.55245167060747</v>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
@@ -29221,28 +29213,28 @@
         <v>10.22999954223633</v>
       </c>
       <c r="BC45" t="n">
-        <v>7.128662244245931</v>
+        <v>7.12866225188</v>
       </c>
       <c r="BD45" t="n">
-        <v>11.18073448119771</v>
+        <v>11.18073448395422</v>
       </c>
       <c r="BE45" t="n">
-        <v>19.06932858947494</v>
+        <v>19.06932857375501</v>
       </c>
       <c r="BF45" t="n">
         <v>24.00353367466198</v>
       </c>
       <c r="BG45" t="n">
-        <v>24.53460084233446</v>
+        <v>24.5346008480833</v>
       </c>
       <c r="BH45" t="n">
-        <v>19.69704939691727</v>
+        <v>19.69704939511363</v>
       </c>
       <c r="BI45" t="n">
-        <v>21.53643113206846</v>
+        <v>21.5364311242085</v>
       </c>
       <c r="BJ45" t="n">
-        <v>19.38278801886161</v>
+        <v>19.38278801178765</v>
       </c>
       <c r="BK45" t="n">
         <v>4</v>
@@ -29254,10 +29246,10 @@
         <v>3.4</v>
       </c>
       <c r="BN45" t="n">
-        <v>89.47007708882499</v>
+        <v>89.47007701967577</v>
       </c>
       <c r="BO45" t="n">
-        <v>92.54203595605833</v>
+        <v>92.54203593842738</v>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
@@ -29479,28 +29471,28 @@
         <v>15.47999954223633</v>
       </c>
       <c r="BC46" t="n">
-        <v>6.00531792663848</v>
+        <v>6.005304912799816</v>
       </c>
       <c r="BD46" t="n">
-        <v>8.192697921389517</v>
+        <v>8.192707861552107</v>
       </c>
       <c r="BE46" t="n">
-        <v>10.04301041040262</v>
+        <v>10.04304435934426</v>
       </c>
       <c r="BF46" t="n">
         <v>11.40440666376979</v>
       </c>
       <c r="BG46" t="n">
-        <v>9.091315837895866</v>
+        <v>9.091337231468279</v>
       </c>
       <c r="BH46" t="n">
-        <v>8.947349752019255</v>
+        <v>8.94736020578685</v>
       </c>
       <c r="BI46" t="n">
-        <v>9.091315837895866</v>
+        <v>9.091337231468279</v>
       </c>
       <c r="BJ46" t="n">
-        <v>8.18218425410628</v>
+        <v>8.18220350832145</v>
       </c>
       <c r="BK46" t="n">
         <v>5</v>
@@ -29512,10 +29504,10 @@
         <v>1.9</v>
       </c>
       <c r="BN46" t="n">
-        <v>-47.14351100733795</v>
+        <v>-47.14338662609933</v>
       </c>
       <c r="BO46" t="n">
-        <v>-42.20058128808788</v>
+        <v>-42.20051375728746</v>
       </c>
       <c r="BP46" t="inlineStr">
         <is>
@@ -29723,10 +29715,10 @@
         <v>40.75</v>
       </c>
       <c r="BC47" t="n">
-        <v>20.81475789541569</v>
+        <v>20.8234608320114</v>
       </c>
       <c r="BD47" t="n">
-        <v>38.6113758959961</v>
+        <v>38.62751984338114</v>
       </c>
       <c r="BE47" t="n">
         <v>56.01011410788382</v>
@@ -29735,16 +29727,16 @@
         <v>42.35975890449271</v>
       </c>
       <c r="BG47" t="n">
-        <v>59.70827304423335</v>
+        <v>59.69355883405037</v>
       </c>
       <c r="BH47" t="n">
-        <v>38.47874929976521</v>
+        <v>38.48703159442545</v>
       </c>
       <c r="BI47" t="n">
-        <v>38.6113758959961</v>
+        <v>38.62751984338114</v>
       </c>
       <c r="BJ47" t="n">
-        <v>34.75023830639649</v>
+        <v>34.76476785904303</v>
       </c>
       <c r="BK47" t="n">
         <v>3</v>
@@ -29756,10 +29748,10 @@
         <v>2.7</v>
       </c>
       <c r="BN47" t="n">
-        <v>-14.72334157939512</v>
+        <v>-14.68768623547722</v>
       </c>
       <c r="BO47" t="n">
-        <v>-5.573621350269431</v>
+        <v>-5.553296700796439</v>
       </c>
       <c r="BP47" t="inlineStr">
         <is>
@@ -29798,7 +29790,7 @@
         <v>-5.60574072640605</v>
       </c>
       <c r="CB47" t="n">
-        <v>-16.35819966493404</v>
+        <v>-16.32274316665727</v>
       </c>
       <c r="CC47" t="b">
         <v>1</v>
@@ -29973,10 +29965,10 @@
         <v>14.60999965667725</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.796142723561469</v>
+        <v>1.796142703837045</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.331844752206525</v>
+        <v>3.331844715617718</v>
       </c>
       <c r="BE48" t="n">
         <v>12.42506389287378</v>
@@ -29985,7 +29977,7 @@
         <v>9.006705029899456</v>
       </c>
       <c r="BG48" t="n">
-        <v>15.68010224518737</v>
+        <v>15.68010222746324</v>
       </c>
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr"/>
@@ -30213,10 +30205,10 @@
         <v>10.76000022888184</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.224745449055138</v>
+        <v>4.224894025804548</v>
       </c>
       <c r="BD49" t="n">
-        <v>7.836902807997281</v>
+        <v>7.837178417867436</v>
       </c>
       <c r="BE49" t="n">
         <v>25.36832794175877</v>
@@ -30225,10 +30217,10 @@
         <v>28.51661379864785</v>
       </c>
       <c r="BG49" t="n">
-        <v>23.95401013502834</v>
+        <v>23.95416912748375</v>
       </c>
       <c r="BH49" t="n">
-        <v>25.94631729181166</v>
+        <v>25.94637028929679</v>
       </c>
       <c r="BI49" t="n">
         <v>25.36832794175877</v>
@@ -30249,7 +30241,7 @@
         <v>112.1886120996441</v>
       </c>
       <c r="BO49" t="n">
-        <v>141.1367726755891</v>
+        <v>141.137265217262</v>
       </c>
       <c r="BP49" t="inlineStr">
         <is>
@@ -30282,10 +30274,10 @@
         </is>
       </c>
       <c r="BZ49" t="n">
-        <v>12.0600004196167</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="CA49" t="n">
-        <v>-10.77943735905924</v>
+        <v>-10.40799314053285</v>
       </c>
       <c r="CB49" t="n">
         <v>-35.14712749925304</v>
@@ -30301,7 +30293,7 @@
       </c>
       <c r="CF49" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-10.4%))</t>
         </is>
       </c>
     </row>
@@ -30358,7 +30350,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -30463,10 +30455,10 @@
         <v>33.63000106811523</v>
       </c>
       <c r="BC50" t="n">
-        <v>9.265734339630411</v>
+        <v>9.265734313710745</v>
       </c>
       <c r="BD50" t="n">
-        <v>17.18793720001441</v>
+        <v>17.18793715193343</v>
       </c>
       <c r="BE50" t="n">
         <v>62.58392052704027</v>
@@ -30475,7 +30467,7 @@
         <v>36.51831633599926</v>
       </c>
       <c r="BG50" t="n">
-        <v>89.06886190681941</v>
+        <v>89.06886185585377</v>
       </c>
       <c r="BH50" t="inlineStr"/>
       <c r="BI50" t="inlineStr"/>
@@ -30506,8 +30498,16 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BS50" t="inlineStr"/>
-      <c r="BT50" t="inlineStr"/>
+      <c r="BS50" t="inlineStr">
+        <is>
+          <t>A Construtora Tenda (TEND3) apresenta uma dinâmica intrigante de qualidade versus preço, onde a alta rentabilidade medida pelo ROE de 37,6% e pelo ROIC de 14,4% — ambos posicionados acima dos pares do setor de consumo discricionário, que registram 12,2% e 12,5% respectivamente — convive com um múltiplo P/L de 7,12, sugerindo que o mercado pode estar precificando o papel com desconto, embora o P/VP de 2,68 indique um prêmio sobre o valor patrimonial. Essa forte rentabilidade operacional é suportada por um endividamento controlado, com a relação dívida/patrimônio em 0,79 e uma liquidez corrente confortável de 1,96, demonstrando que a empresa consegue gerar retornos expressivos sem comprometer sua saúde financeira de curto prazo. Por outro lado, o dividendo atual de 2,45% mostra-se modesto e altamente sustentável frente ao lucro gerado, indicando uma postura conservadora de retenção de caixa para fazer frente à estrutura de capital, especialmente quando se observa que a companhia enfrenta uma severa contração histórica, com um CAGR de receita nos últimos cinco anos de -11,5%, performance que está drasticamente abaixo da média setorial de 49,8%. Esse gargalo no crescimento e a existência de vendas por parte de insiders pesaram no checklist de critérios fundamentalistas, no qual a empresa atendeu a apenas 4 dos 7 requisitos avaliados, falhando em atingir a margem líquida desejada de 15% e em superar a expansão de seus pares. No campo do valuation, a análise dos preços-teto revela uma dispersão brutal entre os métodos de fluxo de caixa descontado e múltiplos de crescimento, com o modelo DCF apontando R$ 62,58 e o método de Lynch alcançando R$ 89,07, enquanto as metodologias focadas em dividendos de Bazin e Gordon limitam-se a R$ 9,27 e R$ 17,19, respectivamente, situando o preço atual de R$ 33,63 próximo ao teto de Graham de R$ 36,52. Em balanço, os prós da TEND3 residem em sua eficiência operacional superior à média do setor e na sólida liquidez, ao passo que os contras concentram-se no encolhimento histórico de sua receita, no baixo retorno em dividendos e na tendência gráfica de baixa que atualmente pressiona o ativo.</t>
+        </is>
+      </c>
+      <c r="BT50" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="BU50" t="b">
         <v>0</v>
       </c>
@@ -30534,14 +30534,14 @@
         <v>1</v>
       </c>
       <c r="CD50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF50" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (+0.5%))</t>
+          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -30703,28 +30703,28 @@
         <v>39.25</v>
       </c>
       <c r="BC51" t="n">
-        <v>29.94848816372241</v>
+        <v>29.94881197511332</v>
       </c>
       <c r="BD51" t="n">
-        <v>34.22993623235111</v>
+        <v>34.22970054837481</v>
       </c>
       <c r="BE51" t="n">
-        <v>37.17367914326704</v>
+        <v>37.17302126563244</v>
       </c>
       <c r="BF51" t="n">
         <v>48.635437456445</v>
       </c>
       <c r="BG51" t="n">
-        <v>55.74358174330671</v>
+        <v>55.74321458326236</v>
       </c>
       <c r="BH51" t="n">
-        <v>41.14622454781845</v>
+        <v>41.14603716576559</v>
       </c>
       <c r="BI51" t="n">
-        <v>37.17367914326704</v>
+        <v>37.17302126563244</v>
       </c>
       <c r="BJ51" t="n">
-        <v>33.45631122894034</v>
+        <v>33.4557191390692</v>
       </c>
       <c r="BK51" t="n">
         <v>5</v>
@@ -30736,10 +30736,10 @@
         <v>1.9</v>
       </c>
       <c r="BN51" t="n">
-        <v>-14.76099049951507</v>
+        <v>-14.76249900874088</v>
       </c>
       <c r="BO51" t="n">
-        <v>4.831145344760368</v>
+        <v>4.830667938256283</v>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
@@ -30953,10 +30953,10 @@
         <v>21.60000038146973</v>
       </c>
       <c r="BC52" t="n">
-        <v>5.970936721719919</v>
+        <v>5.971129789919972</v>
       </c>
       <c r="BD52" t="n">
-        <v>11.07608761879045</v>
+        <v>11.07644576030155</v>
       </c>
       <c r="BE52" t="n">
         <v>32.85878358834372</v>
@@ -30965,10 +30965,10 @@
         <v>33.87983533191721</v>
       </c>
       <c r="BG52" t="n">
-        <v>29.48949481451582</v>
+        <v>29.4894780847462</v>
       </c>
       <c r="BH52" t="n">
-        <v>32.07603791159224</v>
+        <v>32.07603233500237</v>
       </c>
       <c r="BI52" t="n">
         <v>32.85878358834372</v>
@@ -30989,7 +30989,7 @@
         <v>36.91159586681971</v>
       </c>
       <c r="BO52" t="n">
-        <v>48.50017289402333</v>
+        <v>48.50014707647809</v>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
@@ -31211,28 +31211,28 @@
         <v>44.79999923706055</v>
       </c>
       <c r="BC53" t="n">
-        <v>32.52363716000399</v>
+        <v>32.52379706107593</v>
       </c>
       <c r="BD53" t="n">
-        <v>39.13675493205022</v>
+        <v>39.13655681504563</v>
       </c>
       <c r="BE53" t="n">
-        <v>42.97616582344318</v>
+        <v>42.9757369823044</v>
       </c>
       <c r="BF53" t="n">
         <v>48.75816249197349</v>
       </c>
       <c r="BG53" t="n">
-        <v>61.413686761819</v>
+        <v>61.4134056077642</v>
       </c>
       <c r="BH53" t="n">
-        <v>44.96168143385798</v>
+        <v>44.96153179163273</v>
       </c>
       <c r="BI53" t="n">
-        <v>42.97616582344318</v>
+        <v>42.9757369823044</v>
       </c>
       <c r="BJ53" t="n">
-        <v>38.67854924109886</v>
+        <v>38.67816328407396</v>
       </c>
       <c r="BK53" t="n">
         <v>5</v>
@@ -31244,10 +31244,10 @@
         <v>1.9</v>
       </c>
       <c r="BN53" t="n">
-        <v>-13.66395111653874</v>
+        <v>-13.66481262776972</v>
       </c>
       <c r="BO53" t="n">
-        <v>0.3608977668545954</v>
+        <v>0.3605637440247111</v>
       </c>
       <c r="BP53" t="inlineStr">
         <is>
@@ -31280,10 +31280,10 @@
         </is>
       </c>
       <c r="BZ53" t="n">
-        <v>47.18999862670898</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="CA53" t="n">
-        <v>-5.064631191355295</v>
+        <v>-4.416470539784967</v>
       </c>
       <c r="CB53" t="n">
         <v>-15.45867760032158</v>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="CF53" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-4.4%))</t>
         </is>
       </c>
     </row>
@@ -31461,10 +31461,10 @@
         <v>17.01000022888184</v>
       </c>
       <c r="BC54" t="n">
-        <v>4.289789745148792</v>
+        <v>4.28978974483453</v>
       </c>
       <c r="BD54" t="n">
-        <v>7.95755997725101</v>
+        <v>7.957559976668052</v>
       </c>
       <c r="BE54" t="n">
         <v>53.40817607409581</v>
@@ -31473,7 +31473,7 @@
         <v>59.21244778820295</v>
       </c>
       <c r="BG54" t="n">
-        <v>49.87167345048983</v>
+        <v>49.87167344990439</v>
       </c>
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr"/>
@@ -31701,10 +31701,10 @@
         <v>26.88999938964844</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.92953099137617</v>
+        <v>4.92961332041522</v>
       </c>
       <c r="BD55" t="n">
-        <v>9.144279989002793</v>
+        <v>9.144432709370232</v>
       </c>
       <c r="BE55" t="n">
         <v>32.80778010247162</v>
@@ -31713,7 +31713,7 @@
         <v>26.27467010357014</v>
       </c>
       <c r="BG55" t="n">
-        <v>42.01974116688378</v>
+        <v>42.01961712455591</v>
       </c>
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr"/>
@@ -31760,10 +31760,10 @@
         </is>
       </c>
       <c r="BZ55" t="n">
-        <v>29.29999923706055</v>
+        <v>29.29000091552734</v>
       </c>
       <c r="CA55" t="n">
-        <v>-8.225255666094988</v>
+        <v>-8.193927793995414</v>
       </c>
       <c r="CB55" t="n">
         <v>-23.86318934952274</v>
@@ -31937,10 +31937,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BC56" t="n">
-        <v>4.260124235109153</v>
+        <v>4.260415031823313</v>
       </c>
       <c r="BD56" t="n">
-        <v>7.902530456127478</v>
+        <v>7.903069884032244</v>
       </c>
       <c r="BE56" t="n">
         <v>28.50331556048675</v>
@@ -31949,10 +31949,10 @@
         <v>28.40047712893599</v>
       </c>
       <c r="BG56" t="n">
-        <v>25.37662004197035</v>
+        <v>25.37645360232409</v>
       </c>
       <c r="BH56" t="n">
-        <v>27.4268042437977</v>
+        <v>27.42674876391561</v>
       </c>
       <c r="BI56" t="n">
         <v>28.40047712893599</v>
@@ -31973,7 +31973,7 @@
         <v>5.057252347697139</v>
       </c>
       <c r="BO56" t="n">
-        <v>12.7283367439482</v>
+        <v>12.72810871319496</v>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
@@ -32002,10 +32002,10 @@
         </is>
       </c>
       <c r="BZ56" t="n">
-        <v>25.72999954223633</v>
+        <v>25.56999969482422</v>
       </c>
       <c r="CA56" t="n">
-        <v>-5.44111793018941</v>
+        <v>-4.849432091972849</v>
       </c>
       <c r="CB56" t="n">
         <v>-20.03706285314828</v>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="CF56" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.8%))</t>
         </is>
       </c>
     </row>
@@ -32177,10 +32177,10 @@
         <v>53.90999984741211</v>
       </c>
       <c r="BC57" t="n">
-        <v>9.565171248510964</v>
+        <v>9.5651712637509</v>
       </c>
       <c r="BD57" t="n">
-        <v>17.74339266598784</v>
+        <v>17.74339269425792</v>
       </c>
       <c r="BE57" t="n">
         <v>58.9362622094233</v>
@@ -32189,16 +32189,16 @@
         <v>43.81836007058834</v>
       </c>
       <c r="BG57" t="n">
-        <v>77.76917452065473</v>
+        <v>77.76917453825861</v>
       </c>
       <c r="BH57" t="n">
-        <v>13.6542819572494</v>
+        <v>13.65428197900441</v>
       </c>
       <c r="BI57" t="n">
-        <v>13.6542819572494</v>
+        <v>13.65428197900441</v>
       </c>
       <c r="BJ57" t="n">
-        <v>12.28885376152446</v>
+        <v>12.28885378110397</v>
       </c>
       <c r="BK57" t="n">
         <v>2</v>
@@ -32210,10 +32210,10 @@
         <v>6.2</v>
       </c>
       <c r="BN57" t="n">
-        <v>-77.20487145927089</v>
+        <v>-77.20487142295201</v>
       </c>
       <c r="BO57" t="n">
-        <v>-74.67207939918987</v>
+        <v>-74.67207935883556</v>
       </c>
       <c r="BP57" t="inlineStr">
         <is>
@@ -32427,28 +32427,28 @@
         <v>22.85000038146973</v>
       </c>
       <c r="BC58" t="n">
-        <v>9.749536076112411</v>
+        <v>9.749536059041692</v>
       </c>
       <c r="BD58" t="n">
-        <v>14.83800011875651</v>
+        <v>14.83800012820692</v>
       </c>
       <c r="BE58" t="n">
-        <v>20.27745782861943</v>
+        <v>20.2774578770386</v>
       </c>
       <c r="BF58" t="n">
         <v>21.84295533173045</v>
       </c>
       <c r="BG58" t="n">
-        <v>19.34340932121063</v>
+        <v>19.34340934087171</v>
       </c>
       <c r="BH58" t="n">
-        <v>17.21027173528589</v>
+        <v>17.21027174737788</v>
       </c>
       <c r="BI58" t="n">
-        <v>19.34340932121063</v>
+        <v>19.34340934087171</v>
       </c>
       <c r="BJ58" t="n">
-        <v>17.40906838908957</v>
+        <v>17.40906840678454</v>
       </c>
       <c r="BK58" t="n">
         <v>5</v>
@@ -32460,10 +32460,10 @@
         <v>2.2</v>
       </c>
       <c r="BN58" t="n">
-        <v>-23.81151816869334</v>
+        <v>-23.81151809125361</v>
       </c>
       <c r="BO58" t="n">
-        <v>-24.68152539182186</v>
+        <v>-24.68152533890285</v>
       </c>
       <c r="BP58" t="inlineStr">
         <is>
@@ -32677,28 +32677,28 @@
         <v>25.25</v>
       </c>
       <c r="BC59" t="n">
-        <v>23.84003426283585</v>
+        <v>23.8394546539541</v>
       </c>
       <c r="BD59" t="n">
-        <v>29.17643732372149</v>
+        <v>29.17629081891948</v>
       </c>
       <c r="BE59" t="n">
-        <v>37.22237140002338</v>
+        <v>37.22308947716972</v>
       </c>
       <c r="BF59" t="n">
         <v>61.96622221610712</v>
       </c>
       <c r="BG59" t="n">
-        <v>66.06729468284735</v>
+        <v>66.06678887156686</v>
       </c>
       <c r="BH59" t="n">
-        <v>43.65447197710704</v>
+        <v>43.65436920754346</v>
       </c>
       <c r="BI59" t="n">
-        <v>37.22237140002338</v>
+        <v>37.22308947716972</v>
       </c>
       <c r="BJ59" t="n">
-        <v>33.50013426002105</v>
+        <v>33.50078052945275</v>
       </c>
       <c r="BK59" t="n">
         <v>5</v>
@@ -32710,10 +32710,10 @@
         <v>2.8</v>
       </c>
       <c r="BN59" t="n">
-        <v>32.67379904958831</v>
+        <v>32.67635853248614</v>
       </c>
       <c r="BO59" t="n">
-        <v>72.88899792913676</v>
+        <v>72.88859092096421</v>
       </c>
       <c r="BP59" t="inlineStr">
         <is>
@@ -32746,10 +32746,10 @@
         </is>
       </c>
       <c r="BZ59" t="n">
-        <v>26.54999923706055</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="CA59" t="n">
-        <v>-4.896419112682715</v>
+        <v>-4.283545097481212</v>
       </c>
       <c r="CB59" t="n">
         <v>-12.02090826211568</v>
@@ -32765,7 +32765,7 @@
       </c>
       <c r="CF59" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -32927,10 +32927,10 @@
         <v>17.48999977111816</v>
       </c>
       <c r="BC60" t="n">
-        <v>4.023650646863912</v>
+        <v>4.023974876566939</v>
       </c>
       <c r="BD60" t="n">
-        <v>7.463871949932558</v>
+        <v>7.464473396031672</v>
       </c>
       <c r="BE60" t="n">
         <v>27.23178577759291</v>
@@ -32939,7 +32939,7 @@
         <v>33.75103601978793</v>
       </c>
       <c r="BG60" t="n">
-        <v>19.04707891521709</v>
+        <v>19.04723419640374</v>
       </c>
       <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr"/>
@@ -32986,13 +32986,13 @@
         </is>
       </c>
       <c r="BZ60" t="n">
-        <v>18.00869941711426</v>
+        <v>17.81902885437012</v>
       </c>
       <c r="CA60" t="n">
-        <v>-2.880272661462469</v>
+        <v>-1.846504015123462</v>
       </c>
       <c r="CB60" t="n">
-        <v>-39.62281758244762</v>
+        <v>-39.62282580198882</v>
       </c>
       <c r="CC60" t="b">
         <v>1</v>
@@ -33005,7 +33005,7 @@
       </c>
       <c r="CF60" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
         </is>
       </c>
     </row>
@@ -33165,10 +33165,10 @@
         <v>5.449999809265137</v>
       </c>
       <c r="BC61" t="n">
-        <v>6.469480044243205</v>
+        <v>6.469162172284941</v>
       </c>
       <c r="BD61" t="n">
-        <v>9.419562944418105</v>
+        <v>9.419100122846874</v>
       </c>
       <c r="BE61" t="n">
         <v>4.268072139785951</v>
@@ -33178,13 +33178,13 @@
       </c>
       <c r="BG61" t="inlineStr"/>
       <c r="BH61" t="n">
-        <v>5.906721042393592</v>
+        <v>5.906525869011218</v>
       </c>
       <c r="BI61" t="n">
-        <v>5.368776092014578</v>
+        <v>5.368617156035446</v>
       </c>
       <c r="BJ61" t="n">
-        <v>4.83189848281312</v>
+        <v>4.831755440431902</v>
       </c>
       <c r="BK61" t="n">
         <v>4</v>
@@ -33196,10 +33196,10 @@
         <v>2.7</v>
       </c>
       <c r="BN61" t="n">
-        <v>-11.34130913915316</v>
+        <v>-11.34393377009305</v>
       </c>
       <c r="BO61" t="n">
-        <v>8.380206405732672</v>
+        <v>8.376625242627988</v>
       </c>
       <c r="BP61" t="inlineStr">
         <is>
@@ -33413,10 +33413,10 @@
         <v>48.11999893188477</v>
       </c>
       <c r="BC62" t="n">
-        <v>8.009597792940541</v>
+        <v>8.009589100297546</v>
       </c>
       <c r="BD62" t="n">
-        <v>14.8578039059047</v>
+        <v>14.85778778105195</v>
       </c>
       <c r="BE62" t="n">
         <v>19.73962804481341</v>
@@ -33425,16 +33425,16 @@
         <v>12.27215611980214</v>
       </c>
       <c r="BG62" t="n">
-        <v>15.68910802594344</v>
+        <v>15.68914461296023</v>
       </c>
       <c r="BH62" t="n">
-        <v>14.11365877788085</v>
+        <v>14.11366113178506</v>
       </c>
       <c r="BI62" t="n">
-        <v>14.8578039059047</v>
+        <v>14.85778778105195</v>
       </c>
       <c r="BJ62" t="n">
-        <v>13.37202351531423</v>
+        <v>13.37200900294675</v>
       </c>
       <c r="BK62" t="n">
         <v>5</v>
@@ -33446,10 +33446,10 @@
         <v>2.5</v>
       </c>
       <c r="BN62" t="n">
-        <v>-72.2110893347219</v>
+        <v>-72.21111949342473</v>
       </c>
       <c r="BO62" t="n">
-        <v>-70.66986888786275</v>
+        <v>-70.66986399612489</v>
       </c>
       <c r="BP62" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ62" t="n">
@@ -33488,7 +33488,7 @@
         <v>-2.135446972059685</v>
       </c>
       <c r="CB62" t="n">
-        <v>-11.35737468710545</v>
+        <v>-11.35736832508161</v>
       </c>
       <c r="CC62" t="b">
         <v>1</v>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="CF62" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-2.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-2.1%))</t>
         </is>
       </c>
     </row>
@@ -33663,28 +33663,28 @@
         <v>34.04000091552734</v>
       </c>
       <c r="BC63" t="n">
-        <v>15.41291056384467</v>
+        <v>15.41342429954083</v>
       </c>
       <c r="BD63" t="n">
-        <v>23.75471177736489</v>
+        <v>23.75503652995809</v>
       </c>
       <c r="BE63" t="n">
-        <v>44.61155365552684</v>
+        <v>44.61067660215662</v>
       </c>
       <c r="BF63" t="n">
         <v>61.90114319514688</v>
       </c>
       <c r="BG63" t="n">
-        <v>43.95187360773868</v>
+        <v>43.95203649620341</v>
       </c>
       <c r="BH63" t="n">
-        <v>43.55482055894431</v>
+        <v>43.55472320586625</v>
       </c>
       <c r="BI63" t="n">
-        <v>44.28171363163275</v>
+        <v>44.28135654918002</v>
       </c>
       <c r="BJ63" t="n">
-        <v>39.85354226846948</v>
+        <v>39.85322089426202</v>
       </c>
       <c r="BK63" t="n">
         <v>4</v>
@@ -33696,10 +33696,10 @@
         <v>4</v>
       </c>
       <c r="BN63" t="n">
-        <v>17.07855815682511</v>
+        <v>17.07761404930801</v>
       </c>
       <c r="BO63" t="n">
-        <v>27.95187834168591</v>
+        <v>27.95159234557707</v>
       </c>
       <c r="BP63" t="inlineStr">
         <is>
@@ -33732,10 +33732,10 @@
         </is>
       </c>
       <c r="BZ63" t="n">
-        <v>37.22999954223633</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="CA63" t="n">
-        <v>-8.568355267074413</v>
+        <v>-8.346791936095499</v>
       </c>
       <c r="CB63" t="n">
         <v>-30.1313627614148</v>
@@ -33751,7 +33751,7 @@
       </c>
       <c r="CF63" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.6%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.3%))</t>
         </is>
       </c>
     </row>
@@ -33913,10 +33913,10 @@
         <v>14.67000007629395</v>
       </c>
       <c r="BC64" t="n">
-        <v>9.603373387456351</v>
+        <v>9.603183653427763</v>
       </c>
       <c r="BD64" t="n">
-        <v>17.81425763373153</v>
+        <v>17.8139056771085</v>
       </c>
       <c r="BE64" t="n">
         <v>13.92388975722742</v>
@@ -33928,7 +33928,7 @@
         <v>31.52578812957152</v>
       </c>
       <c r="BH64" t="n">
-        <v>17.34212017461504</v>
+        <v>17.34201183648471</v>
       </c>
       <c r="BI64" t="n">
         <v>13.92388975722742</v>
@@ -33949,7 +33949,7 @@
         <v>-14.57736389684815</v>
       </c>
       <c r="BO64" t="n">
-        <v>18.21486083452118</v>
+        <v>18.21412233329578</v>
       </c>
       <c r="BP64" t="inlineStr">
         <is>
@@ -34163,10 +34163,10 @@
         <v>12.02000045776367</v>
       </c>
       <c r="BC65" t="n">
-        <v>2.065662775782936</v>
+        <v>2.065318666548591</v>
       </c>
       <c r="BD65" t="n">
-        <v>3.831804449077346</v>
+        <v>3.831166126447637</v>
       </c>
       <c r="BE65" t="n">
         <v>25.40111739479564</v>
@@ -34175,7 +34175,7 @@
         <v>21.80965139478351</v>
       </c>
       <c r="BG65" t="n">
-        <v>32.93730972477155</v>
+        <v>32.93737962888861</v>
       </c>
       <c r="BH65" t="inlineStr"/>
       <c r="BI65" t="inlineStr"/>
@@ -34403,10 +34403,10 @@
         <v>14.77000045776367</v>
       </c>
       <c r="BC66" t="n">
-        <v>3.587795689824245</v>
+        <v>3.588011762197898</v>
       </c>
       <c r="BD66" t="n">
-        <v>6.655361004623973</v>
+        <v>6.655761818877101</v>
       </c>
       <c r="BE66" t="n">
         <v>33.33943885270335</v>
@@ -34415,7 +34415,7 @@
         <v>35.32769610508908</v>
       </c>
       <c r="BG66" t="n">
-        <v>31.41460505996929</v>
+        <v>31.4147770554192</v>
       </c>
       <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr"/>
@@ -34627,34 +34627,34 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr"/>
       <c r="BA67" t="n">
-        <v>20.25</v>
+        <v>20.27</v>
       </c>
       <c r="BB67" t="n">
         <v>13</v>
       </c>
       <c r="BC67" t="n">
-        <v>10.62770854725094</v>
+        <v>10.62792834638531</v>
       </c>
       <c r="BD67" t="n">
-        <v>11.00447432721045</v>
+        <v>11.0043350966168</v>
       </c>
       <c r="BE67" t="n">
-        <v>11.24550252971299</v>
+        <v>11.24512768117222</v>
       </c>
       <c r="BF67" t="n">
         <v>16.22214211307625</v>
       </c>
       <c r="BG67" t="n">
-        <v>18.04409206779455</v>
+        <v>18.04384576679731</v>
       </c>
       <c r="BH67" t="n">
-        <v>10.95922846805813</v>
+        <v>10.95913037472477</v>
       </c>
       <c r="BI67" t="n">
-        <v>11.00447432721045</v>
+        <v>11.0043350966168</v>
       </c>
       <c r="BJ67" t="n">
-        <v>9.904026894489407</v>
+        <v>9.903901586955119</v>
       </c>
       <c r="BK67" t="n">
         <v>3</v>
@@ -34666,10 +34666,10 @@
         <v>1.1</v>
       </c>
       <c r="BN67" t="n">
-        <v>-23.81517773469687</v>
+        <v>-23.81614163880678</v>
       </c>
       <c r="BO67" t="n">
-        <v>-15.69824255339902</v>
+        <v>-15.69899711750173</v>
       </c>
       <c r="BP67" t="inlineStr">
         <is>
@@ -34698,10 +34698,10 @@
         </is>
       </c>
       <c r="BZ67" t="n">
-        <v>14.73999977111816</v>
+        <v>14.72000026702881</v>
       </c>
       <c r="CA67" t="n">
-        <v>-11.80461192765792</v>
+        <v>-11.68478421078172</v>
       </c>
       <c r="CB67" t="n">
         <v>-39.52341924380666</v>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="CF67" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-11.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-11.7%))</t>
         </is>
       </c>
     </row>
@@ -34873,34 +34873,34 @@
         <v>0.3</v>
       </c>
       <c r="BA68" t="n">
-        <v>38.78</v>
+        <v>38.87</v>
       </c>
       <c r="BB68" t="n">
         <v>30.57999992370605</v>
       </c>
       <c r="BC68" t="n">
-        <v>14.05016486467948</v>
+        <v>14.05152757352989</v>
       </c>
       <c r="BD68" t="n">
-        <v>14.50370224052288</v>
+        <v>14.50397490819717</v>
       </c>
       <c r="BE68" t="n">
-        <v>15.08223511028423</v>
+        <v>15.08105596054267</v>
       </c>
       <c r="BF68" t="n">
         <v>30.63109436188252</v>
       </c>
       <c r="BG68" t="n">
-        <v>13.94588675370759</v>
+        <v>13.94524553766648</v>
       </c>
       <c r="BH68" t="n">
-        <v>17.64261666621534</v>
+        <v>17.64257966836374</v>
       </c>
       <c r="BI68" t="n">
-        <v>14.50370224052288</v>
+        <v>14.50397490819717</v>
       </c>
       <c r="BJ68" t="n">
-        <v>13.05333201647059</v>
+        <v>13.05357741737745</v>
       </c>
       <c r="BK68" t="n">
         <v>5</v>
@@ -34912,10 +34912,10 @@
         <v>2.2</v>
       </c>
       <c r="BN68" t="n">
-        <v>-57.31415288084594</v>
+        <v>-57.31335039259391</v>
       </c>
       <c r="BO68" t="n">
-        <v>-42.30668178472254</v>
+        <v>-42.30680277181111</v>
       </c>
       <c r="BP68" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>14.48999977111816</v>
       </c>
       <c r="BC69" t="n">
-        <v>2.3376867816433</v>
+        <v>2.337709886727121</v>
       </c>
       <c r="BD69" t="n">
-        <v>4.336408979948322</v>
+        <v>4.336451839878809</v>
       </c>
       <c r="BE69" t="n">
         <v>25.42946979699545</v>
@@ -35141,7 +35141,7 @@
         <v>19.47350783979101</v>
       </c>
       <c r="BG69" t="n">
-        <v>33.12286245162632</v>
+        <v>33.12290529549036</v>
       </c>
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr"/>
@@ -35332,7 +35332,7 @@
         <v>1</v>
       </c>
       <c r="AP70" t="n">
-        <v>14564848640</v>
+        <v>14560741376</v>
       </c>
       <c r="AQ70" t="n">
         <v>18.33</v>
@@ -35369,10 +35369,10 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BC70" t="n">
-        <v>6.50100164074772</v>
+        <v>6.500814309339336</v>
       </c>
       <c r="BD70" t="n">
-        <v>12.05935804358702</v>
+        <v>12.05901054382447</v>
       </c>
       <c r="BE70" t="n">
         <v>7.958674469868212</v>
@@ -35384,13 +35384,13 @@
         <v>18.01964030913558</v>
       </c>
       <c r="BH70" t="n">
-        <v>11.70620423882222</v>
+        <v>11.70609727258804</v>
       </c>
       <c r="BI70" t="n">
-        <v>12.05935804358702</v>
+        <v>12.05901054382447</v>
       </c>
       <c r="BJ70" t="n">
-        <v>10.85342223922832</v>
+        <v>10.85310948944202</v>
       </c>
       <c r="BK70" t="n">
         <v>5</v>
@@ -35402,10 +35402,10 @@
         <v>2.8</v>
       </c>
       <c r="BN70" t="n">
-        <v>-1.422143382365948</v>
+        <v>-1.424983979820904</v>
       </c>
       <c r="BO70" t="n">
-        <v>6.323378705425275</v>
+        <v>6.322407168350197</v>
       </c>
       <c r="BP70" t="inlineStr">
         <is>
@@ -35619,28 +35619,28 @@
         <v>18.95000076293945</v>
       </c>
       <c r="BC71" t="n">
-        <v>8.192805130248425</v>
+        <v>8.19280512203467</v>
       </c>
       <c r="BD71" t="n">
-        <v>9.244987540860647</v>
+        <v>9.244987541182551</v>
       </c>
       <c r="BE71" t="n">
-        <v>10.37640922769413</v>
+        <v>10.37640923845837</v>
       </c>
       <c r="BF71" t="n">
         <v>16.95234968520165</v>
       </c>
       <c r="BG71" t="n">
-        <v>9.616899129095341</v>
+        <v>9.61689913623238</v>
       </c>
       <c r="BH71" t="n">
-        <v>10.87669014262004</v>
+        <v>10.87669014462192</v>
       </c>
       <c r="BI71" t="n">
-        <v>9.616899129095341</v>
+        <v>9.61689913623238</v>
       </c>
       <c r="BJ71" t="n">
-        <v>8.655209216185806</v>
+        <v>8.655209222609143</v>
       </c>
       <c r="BK71" t="n">
         <v>5</v>
@@ -35652,10 +35652,10 @@
         <v>2.1</v>
       </c>
       <c r="BN71" t="n">
-        <v>-54.32607457666803</v>
+        <v>-54.32607454277179</v>
       </c>
       <c r="BO71" t="n">
-        <v>-42.6032205555812</v>
+        <v>-42.60322054501716</v>
       </c>
       <c r="BP71" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
       </c>
       <c r="CF71" t="inlineStr">
         <is>
-          <t>Rompimento (vol x6.2, +8.3% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x6.3, +8.3% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -35877,10 +35877,10 @@
         <v>41.70000076293945</v>
       </c>
       <c r="BC72" t="n">
-        <v>9.123429543655545</v>
+        <v>9.123432723708207</v>
       </c>
       <c r="BD72" t="n">
-        <v>16.92396180348103</v>
+        <v>16.92396770247873</v>
       </c>
       <c r="BE72" t="n">
         <v>119.078665971756</v>
@@ -35889,7 +35889,7 @@
         <v>87.55319300258704</v>
       </c>
       <c r="BG72" t="n">
-        <v>162.3336260894977</v>
+        <v>162.3336356844842</v>
       </c>
       <c r="BH72" t="inlineStr"/>
       <c r="BI72" t="inlineStr"/>
@@ -35936,10 +35936,10 @@
         </is>
       </c>
       <c r="BZ72" t="n">
-        <v>43.09999847412109</v>
+        <v>43.31999969482422</v>
       </c>
       <c r="CA72" t="n">
-        <v>-3.248254665304118</v>
+        <v>-3.739609749070061</v>
       </c>
       <c r="CB72" t="n">
         <v>-30.08510558619815</v>
@@ -35955,7 +35955,7 @@
       </c>
       <c r="CF72" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-3.7%))</t>
         </is>
       </c>
     </row>
@@ -36117,10 +36117,10 @@
         <v>29.72999954223633</v>
       </c>
       <c r="BC73" t="n">
-        <v>12.89493640222505</v>
+        <v>12.89530572849013</v>
       </c>
       <c r="BD73" t="n">
-        <v>23.92010702612746</v>
+        <v>23.92079212634919</v>
       </c>
       <c r="BE73" t="n">
         <v>37.02279078333001</v>
@@ -36129,10 +36129,10 @@
         <v>25.83665772834909</v>
       </c>
       <c r="BG73" t="n">
-        <v>43.04383446319062</v>
+        <v>43.04295694009713</v>
       </c>
       <c r="BH73" t="n">
-        <v>28.54366528064445</v>
+        <v>28.54370066132311</v>
       </c>
       <c r="BI73" t="n">
         <v>25.83665772834909</v>
@@ -36153,7 +36153,7 @@
         <v>-21.78610052623948</v>
       </c>
       <c r="BO73" t="n">
-        <v>-3.99036084715203</v>
+        <v>-3.990241840494768</v>
       </c>
       <c r="BP73" t="inlineStr">
         <is>
@@ -36186,10 +36186,10 @@
         </is>
       </c>
       <c r="BZ73" t="n">
-        <v>30.39999961853027</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="CA73" t="n">
-        <v>-2.20394764704388</v>
+        <v>-2.010549134092643</v>
       </c>
       <c r="CB73" t="n">
         <v>-23.41079410625997</v>
@@ -36205,7 +36205,7 @@
       </c>
       <c r="CF73" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -36367,28 +36367,28 @@
         <v>3.470000028610229</v>
       </c>
       <c r="BC74" t="n">
-        <v>2.663573178856252</v>
+        <v>2.663573179221207</v>
       </c>
       <c r="BD74" t="n">
-        <v>3.085953419586554</v>
+        <v>3.08595341970474</v>
       </c>
       <c r="BE74" t="n">
-        <v>3.75374477646637</v>
+        <v>3.753744776095803</v>
       </c>
       <c r="BF74" t="n">
         <v>6.965119785642171</v>
       </c>
       <c r="BG74" t="n">
-        <v>5.64998743979841</v>
+        <v>5.649987439975291</v>
       </c>
       <c r="BH74" t="n">
-        <v>4.423675720069951</v>
+        <v>4.423675720127843</v>
       </c>
       <c r="BI74" t="n">
-        <v>3.75374477646637</v>
+        <v>3.753744776095803</v>
       </c>
       <c r="BJ74" t="n">
-        <v>3.378370298819733</v>
+        <v>3.378370298486223</v>
       </c>
       <c r="BK74" t="n">
         <v>5</v>
@@ -36400,10 +36400,10 @@
         <v>2.6</v>
       </c>
       <c r="BN74" t="n">
-        <v>-2.640626196974283</v>
+        <v>-2.640626206585506</v>
       </c>
       <c r="BO74" t="n">
-        <v>27.48344909500415</v>
+        <v>27.48344909667249</v>
       </c>
       <c r="BP74" t="inlineStr">
         <is>
@@ -36617,10 +36617,10 @@
         <v>9.170000076293945</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.752424108217706</v>
+        <v>1.753115054930721</v>
       </c>
       <c r="BD75" t="n">
-        <v>3.250746720743845</v>
+        <v>3.252028426896487</v>
       </c>
       <c r="BE75" t="n">
         <v>19.22507927387575</v>
@@ -36629,7 +36629,7 @@
         <v>20.82943615071028</v>
       </c>
       <c r="BG75" t="n">
-        <v>16.95076458192487</v>
+        <v>16.95124657935493</v>
       </c>
       <c r="BH75" t="inlineStr"/>
       <c r="BI75" t="inlineStr"/>
@@ -36672,10 +36672,10 @@
         </is>
       </c>
       <c r="BZ75" t="n">
-        <v>10.03999996185303</v>
+        <v>9.710000038146973</v>
       </c>
       <c r="CA75" t="n">
-        <v>-8.665337538492491</v>
+        <v>-5.561276619274647</v>
       </c>
       <c r="CB75" t="n">
         <v>-40.00475990261403</v>
@@ -36691,7 +36691,7 @@
       </c>
       <c r="CF75" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -36853,10 +36853,10 @@
         <v>3.440000057220459</v>
       </c>
       <c r="BC76" t="n">
-        <v>0.8372642180562426</v>
+        <v>0.8373020474611809</v>
       </c>
       <c r="BD76" t="n">
-        <v>1.55312512449433</v>
+        <v>1.55319529804049</v>
       </c>
       <c r="BE76" t="n">
         <v>9.417355528547743</v>
@@ -36865,7 +36865,7 @@
         <v>4.488959679362924</v>
       </c>
       <c r="BG76" t="n">
-        <v>13.08299584939965</v>
+        <v>13.08310527329823</v>
       </c>
       <c r="BH76" t="inlineStr"/>
       <c r="BI76" t="inlineStr"/>
@@ -36908,10 +36908,10 @@
         </is>
       </c>
       <c r="BZ76" t="n">
-        <v>3.670000076293945</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="CA76" t="n">
-        <v>-6.267030362183146</v>
+        <v>-6.010929602486536</v>
       </c>
       <c r="CB76" t="n">
         <v>-52.97215903119552</v>
@@ -36927,7 +36927,7 @@
       </c>
       <c r="CF76" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-6.0%))</t>
         </is>
       </c>
     </row>
@@ -37087,10 +37087,10 @@
         <v>61.93999862670898</v>
       </c>
       <c r="BC77" t="n">
-        <v>45.0485535212121</v>
+        <v>45.04710551264485</v>
       </c>
       <c r="BD77" t="n">
-        <v>65.59069392688482</v>
+        <v>65.5885856264109</v>
       </c>
       <c r="BE77" t="n">
         <v>37.06421091586729</v>
@@ -37100,13 +37100,13 @@
       </c>
       <c r="BG77" t="inlineStr"/>
       <c r="BH77" t="n">
-        <v>47.66826739830245</v>
+        <v>47.66737832104216</v>
       </c>
       <c r="BI77" t="n">
-        <v>44.00908237522884</v>
+        <v>44.00835837094522</v>
       </c>
       <c r="BJ77" t="n">
-        <v>39.60817413770596</v>
+        <v>39.6075225338507</v>
       </c>
       <c r="BK77" t="n">
         <v>4</v>
@@ -37118,10 +37118,10 @@
         <v>1.8</v>
       </c>
       <c r="BN77" t="n">
-        <v>-36.05396348745378</v>
+        <v>-36.05501547949399</v>
       </c>
       <c r="BO77" t="n">
-        <v>-23.04121980114553</v>
+        <v>-23.0426551858404</v>
       </c>
       <c r="BP77" t="inlineStr">
         <is>
@@ -37331,10 +37331,10 @@
         <v>33.91999816894531</v>
       </c>
       <c r="BC78" t="n">
-        <v>9.708250620447918</v>
+        <v>9.70848245768633</v>
       </c>
       <c r="BD78" t="n">
-        <v>18.00880490093089</v>
+        <v>18.00923495900814</v>
       </c>
       <c r="BE78" t="n">
         <v>27.2884016841849</v>
@@ -37343,10 +37343,10 @@
         <v>20.23180672027869</v>
       </c>
       <c r="BG78" t="n">
-        <v>24.60540849899583</v>
+        <v>24.60484769175427</v>
       </c>
       <c r="BH78" t="n">
-        <v>19.96853448496764</v>
+        <v>19.96855470258247</v>
       </c>
       <c r="BI78" t="n">
         <v>20.23180672027869</v>
@@ -37367,7 +37367,7 @@
         <v>-46.31890615807486</v>
       </c>
       <c r="BO78" t="n">
-        <v>-41.13049657163783</v>
+        <v>-41.13043696781733</v>
       </c>
       <c r="BP78" t="inlineStr">
         <is>
@@ -37396,13 +37396,13 @@
         </is>
       </c>
       <c r="BZ78" t="n">
-        <v>35.86999893188477</v>
+        <v>35.77999877929688</v>
       </c>
       <c r="CA78" t="n">
-        <v>-5.436300030681352</v>
+        <v>-5.198436763021363</v>
       </c>
       <c r="CB78" t="n">
-        <v>-24.54173046087656</v>
+        <v>-24.54173690556859</v>
       </c>
       <c r="CC78" t="b">
         <v>0</v>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="CF78" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.2%))</t>
         </is>
       </c>
     </row>
@@ -37577,28 +37577,28 @@
         <v>53.04999923706055</v>
       </c>
       <c r="BC79" t="n">
-        <v>16.20510568840154</v>
+        <v>16.20510571448717</v>
       </c>
       <c r="BD79" t="n">
-        <v>24.67056006408777</v>
+        <v>24.67056007913558</v>
       </c>
       <c r="BE79" t="n">
-        <v>44.54661606467472</v>
+        <v>44.54661602013848</v>
       </c>
       <c r="BF79" t="n">
         <v>61.80687302305529</v>
       </c>
       <c r="BG79" t="n">
-        <v>35.54124215522384</v>
+        <v>35.54124214741591</v>
       </c>
       <c r="BH79" t="n">
-        <v>36.55407939908863</v>
+        <v>36.55407939684649</v>
       </c>
       <c r="BI79" t="n">
-        <v>35.54124215522384</v>
+        <v>35.54124214741591</v>
       </c>
       <c r="BJ79" t="n">
-        <v>31.98711793970146</v>
+        <v>31.98711793267432</v>
       </c>
       <c r="BK79" t="n">
         <v>5</v>
@@ -37610,10 +37610,10 @@
         <v>3.8</v>
       </c>
       <c r="BN79" t="n">
-        <v>-39.70382959524085</v>
+        <v>-39.7038296084871</v>
       </c>
       <c r="BO79" t="n">
-        <v>-31.09504255458674</v>
+        <v>-31.0950425588132</v>
       </c>
       <c r="BP79" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ79" t="n">
@@ -37661,7 +37661,7 @@
       </c>
       <c r="CF79" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-1.2%))</t>
         </is>
       </c>
     </row>
@@ -37786,7 +37786,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>49177673728</v>
+        <v>49176797184</v>
       </c>
       <c r="AQ80" t="n">
         <v>22.15</v>
@@ -37823,10 +37823,10 @@
         <v>25.04999923706055</v>
       </c>
       <c r="BC80" t="n">
-        <v>12.1275111665118</v>
+        <v>12.12707661417643</v>
       </c>
       <c r="BD80" t="n">
-        <v>22.49653321387939</v>
+        <v>22.49572711929728</v>
       </c>
       <c r="BE80" t="n">
         <v>14.98476252329807</v>
@@ -37838,13 +37838,13 @@
         <v>33.92776420369375</v>
       </c>
       <c r="BH80" t="n">
-        <v>21.94332620862896</v>
+        <v>21.94307807924546</v>
       </c>
       <c r="BI80" t="n">
-        <v>22.49653321387939</v>
+        <v>22.49572711929728</v>
       </c>
       <c r="BJ80" t="n">
-        <v>20.24687989249145</v>
+        <v>20.24615440736756</v>
       </c>
       <c r="BK80" t="n">
         <v>5</v>
@@ -37856,10 +37856,10 @@
         <v>2.8</v>
       </c>
       <c r="BN80" t="n">
-        <v>-19.17412970401636</v>
+        <v>-19.17702585230374</v>
       </c>
       <c r="BO80" t="n">
-        <v>-12.40188871477242</v>
+        <v>-12.40287925126364</v>
       </c>
       <c r="BP80" t="inlineStr">
         <is>
@@ -38067,10 +38067,10 @@
         <v>5.679999828338623</v>
       </c>
       <c r="BC81" t="n">
-        <v>3.359240307613577</v>
+        <v>3.359240316814672</v>
       </c>
       <c r="BD81" t="n">
-        <v>4.891053887885368</v>
+        <v>4.891053901282163</v>
       </c>
       <c r="BE81" t="n">
         <v>4.760032088212867</v>
@@ -38080,13 +38080,13 @@
       </c>
       <c r="BG81" t="inlineStr"/>
       <c r="BH81" t="n">
-        <v>5.70067947488144</v>
+        <v>5.700679480530912</v>
       </c>
       <c r="BI81" t="n">
-        <v>4.825542988049118</v>
+        <v>4.825542994747515</v>
       </c>
       <c r="BJ81" t="n">
-        <v>4.342988689244206</v>
+        <v>4.342988695272764</v>
       </c>
       <c r="BK81" t="n">
         <v>4</v>
@@ -38098,10 +38098,10 @@
         <v>2.9</v>
       </c>
       <c r="BN81" t="n">
-        <v>-23.53892921657865</v>
+        <v>-23.53892911044206</v>
       </c>
       <c r="BO81" t="n">
-        <v>0.3640782952077259</v>
+        <v>0.364078394670253</v>
       </c>
       <c r="BP81" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>45849899008</v>
+        <v>45855367168</v>
       </c>
       <c r="AQ82" t="n">
         <v>12.96</v>
@@ -38366,10 +38366,10 @@
         </is>
       </c>
       <c r="BZ82" t="n">
-        <v>60.54000091552734</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="CA82" t="n">
-        <v>-5.104063603995368</v>
+        <v>-5.587506649860686</v>
       </c>
       <c r="CB82" t="n">
         <v>-21.27980526122939</v>
@@ -38385,7 +38385,7 @@
       </c>
       <c r="CF82" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.1%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -38547,10 +38547,10 @@
         <v>31.28000068664551</v>
       </c>
       <c r="BC83" t="n">
-        <v>9.873499916241256</v>
+        <v>9.873499907920982</v>
       </c>
       <c r="BD83" t="n">
-        <v>18.31534234462753</v>
+        <v>18.31534232919342</v>
       </c>
       <c r="BE83" t="n">
         <v>35.57596644618479</v>
@@ -38559,16 +38559,16 @@
         <v>29.8556904910544</v>
       </c>
       <c r="BG83" t="n">
-        <v>35.56105595600039</v>
+        <v>35.56105596719019</v>
       </c>
       <c r="BH83" t="n">
-        <v>29.82701380946678</v>
+        <v>29.8270138084057</v>
       </c>
       <c r="BI83" t="n">
-        <v>32.7083732235274</v>
+        <v>32.7083732291223</v>
       </c>
       <c r="BJ83" t="n">
-        <v>29.43753590117466</v>
+        <v>29.43753590621007</v>
       </c>
       <c r="BK83" t="n">
         <v>4</v>
@@ -38580,10 +38580,10 @@
         <v>3.6</v>
       </c>
       <c r="BN83" t="n">
-        <v>-5.89023256082426</v>
+        <v>-5.890232544726404</v>
       </c>
       <c r="BO83" t="n">
-        <v>-4.64509861024095</v>
+        <v>-4.645098613633136</v>
       </c>
       <c r="BP83" t="inlineStr">
         <is>
@@ -38793,19 +38793,19 @@
         <v>2.220000028610229</v>
       </c>
       <c r="BC84" t="n">
-        <v>0.6362721929965078</v>
+        <v>0.6363302793646299</v>
       </c>
       <c r="BD84" t="n">
-        <v>0.8862434466233294</v>
+        <v>0.8863127917719272</v>
       </c>
       <c r="BE84" t="n">
-        <v>3.238550419861193</v>
+        <v>3.238508175096705</v>
       </c>
       <c r="BF84" t="n">
         <v>6.91532496435787</v>
       </c>
       <c r="BG84" t="n">
-        <v>2.474119964122096</v>
+        <v>2.474199030468747</v>
       </c>
       <c r="BH84" t="inlineStr"/>
       <c r="BI84" t="inlineStr"/>
@@ -39029,28 +39029,28 @@
         <v>26.94000053405762</v>
       </c>
       <c r="BC85" t="n">
-        <v>11.71492734886927</v>
+        <v>11.71574511120483</v>
       </c>
       <c r="BD85" t="n">
-        <v>12.56643079297564</v>
+        <v>12.56682340287455</v>
       </c>
       <c r="BE85" t="n">
-        <v>14.20614666986956</v>
+        <v>14.20559888495571</v>
       </c>
       <c r="BF85" t="n">
         <v>32.56140373822206</v>
       </c>
       <c r="BG85" t="n">
-        <v>12.84342834602552</v>
+        <v>12.84338396094762</v>
       </c>
       <c r="BH85" t="n">
-        <v>12.832733289435</v>
+        <v>12.83288783999568</v>
       </c>
       <c r="BI85" t="n">
-        <v>12.70492956950058</v>
+        <v>12.70510368191109</v>
       </c>
       <c r="BJ85" t="n">
-        <v>11.43443661255052</v>
+        <v>11.43459331371998</v>
       </c>
       <c r="BK85" t="n">
         <v>4</v>
@@ -39062,10 +39062,10 @@
         <v>2.8</v>
       </c>
       <c r="BN85" t="n">
-        <v>-57.55591541991591</v>
+        <v>-57.55533375263175</v>
       </c>
       <c r="BO85" t="n">
-        <v>-52.36550469547384</v>
+        <v>-52.36493101114714</v>
       </c>
       <c r="BP85" t="inlineStr">
         <is>
@@ -39275,10 +39275,10 @@
         <v>6.630000114440918</v>
       </c>
       <c r="BC86" t="n">
-        <v>1.186697225857237</v>
+        <v>1.187139645634204</v>
       </c>
       <c r="BD86" t="n">
-        <v>2.201323353965174</v>
+        <v>2.202144042651447</v>
       </c>
       <c r="BE86" t="n">
         <v>10.39615402560262</v>
@@ -39287,7 +39287,7 @@
         <v>10.22274267960574</v>
       </c>
       <c r="BG86" t="n">
-        <v>10.17951058653554</v>
+        <v>10.17942104286698</v>
       </c>
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr"/>
@@ -39509,10 +39509,10 @@
         <v>74.97000122070312</v>
       </c>
       <c r="BC87" t="n">
-        <v>68.17661969165397</v>
+        <v>68.17661962985244</v>
       </c>
       <c r="BD87" t="n">
-        <v>99.26515827104818</v>
+        <v>99.26515818106516</v>
       </c>
       <c r="BE87" t="n">
         <v>24.28934618988512</v>
@@ -39522,13 +39522,13 @@
       </c>
       <c r="BG87" t="inlineStr"/>
       <c r="BH87" t="n">
-        <v>60.00321591164024</v>
+        <v>60.0032158736941</v>
       </c>
       <c r="BI87" t="n">
-        <v>58.22917959281384</v>
+        <v>58.22917956191307</v>
       </c>
       <c r="BJ87" t="n">
-        <v>52.40626163353245</v>
+        <v>52.40626160572177</v>
       </c>
       <c r="BK87" t="n">
         <v>4</v>
@@ -39540,10 +39540,10 @@
         <v>4.1</v>
       </c>
       <c r="BN87" t="n">
-        <v>-30.0970244361416</v>
+        <v>-30.09702447323734</v>
       </c>
       <c r="BO87" t="n">
-        <v>-19.9636989000472</v>
+        <v>-19.9636989506623</v>
       </c>
       <c r="BP87" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
       <c r="BX87" t="inlineStr"/>
       <c r="BY87" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ87" t="n">
@@ -39591,7 +39591,7 @@
       </c>
       <c r="CF87" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.2%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-2.2%))</t>
         </is>
       </c>
     </row>
@@ -39753,10 +39753,10 @@
         <v>11.63000011444092</v>
       </c>
       <c r="BC88" t="n">
-        <v>1.919229596320884</v>
+        <v>1.919229595656136</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.560170901175239</v>
+        <v>3.560170899942133</v>
       </c>
       <c r="BE88" t="n">
         <v>11.63878410244276</v>
@@ -39765,10 +39765,10 @@
         <v>10.41259687716942</v>
       </c>
       <c r="BG88" t="n">
-        <v>11.80299456100769</v>
+        <v>11.80299456179661</v>
       </c>
       <c r="BH88" t="n">
-        <v>11.28479184687329</v>
+        <v>11.28479184713626</v>
       </c>
       <c r="BI88" t="n">
         <v>11.63878410244276</v>
@@ -39789,7 +39789,7 @@
         <v>-9.932024169184306</v>
       </c>
       <c r="BO88" t="n">
-        <v>-2.968256785646828</v>
+        <v>-2.968256783385681</v>
       </c>
       <c r="BP88" t="inlineStr">
         <is>
@@ -39999,10 +39999,10 @@
         <v>37.81999969482422</v>
       </c>
       <c r="BC89" t="n">
-        <v>9.336898885380197</v>
+        <v>9.338144147594409</v>
       </c>
       <c r="BD89" t="n">
-        <v>17.31994743238026</v>
+        <v>17.32225739378763</v>
       </c>
       <c r="BE89" t="n">
         <v>40.347423184897</v>
@@ -40011,16 +40011,16 @@
         <v>40.62582149389188</v>
       </c>
       <c r="BG89" t="n">
-        <v>32.47464841349172</v>
+        <v>32.47385021805864</v>
       </c>
       <c r="BH89" t="n">
-        <v>32.69196013116522</v>
+        <v>32.69233807265879</v>
       </c>
       <c r="BI89" t="n">
-        <v>36.41103579919437</v>
+        <v>36.41063670147782</v>
       </c>
       <c r="BJ89" t="n">
-        <v>32.76993221927493</v>
+        <v>32.76957303133004</v>
       </c>
       <c r="BK89" t="n">
         <v>4</v>
@@ -40032,10 +40032,10 @@
         <v>4.4</v>
       </c>
       <c r="BN89" t="n">
-        <v>-13.35290194685117</v>
+        <v>-13.35385167701454</v>
       </c>
       <c r="BO89" t="n">
-        <v>-13.55906823119511</v>
+        <v>-13.55806891470486</v>
       </c>
       <c r="BP89" t="inlineStr">
         <is>
@@ -40239,28 +40239,28 @@
         <v>20.05999946594238</v>
       </c>
       <c r="BC90" t="n">
-        <v>11.952026122112</v>
+        <v>11.95216867008045</v>
       </c>
       <c r="BD90" t="n">
-        <v>15.01776554745805</v>
+        <v>15.01785515292355</v>
       </c>
       <c r="BE90" t="n">
-        <v>22.53304523009587</v>
+        <v>22.53291093368629</v>
       </c>
       <c r="BF90" t="n">
         <v>42.75165598391471</v>
       </c>
       <c r="BG90" t="n">
-        <v>27.39822725810817</v>
+        <v>27.39832316298976</v>
       </c>
       <c r="BH90" t="n">
-        <v>16.50094563322197</v>
+        <v>16.5009782522301</v>
       </c>
       <c r="BI90" t="n">
-        <v>15.01776554745805</v>
+        <v>15.01785515292355</v>
       </c>
       <c r="BJ90" t="n">
-        <v>13.51598899271224</v>
+        <v>13.5160696376312</v>
       </c>
       <c r="BK90" t="n">
         <v>3</v>
@@ -40272,10 +40272,10 @@
         <v>1.9</v>
       </c>
       <c r="BN90" t="n">
-        <v>-32.62218667722539</v>
+        <v>-32.62178465867554</v>
       </c>
       <c r="BO90" t="n">
-        <v>-17.7420435068452</v>
+        <v>-17.74188089962189</v>
       </c>
       <c r="BP90" t="inlineStr">
         <is>
@@ -40304,10 +40304,10 @@
         </is>
       </c>
       <c r="BZ90" t="n">
-        <v>21.27000045776367</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="CA90" t="n">
-        <v>-5.688768057264582</v>
+        <v>-6.042158746971138</v>
       </c>
       <c r="CB90" t="n">
         <v>-27.1670659463897</v>
@@ -40323,7 +40323,7 @@
       </c>
       <c r="CF90" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.7%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.0%))</t>
         </is>
       </c>
     </row>
@@ -40485,28 +40485,28 @@
         <v>2.190000057220459</v>
       </c>
       <c r="BC91" t="n">
-        <v>1.003186596366215</v>
+        <v>1.003486603087723</v>
       </c>
       <c r="BD91" t="n">
-        <v>1.348225633975072</v>
+        <v>1.348530487980586</v>
       </c>
       <c r="BE91" t="n">
-        <v>3.190153167786096</v>
+        <v>3.189920551461575</v>
       </c>
       <c r="BF91" t="n">
         <v>6.652606195414778</v>
       </c>
       <c r="BG91" t="n">
-        <v>3.209541446177239</v>
+        <v>3.209942744454935</v>
       </c>
       <c r="BH91" t="n">
-        <v>3.600131610838296</v>
+        <v>3.600249994827969</v>
       </c>
       <c r="BI91" t="n">
-        <v>3.199847306981668</v>
+        <v>3.199931647958255</v>
       </c>
       <c r="BJ91" t="n">
-        <v>2.879862576283501</v>
+        <v>2.87993848316243</v>
       </c>
       <c r="BK91" t="n">
         <v>4</v>
@@ -40518,10 +40518,10 @@
         <v>6.6</v>
       </c>
       <c r="BN91" t="n">
-        <v>31.50057082366533</v>
+        <v>31.50403689110577</v>
       </c>
       <c r="BO91" t="n">
-        <v>64.38956697597405</v>
+        <v>64.39497263746168</v>
       </c>
       <c r="BP91" t="inlineStr">
         <is>
@@ -40733,10 +40733,10 @@
         <v>21.35000038146973</v>
       </c>
       <c r="BC92" t="n">
-        <v>36.75204853365867</v>
+        <v>36.75204869890671</v>
       </c>
       <c r="BD92" t="n">
-        <v>68.17505002993683</v>
+        <v>68.17505033647194</v>
       </c>
       <c r="BE92" t="n">
         <v>26.36416636108796</v>
@@ -40748,13 +40748,13 @@
         <v>59.69245213831237</v>
       </c>
       <c r="BH92" t="n">
-        <v>44.17435086991453</v>
+        <v>44.17435096427117</v>
       </c>
       <c r="BI92" t="n">
-        <v>36.75204853365867</v>
+        <v>36.75204869890671</v>
       </c>
       <c r="BJ92" t="n">
-        <v>33.0768436802928</v>
+        <v>33.07684382901604</v>
       </c>
       <c r="BK92" t="n">
         <v>5</v>
@@ -40766,10 +40766,10 @@
         <v>2.6</v>
       </c>
       <c r="BN92" t="n">
-        <v>54.92666552362753</v>
+        <v>54.92666622022347</v>
       </c>
       <c r="BO92" t="n">
-        <v>106.9056209865678</v>
+        <v>106.9056214285193</v>
       </c>
       <c r="BP92" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
       <c r="BX92" t="inlineStr"/>
       <c r="BY92" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ92" t="n">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="CF92" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-3.0%))</t>
         </is>
       </c>
     </row>
@@ -40979,10 +40979,10 @@
         <v>8.239999771118164</v>
       </c>
       <c r="BC93" t="n">
-        <v>0.4891813438895788</v>
+        <v>0.4891897073671276</v>
       </c>
       <c r="BD93" t="n">
-        <v>0.9074313929151686</v>
+        <v>0.9074469071660217</v>
       </c>
       <c r="BE93" t="n">
         <v>9.436473376604637</v>
@@ -40991,7 +40991,7 @@
         <v>8.661546580675868</v>
       </c>
       <c r="BG93" t="n">
-        <v>10.38261860614533</v>
+        <v>10.38261091698093</v>
       </c>
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="inlineStr"/>
@@ -41217,10 +41217,10 @@
         <v>4</v>
       </c>
       <c r="BC94" t="n">
-        <v>37.13794589100621</v>
+        <v>37.13794598882896</v>
       </c>
       <c r="BD94" t="n">
-        <v>68.89088962781652</v>
+        <v>68.89088980927771</v>
       </c>
       <c r="BE94" t="n">
         <v>5.692803437164339</v>
@@ -41453,10 +41453,10 @@
         <v>20.21999931335449</v>
       </c>
       <c r="BC95" t="n">
-        <v>2.083209347908416</v>
+        <v>2.08320934801593</v>
       </c>
       <c r="BD95" t="n">
-        <v>3.864353340370112</v>
+        <v>3.864353340569551</v>
       </c>
       <c r="BE95" t="n">
         <v>10.14829510992223</v>
@@ -41465,16 +41465,16 @@
         <v>8.467443306015236</v>
       </c>
       <c r="BG95" t="n">
-        <v>9.835854341457441</v>
+        <v>9.835854341237349</v>
       </c>
       <c r="BH95" t="n">
-        <v>8.078986524441255</v>
+        <v>8.078986524436093</v>
       </c>
       <c r="BI95" t="n">
-        <v>9.151648823736338</v>
+        <v>9.151648823626292</v>
       </c>
       <c r="BJ95" t="n">
-        <v>8.236483941362705</v>
+        <v>8.236483941263664</v>
       </c>
       <c r="BK95" t="n">
         <v>4</v>
@@ -41486,10 +41486,10 @@
         <v>4.9</v>
       </c>
       <c r="BN95" t="n">
-        <v>-59.26565667129948</v>
+        <v>-59.2656566717893</v>
       </c>
       <c r="BO95" t="n">
-        <v>-60.04457567362324</v>
+        <v>-60.04457567364876</v>
       </c>
       <c r="BP95" t="inlineStr">
         <is>
@@ -41701,22 +41701,22 @@
         <v>7.150000095367432</v>
       </c>
       <c r="BC96" t="n">
-        <v>3.163893194554441</v>
+        <v>3.163893186398491</v>
       </c>
       <c r="BD96" t="n">
-        <v>5.869021875898488</v>
+        <v>5.8690218607692</v>
       </c>
       <c r="BE96" t="inlineStr"/>
       <c r="BF96" t="inlineStr"/>
       <c r="BG96" t="inlineStr"/>
       <c r="BH96" t="n">
-        <v>4.516457535226465</v>
+        <v>4.516457523583846</v>
       </c>
       <c r="BI96" t="n">
-        <v>4.516457535226465</v>
+        <v>4.516457523583846</v>
       </c>
       <c r="BJ96" t="n">
-        <v>4.064811781703819</v>
+        <v>4.064811771225461</v>
       </c>
       <c r="BK96" t="n">
         <v>2</v>
@@ -41728,10 +41728,10 @@
         <v>1.9</v>
       </c>
       <c r="BN96" t="n">
-        <v>-43.14948632885392</v>
+        <v>-43.14948647540439</v>
       </c>
       <c r="BO96" t="n">
-        <v>-36.83276258761548</v>
+        <v>-36.83276275044932</v>
       </c>
       <c r="BP96" t="inlineStr">
         <is>
@@ -41939,10 +41939,10 @@
         <v>8.22559642791748</v>
       </c>
       <c r="BC97" t="n">
-        <v>5.243573547892507</v>
+        <v>5.243573535580507</v>
       </c>
       <c r="BD97" t="n">
-        <v>7.63464308573149</v>
+        <v>7.634643067805218</v>
       </c>
       <c r="BE97" t="n">
         <v>5.815513450057225</v>
@@ -41952,13 +41952,13 @@
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="n">
-        <v>6.878726586577839</v>
+        <v>6.878726579018271</v>
       </c>
       <c r="BI97" t="n">
-        <v>6.725078267894357</v>
+        <v>6.725078258931221</v>
       </c>
       <c r="BJ97" t="n">
-        <v>6.052570441104922</v>
+        <v>6.052570433038099</v>
       </c>
       <c r="BK97" t="n">
         <v>4</v>
@@ -41970,10 +41970,10 @@
         <v>1.7</v>
       </c>
       <c r="BN97" t="n">
-        <v>-26.41785317156285</v>
+        <v>-26.41785326963261</v>
       </c>
       <c r="BO97" t="n">
-        <v>-16.37412986574927</v>
+        <v>-16.37412995765225</v>
       </c>
       <c r="BP97" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>-1.900233342235125</v>
       </c>
       <c r="CB97" t="n">
-        <v>-15.22972898400896</v>
+        <v>-15.22972048460036</v>
       </c>
       <c r="CC97" t="b">
         <v>0</v>
@@ -42175,22 +42175,22 @@
         <v>52.13999938964844</v>
       </c>
       <c r="BC98" t="n">
-        <v>10.89711111179947</v>
+        <v>10.89431736590257</v>
       </c>
       <c r="BD98" t="n">
-        <v>15.86619377878004</v>
+        <v>15.86212608475414</v>
       </c>
       <c r="BE98" t="inlineStr"/>
       <c r="BF98" t="inlineStr"/>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="n">
-        <v>13.38165244528975</v>
+        <v>13.37822172532836</v>
       </c>
       <c r="BI98" t="n">
-        <v>13.38165244528975</v>
+        <v>13.37822172532836</v>
       </c>
       <c r="BJ98" t="n">
-        <v>12.04348720076078</v>
+        <v>12.04039955279552</v>
       </c>
       <c r="BK98" t="n">
         <v>2</v>
@@ -42202,10 +42202,10 @@
         <v>1.5</v>
       </c>
       <c r="BN98" t="n">
-        <v>-76.90163532462215</v>
+        <v>-76.90755716582163</v>
       </c>
       <c r="BO98" t="n">
-        <v>-74.33515036069129</v>
+        <v>-74.34173018424625</v>
       </c>
       <c r="BP98" t="inlineStr">
         <is>
@@ -42234,10 +42234,10 @@
         </is>
       </c>
       <c r="BZ98" t="n">
-        <v>57.45000076293945</v>
+        <v>57</v>
       </c>
       <c r="CA98" t="n">
-        <v>-9.242822111007619</v>
+        <v>-8.526316860265904</v>
       </c>
       <c r="CB98" t="n">
         <v>-19.44250955845246</v>
@@ -42253,7 +42253,7 @@
       </c>
       <c r="CF98" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-9.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
         </is>
       </c>
     </row>
@@ -42415,10 +42415,10 @@
         <v>3.079999923706055</v>
       </c>
       <c r="BC99" t="n">
-        <v>0.6432281168215788</v>
+        <v>0.643228117716575</v>
       </c>
       <c r="BD99" t="n">
-        <v>1.193188156704029</v>
+        <v>1.193188158364247</v>
       </c>
       <c r="BE99" t="n">
         <v>3.334150244207942</v>
@@ -42427,16 +42427,16 @@
         <v>3.479926007973857</v>
       </c>
       <c r="BG99" t="n">
-        <v>2.64400237792748</v>
+        <v>2.644002377471382</v>
       </c>
       <c r="BH99" t="n">
-        <v>2.662816696703327</v>
+        <v>2.662816697004357</v>
       </c>
       <c r="BI99" t="n">
-        <v>2.989076311067711</v>
+        <v>2.989076310839662</v>
       </c>
       <c r="BJ99" t="n">
-        <v>2.69016867996094</v>
+        <v>2.690168679755696</v>
       </c>
       <c r="BK99" t="n">
         <v>4</v>
@@ -42448,10 +42448,10 @@
         <v>5.4</v>
       </c>
       <c r="BN99" t="n">
-        <v>-12.65685887667311</v>
+        <v>-12.65685888333687</v>
       </c>
       <c r="BO99" t="n">
-        <v>-13.54491030313878</v>
+        <v>-13.54491029336508</v>
       </c>
       <c r="BP99" t="inlineStr">
         <is>
@@ -42661,10 +42661,10 @@
         <v>12.14000034332275</v>
       </c>
       <c r="BC100" t="n">
-        <v>2.155377409415664</v>
+        <v>2.155626246661114</v>
       </c>
       <c r="BD100" t="n">
-        <v>3.998225094466057</v>
+        <v>3.998686687556367</v>
       </c>
       <c r="BE100" t="n">
         <v>12.13084498861436</v>
@@ -42673,16 +42673,16 @@
         <v>13.41315044972623</v>
       </c>
       <c r="BG100" t="n">
-        <v>8.689690943504676</v>
+        <v>8.689589618704805</v>
       </c>
       <c r="BH100" t="n">
-        <v>9.557977869077831</v>
+        <v>9.55806793615044</v>
       </c>
       <c r="BI100" t="n">
-        <v>10.41026796605952</v>
+        <v>10.41021730365958</v>
       </c>
       <c r="BJ100" t="n">
-        <v>9.369241169453568</v>
+        <v>9.369195573293625</v>
       </c>
       <c r="BK100" t="n">
         <v>4</v>
@@ -42694,10 +42694,10 @@
         <v>6.2</v>
       </c>
       <c r="BN100" t="n">
-        <v>-22.82338628921999</v>
+        <v>-22.82376187537035</v>
       </c>
       <c r="BO100" t="n">
-        <v>-21.26871829674278</v>
+        <v>-21.26797639336501</v>
       </c>
       <c r="BP100" t="inlineStr">
         <is>
@@ -42905,10 +42905,10 @@
         <v>60.13999938964844</v>
       </c>
       <c r="BC101" t="n">
-        <v>73.44933954923683</v>
+        <v>73.44933900546151</v>
       </c>
       <c r="BD101" t="n">
-        <v>106.9422383836888</v>
+        <v>106.942237591952</v>
       </c>
       <c r="BE101" t="n">
         <v>24.49886383283759</v>
@@ -42918,13 +42918,13 @@
       </c>
       <c r="BG101" t="inlineStr"/>
       <c r="BH101" t="n">
-        <v>58.86610727828198</v>
+        <v>58.86610694440393</v>
       </c>
       <c r="BI101" t="n">
-        <v>52.01166344830074</v>
+        <v>52.01166317641308</v>
       </c>
       <c r="BJ101" t="n">
-        <v>46.81049710347067</v>
+        <v>46.81049685877177</v>
       </c>
       <c r="BK101" t="n">
         <v>4</v>
@@ -42936,10 +42936,10 @@
         <v>4.4</v>
       </c>
       <c r="BN101" t="n">
-        <v>-22.16412108655941</v>
+        <v>-22.16412149344151</v>
       </c>
       <c r="BO101" t="n">
-        <v>-2.118211048046215</v>
+        <v>-2.118211603214237</v>
       </c>
       <c r="BP101" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>3112041728</v>
+        <v>3136304384</v>
       </c>
       <c r="AQ102" t="n">
         <v>8.56</v>
@@ -43149,28 +43149,28 @@
         <v>7.760000228881836</v>
       </c>
       <c r="BC102" t="n">
-        <v>3.226800467093813</v>
+        <v>3.226800469803481</v>
       </c>
       <c r="BD102" t="n">
-        <v>5.969639563835806</v>
+        <v>5.969639564854945</v>
       </c>
       <c r="BE102" t="n">
-        <v>11.97942388848818</v>
+        <v>11.97942388047373</v>
       </c>
       <c r="BF102" t="n">
         <v>12.4570734425344</v>
       </c>
       <c r="BG102" t="n">
-        <v>10.69857440710086</v>
+        <v>10.69857440701067</v>
       </c>
       <c r="BH102" t="n">
-        <v>10.27617782548981</v>
+        <v>10.27617782371843</v>
       </c>
       <c r="BI102" t="n">
-        <v>11.33899914779452</v>
+        <v>11.3389991437422</v>
       </c>
       <c r="BJ102" t="n">
-        <v>10.20509923301507</v>
+        <v>10.20509922936798</v>
       </c>
       <c r="BK102" t="n">
         <v>4</v>
@@ -43182,10 +43182,10 @@
         <v>3.9</v>
       </c>
       <c r="BN102" t="n">
-        <v>31.50900685586133</v>
+        <v>31.50900680886273</v>
       </c>
       <c r="BO102" t="n">
-        <v>32.4249680720762</v>
+        <v>32.42496804924917</v>
       </c>
       <c r="BP102" t="inlineStr">
         <is>
@@ -43395,28 +43395,28 @@
         <v>34.22999954223633</v>
       </c>
       <c r="BC103" t="n">
-        <v>14.8366535314814</v>
+        <v>14.83510670892156</v>
       </c>
       <c r="BD103" t="n">
-        <v>18.29137994733058</v>
+        <v>18.29156544632415</v>
       </c>
       <c r="BE103" t="n">
-        <v>22.08293134117086</v>
+        <v>22.08545785151941</v>
       </c>
       <c r="BF103" t="n">
         <v>31.96692960002474</v>
       </c>
       <c r="BG103" t="n">
-        <v>21.17173612903934</v>
+        <v>21.17314460220294</v>
       </c>
       <c r="BH103" t="n">
-        <v>21.66992610980938</v>
+        <v>21.67044084179856</v>
       </c>
       <c r="BI103" t="n">
-        <v>21.17173612903934</v>
+        <v>21.17314460220294</v>
       </c>
       <c r="BJ103" t="n">
-        <v>19.05456251613541</v>
+        <v>19.05583014198265</v>
       </c>
       <c r="BK103" t="n">
         <v>5</v>
@@ -43428,10 +43428,10 @@
         <v>2.2</v>
       </c>
       <c r="BN103" t="n">
-        <v>-44.33373423618069</v>
+        <v>-44.33003097627945</v>
       </c>
       <c r="BO103" t="n">
-        <v>-36.69317440956753</v>
+        <v>-36.69167066432635</v>
       </c>
       <c r="BP103" t="inlineStr">
         <is>
@@ -43641,10 +43641,10 @@
         <v>11.39999961853027</v>
       </c>
       <c r="BC104" t="n">
-        <v>0.7705148179367457</v>
+        <v>0.7708221385151649</v>
       </c>
       <c r="BD104" t="n">
-        <v>1.429304987272663</v>
+        <v>1.429875066945631</v>
       </c>
       <c r="BE104" t="n">
         <v>18.85767727160126</v>
@@ -43653,7 +43653,7 @@
         <v>17.44171616518078</v>
       </c>
       <c r="BG104" t="n">
-        <v>20.98487588956752</v>
+        <v>20.98477066768226</v>
       </c>
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr"/>
@@ -43877,28 +43877,28 @@
         <v>20.42000007629395</v>
       </c>
       <c r="BC105" t="n">
-        <v>4.472687242346933</v>
+        <v>4.472773713025131</v>
       </c>
       <c r="BD105" t="n">
-        <v>6.003375190199261</v>
+        <v>6.003404388197215</v>
       </c>
       <c r="BE105" t="n">
-        <v>8.662559286695522</v>
+        <v>8.662433946640117</v>
       </c>
       <c r="BF105" t="n">
         <v>13.2070037248429</v>
       </c>
       <c r="BG105" t="n">
-        <v>5.691330051236234</v>
+        <v>5.691256142069284</v>
       </c>
       <c r="BH105" t="n">
-        <v>7.607391099064171</v>
+        <v>7.607374382954928</v>
       </c>
       <c r="BI105" t="n">
-        <v>6.003375190199261</v>
+        <v>6.003404388197215</v>
       </c>
       <c r="BJ105" t="n">
-        <v>5.403037671179335</v>
+        <v>5.403063949377493</v>
       </c>
       <c r="BK105" t="n">
         <v>5</v>
@@ -43910,10 +43910,10 @@
         <v>3</v>
       </c>
       <c r="BN105" t="n">
-        <v>-73.54046204215324</v>
+        <v>-73.54033335362209</v>
       </c>
       <c r="BO105" t="n">
-        <v>-62.74539142683076</v>
+        <v>-62.74547328828609</v>
       </c>
       <c r="BP105" t="inlineStr">
         <is>
@@ -43942,14 +43942,14 @@
       <c r="BX105" t="inlineStr"/>
       <c r="BY105" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="BZ105" t="n">
-        <v>21.07999992370605</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="CA105" t="n">
-        <v>-3.13092907875151</v>
+        <v>-3.542749160590919</v>
       </c>
       <c r="CB105" t="n">
         <v>-18.72166979656401</v>
@@ -44127,10 +44127,10 @@
         <v>11.11999988555908</v>
       </c>
       <c r="BC106" t="n">
-        <v>2.417292182682204</v>
+        <v>2.417235751125468</v>
       </c>
       <c r="BD106" t="n">
-        <v>4.484076998875488</v>
+        <v>4.483972318337742</v>
       </c>
       <c r="BE106" t="n">
         <v>12.16680416875787</v>
@@ -44139,16 +44139,16 @@
         <v>12.67523300337769</v>
       </c>
       <c r="BG106" t="n">
-        <v>9.642331615971051</v>
+        <v>9.642359681113044</v>
       </c>
       <c r="BH106" t="n">
-        <v>9.742111446745525</v>
+        <v>9.742092292896587</v>
       </c>
       <c r="BI106" t="n">
-        <v>10.90456789236446</v>
+        <v>10.90458192493546</v>
       </c>
       <c r="BJ106" t="n">
-        <v>9.814111103128015</v>
+        <v>9.814123732441912</v>
       </c>
       <c r="BK106" t="n">
         <v>4</v>
@@ -44160,10 +44160,10 @@
         <v>5.2</v>
       </c>
       <c r="BN106" t="n">
-        <v>-11.74360427941147</v>
+        <v>-11.74349070644361</v>
       </c>
       <c r="BO106" t="n">
-        <v>-12.39108321037793</v>
+        <v>-12.39125545722268</v>
       </c>
       <c r="BP106" t="inlineStr">
         <is>
@@ -44373,28 +44373,28 @@
         <v>46.88000106811523</v>
       </c>
       <c r="BC107" t="n">
-        <v>18.41240329675697</v>
+        <v>18.41240337661643</v>
       </c>
       <c r="BD107" t="n">
-        <v>20.23641364450597</v>
+        <v>20.23641368110842</v>
       </c>
       <c r="BE107" t="n">
-        <v>23.6370913609206</v>
+        <v>23.6370913011537</v>
       </c>
       <c r="BF107" t="n">
         <v>51.23206727362304</v>
       </c>
       <c r="BG107" t="n">
-        <v>19.92594600447957</v>
+        <v>19.92594598930348</v>
       </c>
       <c r="BH107" t="n">
-        <v>20.55296357666578</v>
+        <v>20.55296358704551</v>
       </c>
       <c r="BI107" t="n">
-        <v>20.08117982449277</v>
+        <v>20.08117983520595</v>
       </c>
       <c r="BJ107" t="n">
-        <v>18.07306184204349</v>
+        <v>18.07306185168536</v>
       </c>
       <c r="BK107" t="n">
         <v>4</v>
@@ -44406,10 +44406,10 @@
         <v>2.8</v>
       </c>
       <c r="BN107" t="n">
-        <v>-61.44824780233287</v>
+        <v>-61.44824778176574</v>
       </c>
       <c r="BO107" t="n">
-        <v>-56.15835514422677</v>
+        <v>-56.1583551220857</v>
       </c>
       <c r="BP107" t="inlineStr">
         <is>
@@ -44619,10 +44619,10 @@
         <v>3.529999971389771</v>
       </c>
       <c r="BC108" t="n">
-        <v>1.735493823820014</v>
+        <v>1.735493824214105</v>
       </c>
       <c r="BD108" t="n">
-        <v>2.420346386604373</v>
+        <v>2.420346387153979</v>
       </c>
       <c r="BE108" t="n">
         <v>0.6905779749455787</v>
@@ -44631,16 +44631,16 @@
         <v>4.148076663330195</v>
       </c>
       <c r="BG108" t="n">
-        <v>0.7267265009914252</v>
+        <v>0.7267265010997772</v>
       </c>
       <c r="BH108" t="n">
-        <v>2.257660843686502</v>
+        <v>2.257660843949515</v>
       </c>
       <c r="BI108" t="n">
-        <v>2.077920105212193</v>
+        <v>2.077920105684043</v>
       </c>
       <c r="BJ108" t="n">
-        <v>1.870128094690974</v>
+        <v>1.870128095115638</v>
       </c>
       <c r="BK108" t="n">
         <v>4</v>
@@ -44652,10 +44652,10 @@
         <v>6</v>
       </c>
       <c r="BN108" t="n">
-        <v>-47.02186657653995</v>
+        <v>-47.02186656450979</v>
       </c>
       <c r="BO108" t="n">
-        <v>-36.04360164349648</v>
+        <v>-36.04360163604569</v>
       </c>
       <c r="BP108" t="inlineStr">
         <is>
@@ -44865,10 +44865,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="BC109" t="n">
-        <v>1.473661931029555</v>
+        <v>1.47366192878088</v>
       </c>
       <c r="BD109" t="n">
-        <v>2.733642882059824</v>
+        <v>2.733642877888531</v>
       </c>
       <c r="BE109" t="n">
         <v>2.302669853840059</v>
@@ -44880,13 +44880,13 @@
         <v>5.213592121902022</v>
       </c>
       <c r="BH109" t="n">
-        <v>3.558602043766038</v>
+        <v>3.558602042482045</v>
       </c>
       <c r="BI109" t="n">
-        <v>2.733642882059824</v>
+        <v>2.733642877888531</v>
       </c>
       <c r="BJ109" t="n">
-        <v>2.460278593853842</v>
+        <v>2.460278590099678</v>
       </c>
       <c r="BK109" t="n">
         <v>5</v>
@@ -44898,10 +44898,10 @@
         <v>4.1</v>
       </c>
       <c r="BN109" t="n">
-        <v>-54.18475519021921</v>
+        <v>-54.18475526012914</v>
       </c>
       <c r="BO109" t="n">
-        <v>-33.73180410420913</v>
+        <v>-33.73180412811963</v>
       </c>
       <c r="BP109" t="inlineStr">
         <is>
@@ -45109,10 +45109,10 @@
         <v>13.22000026702881</v>
       </c>
       <c r="BC110" t="n">
-        <v>6.656747185849022</v>
+        <v>6.656747174168085</v>
       </c>
       <c r="BD110" t="n">
-        <v>9.692223902596176</v>
+        <v>9.692223885588733</v>
       </c>
       <c r="BE110" t="n">
         <v>6.756167212633886</v>
@@ -45122,13 +45122,13 @@
       </c>
       <c r="BG110" t="inlineStr"/>
       <c r="BH110" t="n">
-        <v>8.897111486495477</v>
+        <v>8.897111479323382</v>
       </c>
       <c r="BI110" t="n">
-        <v>8.224195557615031</v>
+        <v>8.224195549111309</v>
       </c>
       <c r="BJ110" t="n">
-        <v>7.401776001853529</v>
+        <v>7.401775994200179</v>
       </c>
       <c r="BK110" t="n">
         <v>4</v>
@@ -45140,10 +45140,10 @@
         <v>1.9</v>
       </c>
       <c r="BN110" t="n">
-        <v>-44.0107726751425</v>
+        <v>-44.0107727330347</v>
       </c>
       <c r="BO110" t="n">
-        <v>-32.69961190027192</v>
+        <v>-32.69961195452377</v>
       </c>
       <c r="BP110" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
       <c r="BX110" t="inlineStr"/>
       <c r="BY110" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ110" t="n">
@@ -45191,7 +45191,7 @@
       </c>
       <c r="CF110" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -45355,22 +45355,22 @@
         <v>10.77000045776367</v>
       </c>
       <c r="BC111" t="n">
-        <v>0.1010745357187611</v>
+        <v>0.1010745361168909</v>
       </c>
       <c r="BD111" t="n">
-        <v>0.1394828592918903</v>
+        <v>0.1394828598413094</v>
       </c>
       <c r="BE111" t="inlineStr"/>
       <c r="BF111" t="inlineStr"/>
       <c r="BG111" t="inlineStr"/>
       <c r="BH111" t="n">
-        <v>0.1202786975053257</v>
+        <v>0.1202786979791001</v>
       </c>
       <c r="BI111" t="n">
-        <v>0.1202786975053257</v>
+        <v>0.1202786979791001</v>
       </c>
       <c r="BJ111" t="n">
-        <v>0.1082508277547931</v>
+        <v>0.1082508281811901</v>
       </c>
       <c r="BK111" t="n">
         <v>2</v>
@@ -45382,10 +45382,10 @@
         <v>1.4</v>
       </c>
       <c r="BN111" t="n">
-        <v>-98.99488557888817</v>
+        <v>-98.99488557492904</v>
       </c>
       <c r="BO111" t="n">
-        <v>-98.88320619876463</v>
+        <v>-98.88320619436561</v>
       </c>
       <c r="BP111" t="inlineStr">
         <is>
@@ -45819,22 +45819,22 @@
         <v>18.76000022888184</v>
       </c>
       <c r="BC113" t="n">
-        <v>11.98879911493028</v>
+        <v>11.98926382439922</v>
       </c>
       <c r="BD113" t="n">
-        <v>14.95993628689126</v>
+        <v>14.96051616348946</v>
       </c>
       <c r="BE113" t="inlineStr"/>
       <c r="BF113" t="inlineStr"/>
       <c r="BG113" t="inlineStr"/>
       <c r="BH113" t="n">
-        <v>13.47436770091077</v>
+        <v>13.47488999394434</v>
       </c>
       <c r="BI113" t="n">
-        <v>13.47436770091077</v>
+        <v>13.47488999394434</v>
       </c>
       <c r="BJ113" t="n">
-        <v>12.12693093081969</v>
+        <v>12.12740099454991</v>
       </c>
       <c r="BK113" t="n">
         <v>2</v>
@@ -45846,10 +45846,10 @@
         <v>1.2</v>
       </c>
       <c r="BN113" t="n">
-        <v>-35.35751181841801</v>
+        <v>-35.3550061482449</v>
       </c>
       <c r="BO113" t="n">
-        <v>-28.17501313157556</v>
+        <v>-28.17222905360545</v>
       </c>
       <c r="BP113" t="inlineStr">
         <is>
@@ -46059,28 +46059,28 @@
         <v>9.359999656677246</v>
       </c>
       <c r="BC114" t="n">
-        <v>3.635112448152591</v>
+        <v>3.635112448653768</v>
       </c>
       <c r="BD114" t="n">
-        <v>3.732906912416385</v>
+        <v>3.732906912849493</v>
       </c>
       <c r="BE114" t="n">
-        <v>4.364639560568649</v>
+        <v>4.364639560473295</v>
       </c>
       <c r="BF114" t="n">
         <v>18.92207277125496</v>
       </c>
       <c r="BG114" t="n">
-        <v>3.42737940090396</v>
+        <v>3.42737940119355</v>
       </c>
       <c r="BH114" t="n">
-        <v>3.790009580510396</v>
+        <v>3.790009580792526</v>
       </c>
       <c r="BI114" t="n">
-        <v>3.684009680284488</v>
+        <v>3.684009680751631</v>
       </c>
       <c r="BJ114" t="n">
-        <v>3.315608712256039</v>
+        <v>3.315608712676468</v>
       </c>
       <c r="BK114" t="n">
         <v>4</v>
@@ -46092,10 +46092,10 @@
         <v>5.5</v>
       </c>
       <c r="BN114" t="n">
-        <v>-64.57682869795036</v>
+        <v>-64.57682869345859</v>
       </c>
       <c r="BO114" t="n">
-        <v>-59.50844316744526</v>
+        <v>-59.50844316443104</v>
       </c>
       <c r="BP114" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -46305,10 +46305,10 @@
         <v>3.549999952316284</v>
       </c>
       <c r="BC115" t="n">
-        <v>1.206061161728345</v>
+        <v>1.20659031815192</v>
       </c>
       <c r="BD115" t="n">
-        <v>1.504954580069717</v>
+        <v>1.505614875259135</v>
       </c>
       <c r="BE115" t="n">
         <v>1.301040457352757</v>
@@ -46317,16 +46317,16 @@
         <v>3.484995362022676</v>
       </c>
       <c r="BG115" t="n">
-        <v>1.059204611224817</v>
+        <v>1.059509224297599</v>
       </c>
       <c r="BH115" t="n">
-        <v>1.267815202593909</v>
+        <v>1.268188718765353</v>
       </c>
       <c r="BI115" t="n">
-        <v>1.253550809540551</v>
+        <v>1.253815387752339</v>
       </c>
       <c r="BJ115" t="n">
-        <v>1.128195728586496</v>
+        <v>1.128433848977105</v>
       </c>
       <c r="BK115" t="n">
         <v>4</v>
@@ -46338,10 +46338,10 @@
         <v>3.3</v>
       </c>
       <c r="BN115" t="n">
-        <v>-68.21983820449415</v>
+        <v>-68.21313058776717</v>
       </c>
       <c r="BO115" t="n">
-        <v>-64.28689522188044</v>
+        <v>-64.27637363944493</v>
       </c>
       <c r="BP115" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
       <c r="BS115" t="inlineStr"/>
       <c r="BT115" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="BU115" t="b">
@@ -46374,10 +46374,10 @@
         </is>
       </c>
       <c r="BZ115" t="n">
-        <v>3.539999961853027</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="CA115" t="n">
-        <v>0.2824856093507577</v>
+        <v>-0.2808986130333757</v>
       </c>
       <c r="CB115" t="n">
         <v>-43.65079611367132</v>
@@ -46393,7 +46393,7 @@
       </c>
       <c r="CF115" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.7, +0.3% do topo, MM50&gt;MM200)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -46557,22 +46557,22 @@
         <v>5.400000095367432</v>
       </c>
       <c r="BC116" t="n">
-        <v>5.343904102939224</v>
+        <v>5.343904102742365</v>
       </c>
       <c r="BD116" t="n">
-        <v>6.541486714726116</v>
+        <v>6.54148671448514</v>
       </c>
       <c r="BE116" t="inlineStr"/>
       <c r="BF116" t="inlineStr"/>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="n">
-        <v>5.94269540883267</v>
+        <v>5.942695408613753</v>
       </c>
       <c r="BI116" t="n">
-        <v>5.94269540883267</v>
+        <v>5.942695408613753</v>
       </c>
       <c r="BJ116" t="n">
-        <v>5.348425867949403</v>
+        <v>5.348425867752378</v>
       </c>
       <c r="BK116" t="n">
         <v>2</v>
@@ -46584,10 +46584,10 @@
         <v>1.2</v>
       </c>
       <c r="BN116" t="n">
-        <v>-0.9550782686517656</v>
+        <v>-0.9550782723003692</v>
       </c>
       <c r="BO116" t="n">
-        <v>10.04991303483136</v>
+        <v>10.04991303077736</v>
       </c>
       <c r="BP116" t="inlineStr">
         <is>
@@ -46793,10 +46793,10 @@
         <v>14.1899995803833</v>
       </c>
       <c r="BC117" t="n">
-        <v>6.126069902129789</v>
+        <v>6.125926851193306</v>
       </c>
       <c r="BD117" t="n">
-        <v>11.36385966845076</v>
+        <v>11.36359430896358</v>
       </c>
       <c r="BE117" t="n">
         <v>4.775653910085819</v>
@@ -46808,7 +46808,7 @@
         <v>10.81280130585469</v>
       </c>
       <c r="BH117" t="n">
-        <v>8.055617111807853</v>
+        <v>8.05553542972312</v>
       </c>
       <c r="BI117" t="n">
         <v>7.199700772518211</v>
@@ -46829,7 +46829,7 @@
         <v>-54.33593455334437</v>
       </c>
       <c r="BO117" t="n">
-        <v>-43.23032170526495</v>
+        <v>-43.23089733660497</v>
       </c>
       <c r="BP117" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Rompimento</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -47033,25 +47033,25 @@
         <v>1.37</v>
       </c>
       <c r="BA118" t="n">
-        <v>41</v>
+        <v>41.01</v>
       </c>
       <c r="BB118" t="n">
         <v>1.610000014305115</v>
       </c>
       <c r="BC118" t="n">
-        <v>0.143372410237274</v>
+        <v>0.1433907931038036</v>
       </c>
       <c r="BD118" t="n">
-        <v>0.1523911400980908</v>
+        <v>0.1524099494292089</v>
       </c>
       <c r="BE118" t="n">
-        <v>0.4071751717748189</v>
+        <v>0.4071732218113782</v>
       </c>
       <c r="BF118" t="n">
         <v>2.356013490127236</v>
       </c>
       <c r="BG118" t="n">
-        <v>0.1061263173929686</v>
+        <v>0.1061318792351744</v>
       </c>
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr"/>
@@ -47079,7 +47079,11 @@
       </c>
       <c r="BR118" t="inlineStr"/>
       <c r="BS118" t="inlineStr"/>
-      <c r="BT118" t="inlineStr"/>
+      <c r="BT118" t="inlineStr">
+        <is>
+          <t>Rompimento</t>
+        </is>
+      </c>
       <c r="BU118" t="b">
         <v>0</v>
       </c>
@@ -47094,10 +47098,10 @@
         </is>
       </c>
       <c r="BZ118" t="n">
-        <v>1.639999985694885</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="CA118" t="n">
-        <v>-1.829266564112753</v>
+        <v>0.6249993946403354</v>
       </c>
       <c r="CB118" t="n">
         <v>-42.61824784986528</v>
@@ -47106,14 +47110,14 @@
         <v>0</v>
       </c>
       <c r="CD118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE118" t="b">
         <v>0</v>
       </c>
       <c r="CF118" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.8%))</t>
+          <t>Rompimento (vol x0.6, +0.6% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -47275,10 +47279,10 @@
         <v>18.14999961853027</v>
       </c>
       <c r="BC119" t="n">
-        <v>3.405452395988166</v>
+        <v>3.405455027289707</v>
       </c>
       <c r="BD119" t="n">
-        <v>6.317114194558048</v>
+        <v>6.317119075622406</v>
       </c>
       <c r="BE119" t="n">
         <v>14.76289103410228</v>
@@ -47287,16 +47291,16 @@
         <v>15.72528139501627</v>
       </c>
       <c r="BG119" t="n">
-        <v>10.129537430064</v>
+        <v>10.12953552874592</v>
       </c>
       <c r="BH119" t="n">
-        <v>11.73370601343515</v>
+        <v>11.73370675837172</v>
       </c>
       <c r="BI119" t="n">
-        <v>12.44621423208314</v>
+        <v>12.4462132814241</v>
       </c>
       <c r="BJ119" t="n">
-        <v>11.20159280887482</v>
+        <v>11.20159195328169</v>
       </c>
       <c r="BK119" t="n">
         <v>4</v>
@@ -47308,10 +47312,10 @@
         <v>4.6</v>
       </c>
       <c r="BN119" t="n">
-        <v>-38.28323391567161</v>
+        <v>-38.28323862968348</v>
       </c>
       <c r="BO119" t="n">
-        <v>-35.3514806608833</v>
+        <v>-35.35147655654952</v>
       </c>
       <c r="BP119" t="inlineStr">
         <is>
@@ -47340,10 +47344,10 @@
         </is>
       </c>
       <c r="BZ119" t="n">
-        <v>20.82999992370605</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="CA119" t="n">
-        <v>-12.86606008157372</v>
+        <v>-11.97866692615981</v>
       </c>
       <c r="CB119" t="n">
         <v>-31.2598598602242</v>
@@ -47359,7 +47363,7 @@
       </c>
       <c r="CF119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-12.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-12.0%))</t>
         </is>
       </c>
     </row>
@@ -47521,28 +47525,28 @@
         <v>13.59000015258789</v>
       </c>
       <c r="BC120" t="n">
-        <v>1.270943320404341</v>
+        <v>1.270971148125419</v>
       </c>
       <c r="BD120" t="n">
-        <v>2.103244971936693</v>
+        <v>2.103277643012004</v>
       </c>
       <c r="BE120" t="n">
-        <v>6.613442584300999</v>
+        <v>6.613400512641642</v>
       </c>
       <c r="BF120" t="n">
         <v>9.695300387264011</v>
       </c>
       <c r="BG120" t="n">
-        <v>3.590397423295398</v>
+        <v>3.590384282179398</v>
       </c>
       <c r="BH120" t="n">
-        <v>4.102361659844363</v>
+        <v>4.102354145944348</v>
       </c>
       <c r="BI120" t="n">
-        <v>3.590397423295398</v>
+        <v>3.590384282179398</v>
       </c>
       <c r="BJ120" t="n">
-        <v>3.231357680965858</v>
+        <v>3.231345853961459</v>
       </c>
       <c r="BK120" t="n">
         <v>3</v>
@@ -47554,10 +47558,10 @@
         <v>7.6</v>
       </c>
       <c r="BN120" t="n">
-        <v>-76.22253388753256</v>
+        <v>-76.22262091478986</v>
       </c>
       <c r="BO120" t="n">
-        <v>-69.8133803253625</v>
+        <v>-69.81343561528104</v>
       </c>
       <c r="BP120" t="inlineStr">
         <is>
@@ -47582,14 +47586,14 @@
       <c r="BX120" t="inlineStr"/>
       <c r="BY120" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ120" t="n">
-        <v>14.27999973297119</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="CA120" t="n">
-        <v>-4.831929924971612</v>
+        <v>-5.886422801217616</v>
       </c>
       <c r="CB120" t="n">
         <v>-21.57503186501287</v>
@@ -47605,7 +47609,7 @@
       </c>
       <c r="CF120" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-4.8%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -47769,22 +47773,22 @@
         <v>5.21999979019165</v>
       </c>
       <c r="BC121" t="n">
-        <v>1.270845352532034</v>
+        <v>1.270845349694995</v>
       </c>
       <c r="BD121" t="n">
-        <v>1.850350833286641</v>
+        <v>1.850350829155913</v>
       </c>
       <c r="BE121" t="inlineStr"/>
       <c r="BF121" t="inlineStr"/>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="n">
-        <v>1.560598092909338</v>
+        <v>1.560598089425454</v>
       </c>
       <c r="BI121" t="n">
-        <v>1.560598092909338</v>
+        <v>1.560598089425454</v>
       </c>
       <c r="BJ121" t="n">
-        <v>1.404538283618404</v>
+        <v>1.404538280482909</v>
       </c>
       <c r="BK121" t="n">
         <v>2</v>
@@ -47796,10 +47800,10 @@
         <v>1.5</v>
       </c>
       <c r="BN121" t="n">
-        <v>-73.09313524767715</v>
+        <v>-73.09313530774411</v>
       </c>
       <c r="BO121" t="n">
-        <v>-70.10348360853015</v>
+        <v>-70.10348367527124</v>
       </c>
       <c r="BP121" t="inlineStr">
         <is>
@@ -48015,22 +48019,22 @@
         <v>4.989999771118164</v>
       </c>
       <c r="BC122" t="n">
-        <v>1.533580467128494</v>
+        <v>1.533580463418692</v>
       </c>
       <c r="BD122" t="n">
-        <v>2.232893160139088</v>
+        <v>2.232893154737616</v>
       </c>
       <c r="BE122" t="inlineStr"/>
       <c r="BF122" t="inlineStr"/>
       <c r="BG122" t="inlineStr"/>
       <c r="BH122" t="n">
-        <v>1.883236813633791</v>
+        <v>1.883236809078154</v>
       </c>
       <c r="BI122" t="n">
-        <v>1.883236813633791</v>
+        <v>1.883236809078154</v>
       </c>
       <c r="BJ122" t="n">
-        <v>1.694913132270412</v>
+        <v>1.694913128170339</v>
       </c>
       <c r="BK122" t="n">
         <v>2</v>
@@ -48042,10 +48046,10 @@
         <v>1.5</v>
       </c>
       <c r="BN122" t="n">
-        <v>-66.03380340655579</v>
+        <v>-66.03380348872159</v>
       </c>
       <c r="BO122" t="n">
-        <v>-62.25978156283977</v>
+        <v>-62.25978165413508</v>
       </c>
       <c r="BP122" t="inlineStr">
         <is>
@@ -48218,7 +48222,7 @@
         <v>1</v>
       </c>
       <c r="AP123" t="n">
-        <v>2160784384</v>
+        <v>2167328768</v>
       </c>
       <c r="AQ123" t="n">
         <v>35.2</v>
@@ -48255,19 +48259,19 @@
         <v>18.64999961853027</v>
       </c>
       <c r="BC123" t="n">
-        <v>0.5813260412474333</v>
+        <v>0.5812860399528205</v>
       </c>
       <c r="BD123" t="n">
-        <v>0.8170624275747346</v>
+        <v>0.8170101959675572</v>
       </c>
       <c r="BE123" t="n">
-        <v>5.319166563523466</v>
+        <v>5.319192545921164</v>
       </c>
       <c r="BF123" t="n">
         <v>12.05460652644226</v>
       </c>
       <c r="BG123" t="n">
-        <v>2.177455698527987</v>
+        <v>2.177464093708781</v>
       </c>
       <c r="BH123" t="inlineStr"/>
       <c r="BI123" t="inlineStr"/>
@@ -48489,10 +48493,10 @@
         <v>1.919999957084656</v>
       </c>
       <c r="BC124" t="n">
-        <v>0.5385769146372712</v>
+        <v>0.5386118472261938</v>
       </c>
       <c r="BD124" t="n">
-        <v>0.7841679877118669</v>
+        <v>0.7842188495613381</v>
       </c>
       <c r="BE124" t="n">
         <v>0.4365544283708006</v>
@@ -48502,13 +48506,13 @@
       </c>
       <c r="BG124" t="inlineStr"/>
       <c r="BH124" t="n">
-        <v>0.5864331102399797</v>
+        <v>0.5864617083861109</v>
       </c>
       <c r="BI124" t="n">
-        <v>0.5385769146372712</v>
+        <v>0.5386118472261938</v>
       </c>
       <c r="BJ124" t="n">
-        <v>0.4847192231735441</v>
+        <v>0.4847506625035745</v>
       </c>
       <c r="BK124" t="n">
         <v>3</v>
@@ -48520,10 +48524,10 @@
         <v>7.3</v>
       </c>
       <c r="BN124" t="n">
-        <v>-74.75420656209046</v>
+        <v>-74.75256909694811</v>
       </c>
       <c r="BO124" t="n">
-        <v>-69.45660815896973</v>
+        <v>-69.45511867215876</v>
       </c>
       <c r="BP124" t="inlineStr">
         <is>
@@ -48552,13 +48556,13 @@
         </is>
       </c>
       <c r="BZ124" t="n">
-        <v>2.079999923706055</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="CA124" t="n">
-        <v>-7.69230636971937</v>
+        <v>-5.418719992877974</v>
       </c>
       <c r="CB124" t="n">
-        <v>-54.87060603413229</v>
+        <v>-54.87060095233498</v>
       </c>
       <c r="CC124" t="b">
         <v>0</v>
@@ -48571,7 +48575,7 @@
       </c>
       <c r="CF124" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral; sem novo topo (-7.7%))</t>
+          <t>sem sinal (Lateral; sem novo topo (-5.4%))</t>
         </is>
       </c>
     </row>
@@ -48778,10 +48782,10 @@
         </is>
       </c>
       <c r="BZ125" t="n">
-        <v>1.070000052452087</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="CA125" t="n">
-        <v>-32.71028099856381</v>
+        <v>-31.42856558974881</v>
       </c>
       <c r="CB125" t="n">
         <v>-86.86131339225869</v>
@@ -48797,7 +48801,7 @@
       </c>
       <c r="CF125" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-32.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-31.4%))</t>
         </is>
       </c>
     </row>
@@ -48961,22 +48965,22 @@
         <v>4.460000038146973</v>
       </c>
       <c r="BC126" t="n">
-        <v>0.8479444227951365</v>
+        <v>0.8479444236785304</v>
       </c>
       <c r="BD126" t="n">
-        <v>1.572936904284978</v>
+        <v>1.572936905923674</v>
       </c>
       <c r="BE126" t="inlineStr"/>
       <c r="BF126" t="inlineStr"/>
       <c r="BG126" t="inlineStr"/>
       <c r="BH126" t="n">
-        <v>1.210440663540057</v>
+        <v>1.210440664801102</v>
       </c>
       <c r="BI126" t="n">
-        <v>1.210440663540057</v>
+        <v>1.210440664801102</v>
       </c>
       <c r="BJ126" t="n">
-        <v>1.089396597186052</v>
+        <v>1.089396598320992</v>
       </c>
       <c r="BK126" t="n">
         <v>2</v>
@@ -48988,10 +48992,10 @@
         <v>1.9</v>
       </c>
       <c r="BN126" t="n">
-        <v>-75.57406753658526</v>
+        <v>-75.57406751113815</v>
       </c>
       <c r="BO126" t="n">
-        <v>-72.86007504065029</v>
+        <v>-72.86007501237573</v>
       </c>
       <c r="BP126" t="inlineStr">
         <is>
@@ -49020,10 +49024,10 @@
         </is>
       </c>
       <c r="BZ126" t="n">
-        <v>4.840000152587891</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="CA126" t="n">
-        <v>-7.85124178638169</v>
+        <v>-5.907167647502643</v>
       </c>
       <c r="CB126" t="n">
         <v>-57.64482287514247</v>
@@ -49039,7 +49043,7 @@
       </c>
       <c r="CF126" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.9%))</t>
         </is>
       </c>
     </row>
@@ -49439,22 +49443,22 @@
         <v>3.519999980926514</v>
       </c>
       <c r="BC128" t="n">
-        <v>0.2312525866192832</v>
+        <v>0.231159204361707</v>
       </c>
       <c r="BD128" t="n">
-        <v>0.3367037661176764</v>
+        <v>0.3365678015506455</v>
       </c>
       <c r="BE128" t="inlineStr"/>
       <c r="BF128" t="inlineStr"/>
       <c r="BG128" t="inlineStr"/>
       <c r="BH128" t="n">
-        <v>0.2839781763684798</v>
+        <v>0.2838635029561762</v>
       </c>
       <c r="BI128" t="n">
-        <v>0.2839781763684798</v>
+        <v>0.2838635029561762</v>
       </c>
       <c r="BJ128" t="n">
-        <v>0.2555803587316319</v>
+        <v>0.2554771526605586</v>
       </c>
       <c r="BK128" t="n">
         <v>2</v>
@@ -49466,10 +49470,10 @@
         <v>1.5</v>
       </c>
       <c r="BN128" t="n">
-        <v>-92.73919431487158</v>
+        <v>-92.74212630554295</v>
       </c>
       <c r="BO128" t="n">
-        <v>-91.93243812763508</v>
+        <v>-91.93569589504771</v>
       </c>
       <c r="BP128" t="inlineStr">
         <is>
@@ -49681,22 +49685,22 @@
         <v>7.039999961853027</v>
       </c>
       <c r="BC129" t="n">
-        <v>1.122873168591103</v>
+        <v>1.123146229461417</v>
       </c>
       <c r="BD129" t="n">
-        <v>2.082929727736496</v>
+        <v>2.083436255650928</v>
       </c>
       <c r="BE129" t="inlineStr"/>
       <c r="BF129" t="inlineStr"/>
       <c r="BG129" t="inlineStr"/>
       <c r="BH129" t="n">
-        <v>1.6029014481638</v>
+        <v>1.603291242556172</v>
       </c>
       <c r="BI129" t="n">
-        <v>1.6029014481638</v>
+        <v>1.603291242556172</v>
       </c>
       <c r="BJ129" t="n">
-        <v>1.44261130334742</v>
+        <v>1.442962118300555</v>
       </c>
       <c r="BK129" t="n">
         <v>2</v>
@@ -49708,10 +49712,10 @@
         <v>1.9</v>
       </c>
       <c r="BN129" t="n">
-        <v>-79.50836205732445</v>
+        <v>-79.5033788903495</v>
       </c>
       <c r="BO129" t="n">
-        <v>-77.23151339702716</v>
+        <v>-77.22597654483278</v>
       </c>
       <c r="BP129" t="inlineStr">
         <is>
@@ -49923,22 +49927,22 @@
         <v>3.880000114440918</v>
       </c>
       <c r="BC130" t="n">
-        <v>0.7317241885661088</v>
+        <v>0.7318623490146777</v>
       </c>
       <c r="BD130" t="n">
-        <v>1.357348369790132</v>
+        <v>1.357604657422227</v>
       </c>
       <c r="BE130" t="inlineStr"/>
       <c r="BF130" t="inlineStr"/>
       <c r="BG130" t="inlineStr"/>
       <c r="BH130" t="n">
-        <v>1.04453627917812</v>
+        <v>1.044733503218452</v>
       </c>
       <c r="BI130" t="n">
-        <v>1.04453627917812</v>
+        <v>1.044733503218452</v>
       </c>
       <c r="BJ130" t="n">
-        <v>0.9400826512603081</v>
+        <v>0.9402601528966071</v>
       </c>
       <c r="BK130" t="n">
         <v>2</v>
@@ -49950,10 +49954,10 @@
         <v>1.9</v>
       </c>
       <c r="BN130" t="n">
-        <v>-75.7710664038017</v>
+        <v>-75.76649161949594</v>
       </c>
       <c r="BO130" t="n">
-        <v>-73.07896267089077</v>
+        <v>-73.07387957721771</v>
       </c>
       <c r="BP130" t="inlineStr">
         <is>
@@ -49982,10 +49986,10 @@
         </is>
       </c>
       <c r="BZ130" t="n">
-        <v>3.940000057220459</v>
+        <v>3.920000076293945</v>
       </c>
       <c r="CA130" t="n">
-        <v>-1.522841165181832</v>
+        <v>-1.020407170268323</v>
       </c>
       <c r="CB130" t="n">
         <v>-19.23016222053626</v>
@@ -50001,7 +50005,7 @@
       </c>
       <c r="CF130" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-1.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-1.0%))</t>
         </is>
       </c>
     </row>
@@ -50165,22 +50169,22 @@
         <v>4.570000171661377</v>
       </c>
       <c r="BC131" t="n">
-        <v>5.030584391500779</v>
+        <v>5.030584397202853</v>
       </c>
       <c r="BD131" t="n">
-        <v>7.324530874025134</v>
+        <v>7.324530882327355</v>
       </c>
       <c r="BE131" t="inlineStr"/>
       <c r="BF131" t="inlineStr"/>
       <c r="BG131" t="inlineStr"/>
       <c r="BH131" t="n">
-        <v>6.177557632762957</v>
+        <v>6.177557639765104</v>
       </c>
       <c r="BI131" t="n">
-        <v>6.177557632762957</v>
+        <v>6.177557639765104</v>
       </c>
       <c r="BJ131" t="n">
-        <v>5.559801869486662</v>
+        <v>5.559801875788594</v>
       </c>
       <c r="BK131" t="n">
         <v>2</v>
@@ -50192,10 +50196,10 @@
         <v>1.5</v>
       </c>
       <c r="BN131" t="n">
-        <v>21.65867966401962</v>
+        <v>21.65867980191749</v>
       </c>
       <c r="BO131" t="n">
-        <v>35.17631073779957</v>
+        <v>35.17631089101943</v>
       </c>
       <c r="BP131" t="inlineStr">
         <is>
@@ -50405,28 +50409,28 @@
         <v>7.960000038146973</v>
       </c>
       <c r="BC132" t="n">
-        <v>2.047044926677501</v>
+        <v>2.047044918754307</v>
       </c>
       <c r="BD132" t="n">
-        <v>2.293366950486404</v>
+        <v>2.293366943678481</v>
       </c>
       <c r="BE132" t="n">
-        <v>3.461890974527313</v>
+        <v>3.461890977650023</v>
       </c>
       <c r="BF132" t="n">
         <v>10.30229513821885</v>
       </c>
       <c r="BG132" t="n">
-        <v>2.135782918984071</v>
+        <v>2.135782917348172</v>
       </c>
       <c r="BH132" t="n">
-        <v>2.484521442668822</v>
+        <v>2.484521439357746</v>
       </c>
       <c r="BI132" t="n">
-        <v>2.214574934735237</v>
+        <v>2.214574930513327</v>
       </c>
       <c r="BJ132" t="n">
-        <v>1.993117441261714</v>
+        <v>1.993117437461994</v>
       </c>
       <c r="BK132" t="n">
         <v>4</v>
@@ -50438,10 +50442,10 @@
         <v>5</v>
       </c>
       <c r="BN132" t="n">
-        <v>-74.96083628504987</v>
+        <v>-74.96083633278504</v>
       </c>
       <c r="BO132" t="n">
-        <v>-68.78741921153055</v>
+        <v>-68.78741925312698</v>
       </c>
       <c r="BP132" t="inlineStr">
         <is>
@@ -50470,10 +50474,10 @@
         </is>
       </c>
       <c r="BZ132" t="n">
-        <v>8.840000152587891</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="CA132" t="n">
-        <v>-9.954752253972533</v>
+        <v>-7.549357078384833</v>
       </c>
       <c r="CB132" t="n">
         <v>-47.939829574844</v>
@@ -50489,7 +50493,7 @@
       </c>
       <c r="CF132" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-10.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.5%))</t>
         </is>
       </c>
     </row>
@@ -50651,28 +50655,28 @@
         <v>37.27999877929688</v>
       </c>
       <c r="BC133" t="n">
-        <v>8.396728318589608</v>
+        <v>8.396728339013318</v>
       </c>
       <c r="BD133" t="n">
-        <v>8.57562196305012</v>
+        <v>8.575621973962811</v>
       </c>
       <c r="BE133" t="n">
-        <v>8.957805179875638</v>
+        <v>8.957805169486226</v>
       </c>
       <c r="BF133" t="n">
         <v>23.72415321036037</v>
       </c>
       <c r="BG133" t="n">
-        <v>4.187393799694183</v>
+        <v>4.18739379189913</v>
       </c>
       <c r="BH133" t="n">
-        <v>7.529387315302387</v>
+        <v>7.529387318590371</v>
       </c>
       <c r="BI133" t="n">
-        <v>8.486175140819864</v>
+        <v>8.486175156488065</v>
       </c>
       <c r="BJ133" t="n">
-        <v>7.637557626737878</v>
+        <v>7.637557640839258</v>
       </c>
       <c r="BK133" t="n">
         <v>4</v>
@@ -50684,10 +50688,10 @@
         <v>5.7</v>
       </c>
       <c r="BN133" t="n">
-        <v>-79.51298852783405</v>
+        <v>-79.51298849000845</v>
       </c>
       <c r="BO133" t="n">
-        <v>-79.80314495212976</v>
+        <v>-79.80314494331006</v>
       </c>
       <c r="BP133" t="inlineStr">
         <is>
@@ -50716,10 +50720,10 @@
         </is>
       </c>
       <c r="BZ133" t="n">
-        <v>39.84999847412109</v>
+        <v>39.5</v>
       </c>
       <c r="CA133" t="n">
-        <v>-6.449183922787849</v>
+        <v>-5.620256254944622</v>
       </c>
       <c r="CB133" t="n">
         <v>-19.51640970441861</v>
@@ -50735,7 +50739,7 @@
       </c>
       <c r="CF133" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.6%))</t>
         </is>
       </c>
     </row>
@@ -50860,7 +50864,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>49977982976</v>
+        <v>50082459648</v>
       </c>
       <c r="AQ134" t="n">
         <v>39.13</v>
@@ -51139,28 +51143,28 @@
         <v>4.590000152587891</v>
       </c>
       <c r="BC135" t="n">
-        <v>1.422239267877589</v>
+        <v>1.422448349989748</v>
       </c>
       <c r="BD135" t="n">
-        <v>1.596369910924945</v>
+        <v>1.596555891997031</v>
       </c>
       <c r="BE135" t="n">
-        <v>2.525724521238395</v>
+        <v>2.525647481279603</v>
       </c>
       <c r="BF135" t="n">
         <v>7.762065500556266</v>
       </c>
       <c r="BG135" t="n">
-        <v>1.794334359165403</v>
+        <v>1.794427249856229</v>
       </c>
       <c r="BH135" t="n">
-        <v>1.834667014801583</v>
+        <v>1.834769743280653</v>
       </c>
       <c r="BI135" t="n">
-        <v>1.695352135045173</v>
+        <v>1.69549157092663</v>
       </c>
       <c r="BJ135" t="n">
-        <v>1.525816921540656</v>
+        <v>1.525942413833967</v>
       </c>
       <c r="BK135" t="n">
         <v>4</v>
@@ -51172,10 +51176,10 @@
         <v>5.5</v>
       </c>
       <c r="BN135" t="n">
-        <v>-66.75780237871268</v>
+        <v>-66.75506834191228</v>
       </c>
       <c r="BO135" t="n">
-        <v>-60.02904240063744</v>
+        <v>-60.02680430748592</v>
       </c>
       <c r="BP135" t="inlineStr">
         <is>
@@ -51360,7 +51364,7 @@
         <v>1.85</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AU136" t="n">
         <v>0.79</v>
@@ -51379,25 +51383,25 @@
         <v>0.76</v>
       </c>
       <c r="BA136" t="n">
-        <v>471.81</v>
+        <v>473.91</v>
       </c>
       <c r="BB136" t="n">
         <v>4.400000095367432</v>
       </c>
       <c r="BC136" t="n">
-        <v>0.7305245518627088</v>
+        <v>0.7308988747678928</v>
       </c>
       <c r="BD136" t="n">
-        <v>0.735416029430748</v>
+        <v>0.7357710058954502</v>
       </c>
       <c r="BE136" t="n">
-        <v>0.820301086034579</v>
+        <v>0.8202767233153943</v>
       </c>
       <c r="BF136" t="n">
         <v>6.035847779670984</v>
       </c>
       <c r="BG136" t="n">
-        <v>0.2744890196020501</v>
+        <v>0.2745834898717437</v>
       </c>
       <c r="BH136" t="inlineStr"/>
       <c r="BI136" t="inlineStr"/>
@@ -51837,28 +51841,28 @@
         <v>18.39999961853027</v>
       </c>
       <c r="BC138" t="n">
-        <v>2.214185752413772</v>
+        <v>2.214185755542215</v>
       </c>
       <c r="BD138" t="n">
-        <v>3.494659076971378</v>
+        <v>3.494659080017506</v>
       </c>
       <c r="BE138" t="n">
-        <v>8.532878897029127</v>
+        <v>8.532878892410654</v>
       </c>
       <c r="BF138" t="n">
         <v>12.70912726712086</v>
       </c>
       <c r="BG138" t="n">
-        <v>4.841432923378834</v>
+        <v>4.841432921685391</v>
       </c>
       <c r="BH138" t="n">
-        <v>4.770789162448278</v>
+        <v>4.770789162413942</v>
       </c>
       <c r="BI138" t="n">
-        <v>4.168046000175106</v>
+        <v>4.168046000851449</v>
       </c>
       <c r="BJ138" t="n">
-        <v>3.751241400157595</v>
+        <v>3.751241400766304</v>
       </c>
       <c r="BK138" t="n">
         <v>4</v>
@@ -51870,10 +51874,10 @@
         <v>5.7</v>
       </c>
       <c r="BN138" t="n">
-        <v>-79.61281805473629</v>
+        <v>-79.61281805142809</v>
       </c>
       <c r="BO138" t="n">
-        <v>-74.0717974926276</v>
+        <v>-74.07179749281421</v>
       </c>
       <c r="BP138" t="inlineStr">
         <is>
@@ -51902,10 +51906,10 @@
         </is>
       </c>
       <c r="BZ138" t="n">
-        <v>19.70000076293945</v>
+        <v>19.73999977111816</v>
       </c>
       <c r="CA138" t="n">
-        <v>-6.598990325192277</v>
+        <v>-6.788248065475977</v>
       </c>
       <c r="CB138" t="n">
         <v>-16.70439342946463</v>
@@ -51921,7 +51925,7 @@
       </c>
       <c r="CF138" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (-6.6%))</t>
+          <t>sem sinal (Em Alta; sem novo topo (-6.8%))</t>
         </is>
       </c>
     </row>
@@ -52081,22 +52085,22 @@
         <v>18.27000045776367</v>
       </c>
       <c r="BC139" t="n">
-        <v>1.406530330664066</v>
+        <v>1.406412791015326</v>
       </c>
       <c r="BD139" t="n">
-        <v>2.04790816144688</v>
+        <v>2.047737023718315</v>
       </c>
       <c r="BE139" t="inlineStr"/>
       <c r="BF139" t="inlineStr"/>
       <c r="BG139" t="inlineStr"/>
       <c r="BH139" t="n">
-        <v>1.727219246055473</v>
+        <v>1.72707490736682</v>
       </c>
       <c r="BI139" t="n">
-        <v>1.727219246055473</v>
+        <v>1.72707490736682</v>
       </c>
       <c r="BJ139" t="n">
-        <v>1.554497321449926</v>
+        <v>1.554367416630138</v>
       </c>
       <c r="BK139" t="n">
         <v>2</v>
@@ -52108,10 +52112,10 @@
         <v>1.5</v>
       </c>
       <c r="BN139" t="n">
-        <v>-91.49153102079231</v>
+        <v>-91.49224204879741</v>
       </c>
       <c r="BO139" t="n">
-        <v>-90.54614557865813</v>
+        <v>-90.54693560977491</v>
       </c>
       <c r="BP139" t="inlineStr">
         <is>
@@ -52604,7 +52608,7 @@
       <c r="BX141" t="inlineStr"/>
       <c r="BY141" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="BZ141" t="n">
@@ -52627,7 +52631,7 @@
       </c>
       <c r="CF141" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta; sem novo topo (+9.0%))</t>
+          <t>sem sinal (Lateral; sem novo topo (+9.0%))</t>
         </is>
       </c>
     </row>
@@ -52834,10 +52838,10 @@
         </is>
       </c>
       <c r="BZ142" t="n">
-        <v>0.4399999976158142</v>
+        <v>0.4099999964237213</v>
       </c>
       <c r="CA142" t="n">
-        <v>-47.7272714957718</v>
+        <v>-43.90243751743164</v>
       </c>
       <c r="CB142" t="n">
         <v>-98.71937630347001</v>
@@ -52853,7 +52857,7 @@
       </c>
       <c r="CF142" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-47.7%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-43.9%))</t>
         </is>
       </c>
     </row>
@@ -53015,10 +53019,10 @@
         <v>92.51999664306641</v>
       </c>
       <c r="BC143" t="n">
-        <v>4.738941172031056</v>
+        <v>4.738655123127625</v>
       </c>
       <c r="BD143" t="n">
-        <v>8.790735874117606</v>
+        <v>8.790205253401744</v>
       </c>
       <c r="BE143" t="n">
         <v>30.30630297949641</v>
@@ -53027,16 +53031,16 @@
         <v>34.54467861351081</v>
       </c>
       <c r="BG143" t="n">
-        <v>17.63476880961933</v>
+        <v>17.63506426772841</v>
       </c>
       <c r="BH143" t="n">
-        <v>22.81912156918604</v>
+        <v>22.81906277853435</v>
       </c>
       <c r="BI143" t="n">
-        <v>23.97053589455787</v>
+        <v>23.97068362361241</v>
       </c>
       <c r="BJ143" t="n">
-        <v>21.57348230510208</v>
+        <v>21.57361526125117</v>
       </c>
       <c r="BK143" t="n">
         <v>4</v>
@@ -53048,10 +53052,10 @@
         <v>7.3</v>
       </c>
       <c r="BN143" t="n">
-        <v>-76.68235723318216</v>
+        <v>-76.68221352787097</v>
       </c>
       <c r="BO143" t="n">
-        <v>-75.33601124390428</v>
+        <v>-75.33607478762869</v>
       </c>
       <c r="BP143" t="inlineStr">
         <is>
@@ -53497,10 +53501,10 @@
         <v>18.01000022888184</v>
       </c>
       <c r="BC145" t="n">
-        <v>9.126588130856087</v>
+        <v>9.126588152420672</v>
       </c>
       <c r="BD145" t="n">
-        <v>13.28831231852646</v>
+        <v>13.2883123499245</v>
       </c>
       <c r="BE145" t="n">
         <v>4.677922137371906</v>
@@ -53510,13 +53514,13 @@
       </c>
       <c r="BG145" t="inlineStr"/>
       <c r="BH145" t="n">
-        <v>8.96562576510911</v>
+        <v>8.965625778349764</v>
       </c>
       <c r="BI145" t="n">
-        <v>8.948134302269034</v>
+        <v>8.948134313051327</v>
       </c>
       <c r="BJ145" t="n">
-        <v>8.05332087204213</v>
+        <v>8.053320881746194</v>
       </c>
       <c r="BK145" t="n">
         <v>4</v>
@@ -53528,10 +53532,10 @@
         <v>2.8</v>
       </c>
       <c r="BN145" t="n">
-        <v>-55.2841711843658</v>
+        <v>-55.28417113048427</v>
       </c>
       <c r="BO145" t="n">
-        <v>-50.21862492410558</v>
+        <v>-50.21862485058723</v>
       </c>
       <c r="BP145" t="inlineStr">
         <is>
@@ -53802,10 +53806,10 @@
         </is>
       </c>
       <c r="BZ146" t="n">
-        <v>74.15000152587891</v>
+        <v>73.62000274658203</v>
       </c>
       <c r="CA146" t="n">
-        <v>-8.496295242231467</v>
+        <v>-7.837549656609899</v>
       </c>
       <c r="CB146" t="n">
         <v>-20.08245317470424</v>
@@ -53821,7 +53825,7 @@
       </c>
       <c r="CF146" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
         </is>
       </c>
     </row>
@@ -53985,22 +53989,22 @@
         <v>3.670000076293945</v>
       </c>
       <c r="BC147" t="n">
-        <v>0.6630815617780936</v>
+        <v>0.6630815599016783</v>
       </c>
       <c r="BD147" t="n">
-        <v>1.230016297098364</v>
+        <v>1.230016293617613</v>
       </c>
       <c r="BE147" t="inlineStr"/>
       <c r="BF147" t="inlineStr"/>
       <c r="BG147" t="inlineStr"/>
       <c r="BH147" t="n">
-        <v>0.9465489294382287</v>
+        <v>0.9465489267596459</v>
       </c>
       <c r="BI147" t="n">
-        <v>0.9465489294382287</v>
+        <v>0.9465489267596459</v>
       </c>
       <c r="BJ147" t="n">
-        <v>0.8518940364944058</v>
+        <v>0.8518940340836813</v>
       </c>
       <c r="BK147" t="n">
         <v>2</v>
@@ -54012,10 +54016,10 @@
         <v>1.9</v>
       </c>
       <c r="BN147" t="n">
-        <v>-76.78762891594626</v>
+        <v>-76.78762898163359</v>
       </c>
       <c r="BO147" t="n">
-        <v>-74.20847657327363</v>
+        <v>-74.20847664625954</v>
       </c>
       <c r="BP147" t="inlineStr">
         <is>
@@ -54227,22 +54231,22 @@
         <v>10.8100004196167</v>
       </c>
       <c r="BC148" t="n">
-        <v>5.775801266572858</v>
+        <v>5.775801265231578</v>
       </c>
       <c r="BD148" t="n">
-        <v>10.57185550348261</v>
+        <v>10.57185550102757</v>
       </c>
       <c r="BE148" t="inlineStr"/>
       <c r="BF148" t="inlineStr"/>
       <c r="BG148" t="inlineStr"/>
       <c r="BH148" t="n">
-        <v>8.173828385027736</v>
+        <v>8.173828383129576</v>
       </c>
       <c r="BI148" t="n">
-        <v>8.173828385027736</v>
+        <v>8.173828383129576</v>
       </c>
       <c r="BJ148" t="n">
-        <v>7.356445546524963</v>
+        <v>7.356445544816619</v>
       </c>
       <c r="BK148" t="n">
         <v>2</v>
@@ -54254,10 +54258,10 @@
         <v>1.8</v>
       </c>
       <c r="BN148" t="n">
-        <v>-31.94777741936657</v>
+        <v>-31.94777743516994</v>
       </c>
       <c r="BO148" t="n">
-        <v>-24.38641935485176</v>
+        <v>-24.38641937241105</v>
       </c>
       <c r="BP148" t="inlineStr">
         <is>
@@ -54286,10 +54290,10 @@
         </is>
       </c>
       <c r="BZ148" t="n">
-        <v>11.76000022888184</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="CA148" t="n">
-        <v>-8.078229513397417</v>
+        <v>-6.729937210544623</v>
       </c>
       <c r="CB148" t="n">
         <v>-26.26193361437886</v>
@@ -54305,7 +54309,7 @@
       </c>
       <c r="CF148" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.7%))</t>
         </is>
       </c>
     </row>
@@ -54469,22 +54473,22 @@
         <v>14.22000026702881</v>
       </c>
       <c r="BC149" t="n">
-        <v>3.789460836050028</v>
+        <v>3.789460831778972</v>
       </c>
       <c r="BD149" t="n">
-        <v>5.517454977288841</v>
+        <v>5.517454971070183</v>
       </c>
       <c r="BE149" t="inlineStr"/>
       <c r="BF149" t="inlineStr"/>
       <c r="BG149" t="inlineStr"/>
       <c r="BH149" t="n">
-        <v>4.653457906669434</v>
+        <v>4.653457901424577</v>
       </c>
       <c r="BI149" t="n">
-        <v>4.653457906669434</v>
+        <v>4.653457901424577</v>
       </c>
       <c r="BJ149" t="n">
-        <v>4.188112116002491</v>
+        <v>4.18811211128212</v>
       </c>
       <c r="BK149" t="n">
         <v>2</v>
@@ -54496,10 +54500,10 @@
         <v>1.5</v>
       </c>
       <c r="BN149" t="n">
-        <v>-70.5477353209813</v>
+        <v>-70.5477353541766</v>
       </c>
       <c r="BO149" t="n">
-        <v>-67.27526146775699</v>
+        <v>-67.27526150464065</v>
       </c>
       <c r="BP149" t="inlineStr">
         <is>
@@ -55163,10 +55167,10 @@
         <v>16.06999969482422</v>
       </c>
       <c r="BC152" t="n">
-        <v>24.61860019838685</v>
+        <v>24.61860017985369</v>
       </c>
       <c r="BD152" t="n">
-        <v>33.41201315480128</v>
+        <v>33.41201312964834</v>
       </c>
       <c r="BE152" t="n">
         <v>2.679489710195444</v>
@@ -55175,7 +55179,7 @@
         <v>7.177426418428193</v>
       </c>
       <c r="BG152" t="n">
-        <v>6.851293459892135</v>
+        <v>6.851293455429388</v>
       </c>
       <c r="BH152" t="inlineStr"/>
       <c r="BI152" t="inlineStr"/>
